--- a/data/input/puma.xlsx
+++ b/data/input/puma.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Saowalak/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Saowalak/Desktop/CEOCommunication/data/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F87F266-071E-FE4B-9F14-9B36641BCF7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A41CC91-8584-2D47-87B2-CA2201111921}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2260" yWindow="600" windowWidth="26540" windowHeight="17400" activeTab="5" xr2:uid="{05EFD2A9-923A-834E-A816-A8C1AAE62552}"/>
+    <workbookView xWindow="9940" yWindow="600" windowWidth="18860" windowHeight="17400" xr2:uid="{05EFD2A9-923A-834E-A816-A8C1AAE62552}"/>
   </bookViews>
   <sheets>
     <sheet name="2020" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="67">
   <si>
     <t>ID</t>
   </si>
@@ -61,9 +61,6 @@
     <t>Covid</t>
   </si>
   <si>
-    <t>CEO</t>
-  </si>
-  <si>
     <t>Communication_type</t>
   </si>
   <si>
@@ -113,6 +110,143 @@
   </si>
   <si>
     <t xml:space="preserve">False </t>
+  </si>
+  <si>
+    <t>Source_type</t>
+  </si>
+  <si>
+    <t>Communicator_name</t>
+  </si>
+  <si>
+    <t>Communicator_role</t>
+  </si>
+  <si>
+    <t>annual_report</t>
+  </si>
+  <si>
+    <t>DEAR SHAREHOLDERS,</t>
+  </si>
+  <si>
+    <t>I hope this letter finds you healthy and in good spirit despite all the negative impact of COVID-19. 2020 was surely a very difficult year for all of us - for me it was definitely the most difficult year in my life.</t>
+  </si>
+  <si>
+    <t>We started the year 2020 with a very positive feeling: we had a very solid order book, our sales at the end of 2019 were strong, our new products were very well received and the start in January was also positive.</t>
+  </si>
+  <si>
+    <t>Then COVID-19 hit the city of Wuhan in China and we immediately set our focus on securing our supply chain as approx. 30% of our sourcing is done in the country as well as on reducing the damage from the “shutdown” of physical retail in China. During the first two weeks, we did not even think that this would turn into a global pandemic.</t>
+  </si>
+  <si>
+    <t>It then became obvious that COVID-19 was unfortunately spreading globally and that we were in a situation we had never been in before. We were in the middle of a worldwide pandemic in which basically all physical retail stores selling sports and sports-inspired products had to shut down globally during the months of March and April.</t>
+  </si>
+  <si>
+    <t>Back then we quickly focused on three main areas: Deal with COVID, continue to drive the business and continue to do the right thing, such as focusing on Sustainability and #REFORM.</t>
+  </si>
+  <si>
+    <t>Deal with COVID meant first and foremost to ensure the health and safety of our people. Among other things, this included the following measures: organize work from home wherever possible, set up digital communication tools, buy and distribute masks for our employees, organize regular testing (PCR and Quick Tests), sanitize our working spaces on a regular basis, install health and safety equipment in all our stores and in general do whatever we could to ensure that our PUMA employees felt as good and safe as possible. I am very proud of how our People &amp; Organization teams (previously called Human Resources) around the world worked and organized all these measures. So far, we have been lucky: none of our almost 16,000 employees has died of COVID-19 and “only” four colleagues were hospitalized, but recovered 100% and are fully back to work.</t>
+  </si>
+  <si>
+    <t>The second priority was to secure financing and liquidity. The uncertainty around the pandemic and its impact on our business has made us act quickly to secure as much financing as possible. We did not know if the lockdowns would last one month, two months or even longer. We prepared for a “worst case scenario” of a four-month lockdown and managed to get financing that would “keep us alive” throughout this period. A consortium of twelve banks led by the German state-owned Kreditanstalt für Wiederaufbau (KfW) gave us an additional credit line of € 900 million - together with existing credit facilities this provided us with a total financing of around €1,800 million.</t>
+  </si>
+  <si>
+    <t>We never used this additional credit line and it has been replaced by other credit facilities in the meantime. The KfW-led credit line was not a “gift” by the German state. It was a regular credit line for which we paid high, above-market fees for availability and that gave the KfW preference compared to other creditors. Nevertheless, this credit line was crucial for us because it gave us security and allowed us to make sound business decisions in a time of high uncertainty. I would like to thank the KfW and the other eleven banks for their fast and unbureaucratic processes, and for making this “life insurance” available to us.</t>
+  </si>
+  <si>
+    <t>The third priority was to quickly find solutions to continue working upstream with our retail partners and downstream with our suppliers. Our objective was to avoid high cancellations that could have caused massive problems for our suppliers including the loss of thousands of jobs among their employees. We offered all our retail partners delayed deliveries and extended payment terms. We slowed down shipments, asked our suppliers to slow down their production without laying off people and to extend payment terms by one month. We agreed to hold some inventories in the factories, some in temporary warehouses in Asia and of course in our normal warehouses. Most retailers agreed to this approach and I am very proud that we managed to get through 2020 with cancelling less than 1% of our orders with our suppliers. We continue to work with all of our suppliers and none of them had to lay off workers due to the crisis.</t>
+  </si>
+  <si>
+    <t>As most physical retail stores had to shut down globally in March and April, the eCommerce channels became even more important. Our focus was to strengthen our own puma.com channel, the marketplaces, the pure eCommerce players, but also the eCommerce channels of our Brick &amp; Mortar retail partners. This caused massive changes in our marketing activities with budget shifts to performance marketing and significant pressure on our logistics to service the increased eCommerce demand. I am very pleased on how quickly and flexible both our marketing and logistics teams acted during this turbulent time.</t>
+  </si>
+  <si>
+    <t>We also continued to drive the business during this period. This meant maximizing our sales short-term while at the same time investing into the development of new product ranges and strong marketing in order to continue the positive mid-term momentum for the brand. We did everything to please and service our retail partners in the best way possible, we rather gave deep discounts instead of building excess inventories, we continued to develop full new collections for the year 2021 and used the marketing opportunities that will benefit PUMA mid-term while we reduced our overall marketing spent. During the crisis, we signed football icon Neymar Jr., the most exciting rookie in the NBA LaMelo Ball, the currently most popular female artist Dua Lipa and the very youth culture relevant DJ Snake. All these exciting additions to the PUMA family were done because we are confident that they will further strengthen the relevance of our brand both during the pandemic and also later in the “new normal”.</t>
+  </si>
+  <si>
+    <t>I am very thankful that our supervisory board showed us their trust and support by allowing us to do these investments in the middle of the year.</t>
+  </si>
+  <si>
+    <t>We also continued to focus on what we call “do the right thing”. This includes both our social responsibility and the environmental sustainability of our business practices. We want to be a good corporate citizen and have a positive impact on our society as a whole. As part of our #REFORM platform, we focused on three main aspects: gender equality, an end to systematic racism and LGTBQ+ rights. Everybody on this planet should be treated equally and we at PUMA want to do our part to fight any form of discrimination. Sustainability also continued to be a key focus area for us, and we strive to leave the planet to our children in a better condition than we inherited it from our parents. In 2020, we launched our 10FOR25 sustainability targets which will guide our ambitious sustainability actions until 2025. We also continue to support the UN Global Compact and its 10 principles for sustainable development. We also launched multiple sustainable product collections as well as our new FOREVER BETTER communication platform. Both responsibility and sustainability are and will continue to be an important part of PUMA’s values.</t>
+  </si>
+  <si>
+    <t>After a very difficult second quarter during which most of the markets had either lockdowns or other restrictions, we experienced a very strong third quarter. In the third quarter, our Net Sales increased by 13.3% (in constant currency) to € 1,583 million – the highest revenue PUMA has ever had in a quarter – and the third quarter EBIT of € 190 million (12% of Net Sales) shows the potential of our company. The fourth quarter started with 25% growth in October before new restrictions, especially in Europe, slowed our revenue growth once again. We ended the fourth quarter with Net Sales being up 9.1% (in constant currency) and an EBIT of € 63 million (+15% vs last year).</t>
+  </si>
+  <si>
+    <t>The full financial year 2020 was “destroyed” mainly due to the terrible second quarter, but I hope that the strong second half of 2020 demonstrated the continued momentum of PUMA. We are very optimistic about the future of both the sports industry and for PUMA. During the pandemic, we have seen that the consumers continued to buy our products, queued up in front of the sneaker stores when they reopened, started to do more individual sports and we foresee team sports to “explode” again once the restrictions will be lifted. We see a continued trend for sportive casual wear both in footwear and apparel, comfort being more and more important to the consumer and sports brands still being in strong demand across all markets.</t>
+  </si>
+  <si>
+    <t>While we do not have a “crystal ball”, we clearly foresee that the pandemic will continue to have a negative impact on our business also in 2021. We believe that the negative impact will be strongest in the first half and believe that it will weaken during the second half. Given the uncertainty around the future development of the pandemic, we do not feel comfortable giving you a specific financial outlook for the full year. But as of today, we expect that 2021 will be a better financial year than 2020, both in terms of Net Sales and EBIT.</t>
+  </si>
+  <si>
+    <t>Let us hope that 2022 will be a “new normal” year.</t>
+  </si>
+  <si>
+    <t>Stay strong and stay healthy,
+Bjørn Gulden
+Chief Executive Officer PUMA</t>
+  </si>
+  <si>
+    <t>title</t>
+  </si>
+  <si>
+    <t>body_text</t>
+  </si>
+  <si>
+    <t>JPN20P01-00</t>
+  </si>
+  <si>
+    <t>JPN20P02-00</t>
+  </si>
+  <si>
+    <t>JPN20P03-00</t>
+  </si>
+  <si>
+    <t>JPN20P04-00</t>
+  </si>
+  <si>
+    <t>JPN20P05-00</t>
+  </si>
+  <si>
+    <t>JPN20P06-00</t>
+  </si>
+  <si>
+    <t>JPN20P07-00</t>
+  </si>
+  <si>
+    <t>JPN20P08-00</t>
+  </si>
+  <si>
+    <t>JPN20P09-00</t>
+  </si>
+  <si>
+    <t>JPN20P10-00</t>
+  </si>
+  <si>
+    <t>JPN20P11-00</t>
+  </si>
+  <si>
+    <t>JPN20P12-00</t>
+  </si>
+  <si>
+    <t>JPN20P13-00</t>
+  </si>
+  <si>
+    <t>JPN20P15-00</t>
+  </si>
+  <si>
+    <t>JPN20P16-00</t>
+  </si>
+  <si>
+    <t>JPN20P17-00</t>
+  </si>
+  <si>
+    <t>JPN20P18-00</t>
+  </si>
+  <si>
+    <t>JPN20P19-00</t>
+  </si>
+  <si>
+    <t>Bjørn Gulden</t>
+  </si>
+  <si>
+    <t>ceo</t>
   </si>
 </sst>
 </file>
@@ -166,7 +300,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="84">
+  <dxfs count="96">
     <dxf>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -198,6 +332,12 @@
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -210,6 +350,39 @@
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -253,9 +426,6 @@
     </dxf>
     <dxf>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -433,144 +603,156 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}" name="Tableau1" displayName="Tableau1" ref="A1:L2" totalsRowShown="0" headerRowDxfId="69" dataDxfId="68">
-  <autoFilter ref="A1:L2" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}" name="Tableau1" displayName="Tableau1" ref="A1:N20" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14">
+  <autoFilter ref="A1:N20" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N2">
     <sortCondition ref="A1:A2"/>
   </sortState>
-  <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{3EB1D0B3-009A-5A47-8B93-8EF6255B1304}" name="ID" dataDxfId="67"/>
-    <tableColumn id="2" xr3:uid="{DA8A41BF-F097-BC45-906C-4BABEC2244DD}" name="Text" dataDxfId="66"/>
-    <tableColumn id="3" xr3:uid="{2EF94B43-4C8E-044F-B78E-77B5B2C749ED}" name="Text_type" dataDxfId="65"/>
-    <tableColumn id="4" xr3:uid="{CCEEA6CD-C218-094D-9E25-C77D75EA7E8B}" name="Leadership_context" dataDxfId="64"/>
-    <tableColumn id="5" xr3:uid="{7597EAEA-F46D-374E-8954-A78718D8A002}" name="Information_valence" dataDxfId="63"/>
-    <tableColumn id="6" xr3:uid="{FAAD26A2-D031-3F47-A9AF-C78AE4508844}" name="Communication_type" dataDxfId="62"/>
-    <tableColumn id="7" xr3:uid="{0B866C2F-1672-9C45-8132-39C1E3DA8EAF}" name="Company" dataDxfId="61"/>
-    <tableColumn id="8" xr3:uid="{CC5E1A75-8194-974B-BC62-732998981044}" name="Country" dataDxfId="60"/>
-    <tableColumn id="9" xr3:uid="{3B4764F6-42C4-5740-9A0F-8733D2FFE2C1}" name="Year" dataDxfId="59"/>
-    <tableColumn id="10" xr3:uid="{DF6E8D3A-208E-A448-B107-E9C070DE225E}" name="Covid" dataDxfId="58"/>
-    <tableColumn id="11" xr3:uid="{C327315D-BA1F-BF4E-979D-02C312D440C8}" name="CEO" dataDxfId="57"/>
-    <tableColumn id="12" xr3:uid="{1977CE7B-3E0B-714D-8E54-438D9A354605}" name="Comment" dataDxfId="56"/>
+  <tableColumns count="14">
+    <tableColumn id="1" xr3:uid="{3EB1D0B3-009A-5A47-8B93-8EF6255B1304}" name="ID" dataDxfId="13"/>
+    <tableColumn id="2" xr3:uid="{DA8A41BF-F097-BC45-906C-4BABEC2244DD}" name="Text" dataDxfId="12"/>
+    <tableColumn id="3" xr3:uid="{2EF94B43-4C8E-044F-B78E-77B5B2C749ED}" name="Text_type" dataDxfId="11"/>
+    <tableColumn id="4" xr3:uid="{CCEEA6CD-C218-094D-9E25-C77D75EA7E8B}" name="Leadership_context" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{7597EAEA-F46D-374E-8954-A78718D8A002}" name="Information_valence" dataDxfId="9"/>
+    <tableColumn id="6" xr3:uid="{FAAD26A2-D031-3F47-A9AF-C78AE4508844}" name="Communication_type" dataDxfId="8"/>
+    <tableColumn id="14" xr3:uid="{DC551193-3E78-054D-9E02-55B526E3955D}" name="Source_type" dataDxfId="7"/>
+    <tableColumn id="7" xr3:uid="{0B866C2F-1672-9C45-8132-39C1E3DA8EAF}" name="Company" dataDxfId="6"/>
+    <tableColumn id="8" xr3:uid="{CC5E1A75-8194-974B-BC62-732998981044}" name="Country" dataDxfId="5"/>
+    <tableColumn id="9" xr3:uid="{3B4764F6-42C4-5740-9A0F-8733D2FFE2C1}" name="Year" dataDxfId="4"/>
+    <tableColumn id="10" xr3:uid="{DF6E8D3A-208E-A448-B107-E9C070DE225E}" name="Covid" dataDxfId="3"/>
+    <tableColumn id="13" xr3:uid="{CB3B9ED9-A903-D142-8C47-DBFE1BB21BB9}" name="Communicator_role" dataDxfId="2"/>
+    <tableColumn id="11" xr3:uid="{C327315D-BA1F-BF4E-979D-02C312D440C8}" name="Communicator_name" dataDxfId="1"/>
+    <tableColumn id="12" xr3:uid="{1977CE7B-3E0B-714D-8E54-438D9A354605}" name="Comment" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DA7F0E8F-45C6-6043-B094-E3D95B97FF2A}" name="Tableau13" displayName="Tableau13" ref="A1:L2" totalsRowShown="0" headerRowDxfId="83" dataDxfId="82">
-  <autoFilter ref="A1:L2" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DA7F0E8F-45C6-6043-B094-E3D95B97FF2A}" name="Tableau13" displayName="Tableau13" ref="A1:N2" totalsRowShown="0" headerRowDxfId="81" dataDxfId="80">
+  <autoFilter ref="A1:N2" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N2">
     <sortCondition ref="A1:A2"/>
   </sortState>
-  <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{CEF716DC-F71C-F64A-9417-BFA8F7223C3C}" name="ID" dataDxfId="81"/>
-    <tableColumn id="2" xr3:uid="{E18EF473-8BB2-B249-A671-AEC1D227D58C}" name="Text" dataDxfId="80"/>
-    <tableColumn id="3" xr3:uid="{43ED120E-0AAC-5B48-BFFE-E2FEDCE871CC}" name="Text_type" dataDxfId="79"/>
-    <tableColumn id="4" xr3:uid="{C80CD8E5-01BF-A441-83A4-5AD3DB190355}" name="Leadership_context" dataDxfId="78"/>
-    <tableColumn id="5" xr3:uid="{923FAB0A-F1C7-8C4E-9079-3F151BDD8845}" name="Information_valence" dataDxfId="77"/>
-    <tableColumn id="6" xr3:uid="{68020A6C-474C-354D-9F87-DDFAD6E6FCBF}" name="Communication_type" dataDxfId="76"/>
-    <tableColumn id="7" xr3:uid="{BE35D812-E006-C241-B735-D50938782E5F}" name="Company" dataDxfId="75"/>
-    <tableColumn id="8" xr3:uid="{D7B81200-66AC-0046-9542-315523411E25}" name="Country" dataDxfId="74"/>
-    <tableColumn id="9" xr3:uid="{79CD73A8-8993-8248-A866-07B7E35F6DCB}" name="Year" dataDxfId="73"/>
-    <tableColumn id="10" xr3:uid="{9CEEE324-6A65-1042-8C7C-96F54D0F2756}" name="Covid" dataDxfId="72"/>
-    <tableColumn id="11" xr3:uid="{64EE7B30-27FC-9945-8BF4-F74D9FF6D07C}" name="CEO" dataDxfId="71"/>
-    <tableColumn id="12" xr3:uid="{5C43064B-4CDF-ED4E-B988-64FD2F0806AA}" name="Comment" dataDxfId="70"/>
+  <tableColumns count="14">
+    <tableColumn id="1" xr3:uid="{CEF716DC-F71C-F64A-9417-BFA8F7223C3C}" name="ID" dataDxfId="79"/>
+    <tableColumn id="2" xr3:uid="{E18EF473-8BB2-B249-A671-AEC1D227D58C}" name="Text" dataDxfId="78"/>
+    <tableColumn id="3" xr3:uid="{43ED120E-0AAC-5B48-BFFE-E2FEDCE871CC}" name="Text_type" dataDxfId="77"/>
+    <tableColumn id="4" xr3:uid="{C80CD8E5-01BF-A441-83A4-5AD3DB190355}" name="Leadership_context" dataDxfId="76"/>
+    <tableColumn id="5" xr3:uid="{923FAB0A-F1C7-8C4E-9079-3F151BDD8845}" name="Information_valence" dataDxfId="75"/>
+    <tableColumn id="6" xr3:uid="{68020A6C-474C-354D-9F87-DDFAD6E6FCBF}" name="Communication_type" dataDxfId="74"/>
+    <tableColumn id="13" xr3:uid="{DD700407-60FC-C348-A601-E8685620E07F}" name="Source_type" dataDxfId="17"/>
+    <tableColumn id="7" xr3:uid="{BE35D812-E006-C241-B735-D50938782E5F}" name="Company" dataDxfId="73"/>
+    <tableColumn id="8" xr3:uid="{D7B81200-66AC-0046-9542-315523411E25}" name="Country" dataDxfId="72"/>
+    <tableColumn id="9" xr3:uid="{79CD73A8-8993-8248-A866-07B7E35F6DCB}" name="Year" dataDxfId="71"/>
+    <tableColumn id="10" xr3:uid="{9CEEE324-6A65-1042-8C7C-96F54D0F2756}" name="Covid" dataDxfId="70"/>
+    <tableColumn id="14" xr3:uid="{18CC61B1-AC23-BA4F-B2B3-2D2FB5AC969E}" name="Communicator_role" dataDxfId="16"/>
+    <tableColumn id="11" xr3:uid="{64EE7B30-27FC-9945-8BF4-F74D9FF6D07C}" name="Communicator_name" dataDxfId="69"/>
+    <tableColumn id="12" xr3:uid="{5C43064B-4CDF-ED4E-B988-64FD2F0806AA}" name="Comment" dataDxfId="68"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{C7C650FA-A8BE-374F-A02C-24C279A2D67A}" name="Tableau134" displayName="Tableau134" ref="A1:L2" totalsRowShown="0" headerRowDxfId="55" dataDxfId="54">
-  <autoFilter ref="A1:L2" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{C7C650FA-A8BE-374F-A02C-24C279A2D67A}" name="Tableau134" displayName="Tableau134" ref="A1:N2" totalsRowShown="0" headerRowDxfId="67" dataDxfId="66">
+  <autoFilter ref="A1:N2" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N2">
     <sortCondition ref="A1:A2"/>
   </sortState>
-  <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{E398D18F-D9B1-8C4A-B81C-4F23A58404BA}" name="ID" dataDxfId="53"/>
-    <tableColumn id="2" xr3:uid="{41682781-F3C4-A842-B6E4-CD72DE688AF5}" name="Text" dataDxfId="52"/>
-    <tableColumn id="3" xr3:uid="{C1B517F2-40CD-8F40-9B4C-E34FFCCE3881}" name="Text_type" dataDxfId="51"/>
-    <tableColumn id="4" xr3:uid="{74E0C65C-5577-A146-9EE5-20C594C4316D}" name="Leadership_context" dataDxfId="50"/>
-    <tableColumn id="5" xr3:uid="{DDC33EC8-2DCC-DF43-9A08-EC991A2EA183}" name="Information_valence" dataDxfId="49"/>
-    <tableColumn id="6" xr3:uid="{C7BBAC6F-3D8E-B149-B9F0-D0A909FCC061}" name="Communication_type" dataDxfId="48"/>
-    <tableColumn id="7" xr3:uid="{3FFDDD67-7E94-CE4D-B56E-DFAC9F1681E3}" name="Company" dataDxfId="47"/>
-    <tableColumn id="8" xr3:uid="{342E13F5-266B-7B42-BD6B-BB868EA49B97}" name="Country" dataDxfId="46"/>
-    <tableColumn id="9" xr3:uid="{69240109-8B46-AB43-AD07-1F40DB5F9C94}" name="Year" dataDxfId="45"/>
-    <tableColumn id="10" xr3:uid="{5ED27922-9168-D142-BBEF-32C7AE06ABD3}" name="Covid" dataDxfId="44"/>
-    <tableColumn id="11" xr3:uid="{C38872CB-C9B9-1249-9741-B341922B9857}" name="CEO" dataDxfId="43"/>
-    <tableColumn id="12" xr3:uid="{DBF7903A-F082-FB40-B41C-987ABF6BC279}" name="Comment" dataDxfId="42"/>
+  <tableColumns count="14">
+    <tableColumn id="1" xr3:uid="{E398D18F-D9B1-8C4A-B81C-4F23A58404BA}" name="ID" dataDxfId="65"/>
+    <tableColumn id="2" xr3:uid="{41682781-F3C4-A842-B6E4-CD72DE688AF5}" name="Text" dataDxfId="64"/>
+    <tableColumn id="3" xr3:uid="{C1B517F2-40CD-8F40-9B4C-E34FFCCE3881}" name="Text_type" dataDxfId="63"/>
+    <tableColumn id="4" xr3:uid="{74E0C65C-5577-A146-9EE5-20C594C4316D}" name="Leadership_context" dataDxfId="62"/>
+    <tableColumn id="5" xr3:uid="{DDC33EC8-2DCC-DF43-9A08-EC991A2EA183}" name="Information_valence" dataDxfId="61"/>
+    <tableColumn id="6" xr3:uid="{C7BBAC6F-3D8E-B149-B9F0-D0A909FCC061}" name="Communication_type" dataDxfId="60"/>
+    <tableColumn id="14" xr3:uid="{DA857B5E-985B-B946-AB84-87E571EEF3AB}" name="Source_type" dataDxfId="18"/>
+    <tableColumn id="7" xr3:uid="{3FFDDD67-7E94-CE4D-B56E-DFAC9F1681E3}" name="Company" dataDxfId="59"/>
+    <tableColumn id="8" xr3:uid="{342E13F5-266B-7B42-BD6B-BB868EA49B97}" name="Country" dataDxfId="58"/>
+    <tableColumn id="9" xr3:uid="{69240109-8B46-AB43-AD07-1F40DB5F9C94}" name="Year" dataDxfId="57"/>
+    <tableColumn id="10" xr3:uid="{5ED27922-9168-D142-BBEF-32C7AE06ABD3}" name="Covid" dataDxfId="56"/>
+    <tableColumn id="13" xr3:uid="{0563ACCB-80F5-4F46-ADA0-9040F1D87085}" name="Communicator_role" dataDxfId="19"/>
+    <tableColumn id="11" xr3:uid="{C38872CB-C9B9-1249-9741-B341922B9857}" name="Communicator_name" dataDxfId="55"/>
+    <tableColumn id="12" xr3:uid="{DBF7903A-F082-FB40-B41C-987ABF6BC279}" name="Comment" dataDxfId="54"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{49AA2418-AB03-1149-B07A-3CC5FF67C997}" name="Tableau1345" displayName="Tableau1345" ref="A1:L2" totalsRowShown="0" headerRowDxfId="41" dataDxfId="40">
-  <autoFilter ref="A1:L2" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{49AA2418-AB03-1149-B07A-3CC5FF67C997}" name="Tableau1345" displayName="Tableau1345" ref="A1:N2" totalsRowShown="0" headerRowDxfId="53" dataDxfId="52">
+  <autoFilter ref="A1:N2" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N2">
     <sortCondition ref="A1:A2"/>
   </sortState>
-  <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{E88F34DD-82B0-AD49-8C17-D8E9CFF03D07}" name="ID" dataDxfId="39"/>
-    <tableColumn id="2" xr3:uid="{88FC91F1-83E8-1B40-AC59-24D584573CCF}" name="Text" dataDxfId="38"/>
-    <tableColumn id="3" xr3:uid="{15432912-C615-E748-A229-EAA1D750204D}" name="Text_type" dataDxfId="37"/>
-    <tableColumn id="4" xr3:uid="{1025B200-F152-0B42-88C1-A31B3C27DB9E}" name="Leadership_context" dataDxfId="36"/>
-    <tableColumn id="5" xr3:uid="{D41F3D09-61AB-B841-88C7-5242CDC613BF}" name="Information_valence" dataDxfId="35"/>
-    <tableColumn id="6" xr3:uid="{CE749A1F-4ED8-1C40-9BE6-FB737E09C230}" name="Communication_type" dataDxfId="34"/>
-    <tableColumn id="7" xr3:uid="{A6F61E0C-8D32-F54F-8B88-CFAABE31D5B0}" name="Company" dataDxfId="33"/>
-    <tableColumn id="8" xr3:uid="{84CFAC4D-579E-AA4B-9DFE-FB605F75FBA9}" name="Country" dataDxfId="32"/>
-    <tableColumn id="9" xr3:uid="{1BA4063C-1918-624B-9757-FC2F3E5A7EE2}" name="Year" dataDxfId="31"/>
-    <tableColumn id="10" xr3:uid="{82840B5F-FD1C-614B-9755-28207407D6E2}" name="Covid" dataDxfId="30"/>
-    <tableColumn id="11" xr3:uid="{3C67D01C-1B28-EB45-A3B2-FA7774BA5A24}" name="CEO" dataDxfId="29"/>
-    <tableColumn id="12" xr3:uid="{7581B405-4702-5B40-9BBE-C98F342B9125}" name="Comment" dataDxfId="28"/>
+  <tableColumns count="14">
+    <tableColumn id="1" xr3:uid="{E88F34DD-82B0-AD49-8C17-D8E9CFF03D07}" name="ID" dataDxfId="51"/>
+    <tableColumn id="2" xr3:uid="{88FC91F1-83E8-1B40-AC59-24D584573CCF}" name="Text" dataDxfId="50"/>
+    <tableColumn id="3" xr3:uid="{15432912-C615-E748-A229-EAA1D750204D}" name="Text_type" dataDxfId="49"/>
+    <tableColumn id="4" xr3:uid="{1025B200-F152-0B42-88C1-A31B3C27DB9E}" name="Leadership_context" dataDxfId="48"/>
+    <tableColumn id="5" xr3:uid="{D41F3D09-61AB-B841-88C7-5242CDC613BF}" name="Information_valence" dataDxfId="47"/>
+    <tableColumn id="6" xr3:uid="{CE749A1F-4ED8-1C40-9BE6-FB737E09C230}" name="Communication_type" dataDxfId="46"/>
+    <tableColumn id="13" xr3:uid="{BDC21215-E7B5-5C4C-B5AB-80E86EA24E05}" name="Source_type" dataDxfId="22"/>
+    <tableColumn id="7" xr3:uid="{A6F61E0C-8D32-F54F-8B88-CFAABE31D5B0}" name="Company" dataDxfId="45"/>
+    <tableColumn id="8" xr3:uid="{84CFAC4D-579E-AA4B-9DFE-FB605F75FBA9}" name="Country" dataDxfId="44"/>
+    <tableColumn id="9" xr3:uid="{1BA4063C-1918-624B-9757-FC2F3E5A7EE2}" name="Year" dataDxfId="43"/>
+    <tableColumn id="10" xr3:uid="{82840B5F-FD1C-614B-9755-28207407D6E2}" name="Covid" dataDxfId="42"/>
+    <tableColumn id="14" xr3:uid="{3F460577-A4A9-C947-8FBE-832A71AF2E55}" name="Communicator_role" dataDxfId="20"/>
+    <tableColumn id="11" xr3:uid="{3C67D01C-1B28-EB45-A3B2-FA7774BA5A24}" name="Communicator_name" dataDxfId="21"/>
+    <tableColumn id="12" xr3:uid="{7581B405-4702-5B40-9BBE-C98F342B9125}" name="Comment" dataDxfId="41"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{3E6C7F84-1A88-2149-AAB1-B94EF8830151}" name="Tableau13456" displayName="Tableau13456" ref="A1:L2" totalsRowShown="0" headerRowDxfId="27" dataDxfId="26">
-  <autoFilter ref="A1:L2" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{3E6C7F84-1A88-2149-AAB1-B94EF8830151}" name="Tableau13456" displayName="Tableau13456" ref="A1:N2" totalsRowShown="0" headerRowDxfId="40" dataDxfId="39">
+  <autoFilter ref="A1:N2" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N2">
     <sortCondition ref="A1:A2"/>
   </sortState>
-  <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{86F19330-6E72-0543-BBCC-6D193B41E96F}" name="ID" dataDxfId="25"/>
-    <tableColumn id="2" xr3:uid="{6C469BD5-B4CF-8D4F-A2F6-F0E834902E4A}" name="Text" dataDxfId="24"/>
-    <tableColumn id="3" xr3:uid="{FE673CA5-CBC5-A34F-8A0C-C1CD6D144617}" name="Text_type" dataDxfId="23"/>
-    <tableColumn id="4" xr3:uid="{4248AFAD-ABBE-A942-8BC5-6258F7CF5E07}" name="Leadership_context" dataDxfId="22"/>
-    <tableColumn id="5" xr3:uid="{9D393B8E-A5EB-6240-B5FD-D449006530E5}" name="Information_valence" dataDxfId="21"/>
-    <tableColumn id="6" xr3:uid="{9677B29B-2D61-544A-85E3-A9C0FF7FBFCF}" name="Communication_type" dataDxfId="20"/>
-    <tableColumn id="7" xr3:uid="{9949BF20-7E90-2D45-A547-C4EF102C2AF9}" name="Company" dataDxfId="19"/>
-    <tableColumn id="8" xr3:uid="{5676BCFB-C3B1-444F-8A31-FAE43C2412E4}" name="Country" dataDxfId="18"/>
-    <tableColumn id="9" xr3:uid="{065AECA5-A4C6-784E-B897-9C586B53EEC2}" name="Year" dataDxfId="17"/>
-    <tableColumn id="10" xr3:uid="{9FE554FC-C9E9-BD44-8CBB-7E5AF11D1DDA}" name="Covid" dataDxfId="16"/>
-    <tableColumn id="11" xr3:uid="{3C88AB16-0597-6246-B1EA-CED5E74629EC}" name="CEO" dataDxfId="15"/>
-    <tableColumn id="12" xr3:uid="{75A6A75A-B89A-C341-99C3-8E0AF84308E5}" name="Comment" dataDxfId="14"/>
+  <tableColumns count="14">
+    <tableColumn id="1" xr3:uid="{86F19330-6E72-0543-BBCC-6D193B41E96F}" name="ID" dataDxfId="38"/>
+    <tableColumn id="2" xr3:uid="{6C469BD5-B4CF-8D4F-A2F6-F0E834902E4A}" name="Text" dataDxfId="37"/>
+    <tableColumn id="3" xr3:uid="{FE673CA5-CBC5-A34F-8A0C-C1CD6D144617}" name="Text_type" dataDxfId="36"/>
+    <tableColumn id="4" xr3:uid="{4248AFAD-ABBE-A942-8BC5-6258F7CF5E07}" name="Leadership_context" dataDxfId="35"/>
+    <tableColumn id="5" xr3:uid="{9D393B8E-A5EB-6240-B5FD-D449006530E5}" name="Information_valence" dataDxfId="34"/>
+    <tableColumn id="6" xr3:uid="{9677B29B-2D61-544A-85E3-A9C0FF7FBFCF}" name="Communication_type" dataDxfId="33"/>
+    <tableColumn id="14" xr3:uid="{5175FC7C-275C-FB4E-8512-D7A2B81AEEA9}" name="Source_type" dataDxfId="23"/>
+    <tableColumn id="7" xr3:uid="{9949BF20-7E90-2D45-A547-C4EF102C2AF9}" name="Company" dataDxfId="32"/>
+    <tableColumn id="8" xr3:uid="{5676BCFB-C3B1-444F-8A31-FAE43C2412E4}" name="Country" dataDxfId="31"/>
+    <tableColumn id="9" xr3:uid="{065AECA5-A4C6-784E-B897-9C586B53EEC2}" name="Year" dataDxfId="30"/>
+    <tableColumn id="10" xr3:uid="{9FE554FC-C9E9-BD44-8CBB-7E5AF11D1DDA}" name="Covid" dataDxfId="29"/>
+    <tableColumn id="13" xr3:uid="{93285A16-1AFB-F940-A523-560D3B0D9284}" name="Communicator_role" dataDxfId="24"/>
+    <tableColumn id="11" xr3:uid="{3C88AB16-0597-6246-B1EA-CED5E74629EC}" name="Communicator_name" dataDxfId="28"/>
+    <tableColumn id="12" xr3:uid="{75A6A75A-B89A-C341-99C3-8E0AF84308E5}" name="Comment" dataDxfId="27"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{4E11BC3F-0045-1646-B076-F2B520D6852E}" name="Tableau134567" displayName="Tableau134567" ref="A1:L2" totalsRowShown="0" headerRowDxfId="13" dataDxfId="12">
-  <autoFilter ref="A1:L2" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{4E11BC3F-0045-1646-B076-F2B520D6852E}" name="Tableau134567" displayName="Tableau134567" ref="A1:N2" totalsRowShown="0" headerRowDxfId="95" dataDxfId="94">
+  <autoFilter ref="A1:N2" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N2">
     <sortCondition ref="A1:A2"/>
   </sortState>
-  <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{31CE9BA4-76C4-7243-9CC4-2D69B48697C4}" name="ID" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{E9507622-53C7-7C46-AD19-75B0C284C739}" name="Text" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{B61A97EA-38E3-824E-AFFF-6DA5B0F5F799}" name="Text_type" dataDxfId="9"/>
-    <tableColumn id="4" xr3:uid="{C4A6AEE0-93C2-654B-AED8-9DFE0C336FBC}" name="Leadership_context" dataDxfId="8"/>
-    <tableColumn id="5" xr3:uid="{8B799C91-B83E-4740-8FF8-D018A500B838}" name="Information_valence" dataDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{66E32C8C-3CF0-FF4A-8434-3DDE14801826}" name="Communication_type" dataDxfId="6"/>
-    <tableColumn id="7" xr3:uid="{BB1E2451-7FCA-A546-B2ED-629286E517B1}" name="Company" dataDxfId="5"/>
-    <tableColumn id="8" xr3:uid="{A7D9EB9F-21C3-A443-AA66-25E92544A3D1}" name="Country" dataDxfId="4"/>
-    <tableColumn id="9" xr3:uid="{B9243626-106E-F940-9214-C16A4B219151}" name="Year" dataDxfId="3"/>
-    <tableColumn id="10" xr3:uid="{F1B3134A-8772-B940-A033-7567227076E7}" name="Covid" dataDxfId="2"/>
-    <tableColumn id="11" xr3:uid="{AB9A4529-C11B-2A4B-9D39-3BBE9A62DD87}" name="CEO" dataDxfId="1"/>
-    <tableColumn id="12" xr3:uid="{A2188241-51A1-7D40-927A-99ACD6E9501D}" name="Comment" dataDxfId="0"/>
+  <tableColumns count="14">
+    <tableColumn id="1" xr3:uid="{31CE9BA4-76C4-7243-9CC4-2D69B48697C4}" name="ID" dataDxfId="93"/>
+    <tableColumn id="2" xr3:uid="{E9507622-53C7-7C46-AD19-75B0C284C739}" name="Text" dataDxfId="92"/>
+    <tableColumn id="3" xr3:uid="{B61A97EA-38E3-824E-AFFF-6DA5B0F5F799}" name="Text_type" dataDxfId="91"/>
+    <tableColumn id="4" xr3:uid="{C4A6AEE0-93C2-654B-AED8-9DFE0C336FBC}" name="Leadership_context" dataDxfId="90"/>
+    <tableColumn id="5" xr3:uid="{8B799C91-B83E-4740-8FF8-D018A500B838}" name="Information_valence" dataDxfId="89"/>
+    <tableColumn id="6" xr3:uid="{66E32C8C-3CF0-FF4A-8434-3DDE14801826}" name="Communication_type" dataDxfId="88"/>
+    <tableColumn id="13" xr3:uid="{0421BDDD-F24B-E84B-BE66-A9572A63BB7E}" name="Source_type" dataDxfId="26"/>
+    <tableColumn id="7" xr3:uid="{BB1E2451-7FCA-A546-B2ED-629286E517B1}" name="Company" dataDxfId="87"/>
+    <tableColumn id="8" xr3:uid="{A7D9EB9F-21C3-A443-AA66-25E92544A3D1}" name="Country" dataDxfId="86"/>
+    <tableColumn id="9" xr3:uid="{B9243626-106E-F940-9214-C16A4B219151}" name="Year" dataDxfId="85"/>
+    <tableColumn id="10" xr3:uid="{F1B3134A-8772-B940-A033-7567227076E7}" name="Covid" dataDxfId="84"/>
+    <tableColumn id="14" xr3:uid="{2561A683-C0E9-A44B-9AEB-9C3356F44833}" name="Communicator_role" dataDxfId="25"/>
+    <tableColumn id="11" xr3:uid="{AB9A4529-C11B-2A4B-9D39-3BBE9A62DD87}" name="Communicator_name" dataDxfId="83"/>
+    <tableColumn id="12" xr3:uid="{A2188241-51A1-7D40-927A-99ACD6E9501D}" name="Comment" dataDxfId="82"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -893,74 +1075,671 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3826A9C-6C80-494E-9252-B920A5705A8F}">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:N20"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="64.1640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="86" style="1" customWidth="1"/>
     <col min="3" max="3" width="12.5" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18.83203125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="19.6640625" style="1" customWidth="1"/>
-    <col min="7" max="10" width="10.83203125" style="1"/>
-    <col min="11" max="11" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="59.6640625" style="2" customWidth="1"/>
+    <col min="6" max="7" width="19.6640625" style="1" customWidth="1"/>
+    <col min="8" max="11" width="10.83203125" style="1"/>
+    <col min="12" max="12" width="20.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="21.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="59.6640625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" ht="17" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J2" s="1">
+        <v>2020</v>
+      </c>
+      <c r="K2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B2" s="2"/>
-      <c r="G2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="I2" s="1">
+      <c r="L2" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="51" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J3" s="1">
         <v>2020</v>
       </c>
-      <c r="J2" s="1" t="s">
-        <v>11</v>
+      <c r="K3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="51" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J4" s="1">
+        <v>2020</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="68" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J5" s="1">
+        <v>2020</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="68" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J6" s="1">
+        <v>2020</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="51" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J7" s="1">
+        <v>2020</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="170" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J8" s="1">
+        <v>2020</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="136" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J9" s="1">
+        <v>2020</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="136" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J10" s="1">
+        <v>2020</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="170" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J11" s="1">
+        <v>2020</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="119" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J12" s="1">
+        <v>2020</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="170" x14ac:dyDescent="0.2">
+      <c r="A13" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J13" s="1">
+        <v>2020</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M13" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="34" x14ac:dyDescent="0.2">
+      <c r="A14" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J14" s="1">
+        <v>2020</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M14" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="204" x14ac:dyDescent="0.2">
+      <c r="A15" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J15" s="1">
+        <v>2020</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M15" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="119" x14ac:dyDescent="0.2">
+      <c r="A16" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J16" s="1">
+        <v>2020</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L16" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M16" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="136" x14ac:dyDescent="0.2">
+      <c r="A17" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J17" s="1">
+        <v>2020</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L17" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M17" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="102" x14ac:dyDescent="0.2">
+      <c r="A18" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J18" s="1">
+        <v>2020</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L18" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M18" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="17" x14ac:dyDescent="0.2">
+      <c r="A19" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J19" s="1">
+        <v>2020</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L19" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M19" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="51" x14ac:dyDescent="0.2">
+      <c r="A20" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J20" s="1">
+        <v>2020</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M20" s="1" t="s">
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -974,7 +1753,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAD18CE3-D2D1-DD49-8602-5C2A7C693BA7}">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
@@ -982,66 +1761,76 @@
     <col min="3" max="3" width="12.5" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18.83203125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="19.6640625" style="1" customWidth="1"/>
-    <col min="7" max="10" width="10.83203125" style="1"/>
-    <col min="11" max="11" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="59.6640625" style="2" customWidth="1"/>
+    <col min="6" max="7" width="19.6640625" style="1" customWidth="1"/>
+    <col min="8" max="11" width="10.83203125" style="1"/>
+    <col min="12" max="12" width="20.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="21.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="59.6640625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="N1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B2" s="2"/>
       <c r="G2" s="1" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="I2" s="1">
+        <v>12</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J2" s="1">
         <v>2021</v>
       </c>
-      <c r="J2" s="1" t="s">
-        <v>11</v>
+      <c r="K2" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1054,7 +1843,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8482D037-842C-3D44-82D2-0DCAF2D2098B}">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
@@ -1062,66 +1851,76 @@
     <col min="3" max="3" width="12.5" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18.83203125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="19.6640625" style="1" customWidth="1"/>
-    <col min="7" max="10" width="10.83203125" style="1"/>
-    <col min="11" max="11" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="59.6640625" style="2" customWidth="1"/>
+    <col min="6" max="7" width="19.6640625" style="1" customWidth="1"/>
+    <col min="8" max="11" width="10.83203125" style="1"/>
+    <col min="12" max="12" width="20.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="21.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="59.6640625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="N1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B2" s="2"/>
       <c r="G2" s="1" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="I2" s="1">
+        <v>12</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J2" s="1">
         <v>2022</v>
       </c>
-      <c r="J2" s="1" t="s">
-        <v>11</v>
+      <c r="K2" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1134,7 +1933,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C026E3D-BA89-8B46-8C08-84D4DE3BA69B}">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
@@ -1142,66 +1941,76 @@
     <col min="3" max="3" width="12.5" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18.83203125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="19.6640625" style="1" customWidth="1"/>
-    <col min="7" max="10" width="10.83203125" style="1"/>
-    <col min="11" max="11" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="59.6640625" style="2" customWidth="1"/>
+    <col min="6" max="7" width="19.6640625" style="1" customWidth="1"/>
+    <col min="8" max="11" width="10.83203125" style="1"/>
+    <col min="12" max="12" width="20.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="21.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="59.6640625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="N1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B2" s="2"/>
       <c r="G2" s="1" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="I2" s="1">
+        <v>12</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J2" s="1">
         <v>2023</v>
       </c>
-      <c r="J2" s="1" t="s">
-        <v>11</v>
+      <c r="K2" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1214,7 +2023,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46F01D49-A94C-464D-86C0-23DAAD0A1777}">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
@@ -1222,66 +2031,76 @@
     <col min="3" max="3" width="12.5" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18.83203125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="19.6640625" style="1" customWidth="1"/>
-    <col min="7" max="10" width="10.83203125" style="1"/>
-    <col min="11" max="11" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="59.6640625" style="2" customWidth="1"/>
+    <col min="6" max="7" width="19.6640625" style="1" customWidth="1"/>
+    <col min="8" max="11" width="10.83203125" style="1"/>
+    <col min="12" max="12" width="20.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="21.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="59.6640625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="N1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B2" s="2"/>
       <c r="G2" s="1" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="I2" s="1">
+        <v>12</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J2" s="1">
         <v>2024</v>
       </c>
-      <c r="J2" s="1" t="s">
-        <v>20</v>
+      <c r="K2" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -1294,7 +2113,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F043F7F6-3A06-0B46-BD8B-5A267CD4419E}">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
@@ -1302,66 +2121,76 @@
     <col min="3" max="3" width="12.5" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18.83203125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="19.6640625" style="1" customWidth="1"/>
-    <col min="7" max="10" width="10.83203125" style="1"/>
-    <col min="11" max="11" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="59.6640625" style="2" customWidth="1"/>
+    <col min="6" max="7" width="19.6640625" style="1" customWidth="1"/>
+    <col min="8" max="11" width="10.83203125" style="1"/>
+    <col min="12" max="12" width="20.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="59.6640625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="N1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B2" s="2"/>
       <c r="G2" s="1" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="I2" s="1">
+        <v>12</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J2" s="1">
         <v>2025</v>
       </c>
-      <c r="J2" s="1" t="s">
-        <v>22</v>
+      <c r="K2" s="1" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/data/input/puma.xlsx
+++ b/data/input/puma.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Saowalak/Desktop/CEOCommunication/data/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A41CC91-8584-2D47-87B2-CA2201111921}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{678E623C-AB8D-1C40-977D-5718C03E6851}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9940" yWindow="600" windowWidth="18860" windowHeight="17400" xr2:uid="{05EFD2A9-923A-834E-A816-A8C1AAE62552}"/>
+    <workbookView xWindow="280" yWindow="600" windowWidth="28520" windowHeight="17400" activeTab="2" xr2:uid="{05EFD2A9-923A-834E-A816-A8C1AAE62552}"/>
   </bookViews>
   <sheets>
     <sheet name="2020" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="137">
   <si>
     <t>ID</t>
   </si>
@@ -247,6 +247,221 @@
   </si>
   <si>
     <t>ceo</t>
+  </si>
+  <si>
+    <t>I hope this letter finds you well despite the current challenges around the world. After more than two years, the COVID-19 pandemic still has a negative impact on our daily lives and business and now we’re also facing a conflict in the heart of Europe that is causing terrible human suffering.</t>
+  </si>
+  <si>
+    <t>We’re in constant dialogue with all our stakeholders in Ukraine and we do our utmost to support our local employees and their families as well as all our partners, ambassadors, and athletes wherever we can. Ensuring the health and safety of our people continues to be our number one priority, as we have already demonstrated throughout the COVID-19 pandemic. We have set up a safe house in Ukraine, we are delivering food, water, and other necessities directly to our people and we are helping women and children who want to leave the country. We currently have 40 women and children in accommodation in Poland and about 120 here in Germany. Many of the adults have already started working and most of the children are already attending schools and kindergarten. Their positive attitude and mindset, as well as their willingness to work and integrate, is remarkable. They are strong and positive people. I sincerely hope that this conflict will be solved diplomatically as soon as possible, that further bloodshed can be avoided and that peace will be restored.</t>
+  </si>
+  <si>
+    <t>While we are most concerned about the lives and livelihoods of the people who are directly affected in Ukraine and by the COVID-19 pandemic, the conflict as well as the pandemic also have a significant business impact on our sector and on PUMA. In addition to the impact on our operations in Russia and Ukraine, we continue to face some of the challenges that we already saw during the course of 2021: COVID-19 related lockdowns and restrictions in different parts of the world, a weak consumer sentiment in some key markets, significant challenges in our supply chain, strong inflationary pressures, and geopolitical tensions.</t>
+  </si>
+  <si>
+    <t>Despite all these challenges, 2021 was a very successful year for us. To be specific, it was the best year in PUMA’s history. Due to our continued brand momentum combined with high operational flexibility and a fantastic effort from our employees, our sales grew by 32% to EUR 6,805m and EBIT grew by 166% to EUR 557m. Compared to the pre-pandemic level of 2019, our sales increased by 30%, resulting in a two-year CAGR of around 15% during these challenging times. Our strategy of working closely together with all our suppliers and retail partners to manage short-term issues without hindering our mid-term momentum continued to pay off. Our external partners supported us in an extraordinary way and the dedication and commitment of all our employees during such a challenging year was truly exceptional. A lot of our employees went far beyond what a company can expect from them and in the name of the entire PUMA Board, I would like to thank everyone for their contribution towards making these results possible. People make the difference and our PUMA family is our biggest strength and asset.</t>
+  </si>
+  <si>
+    <t>Throughout 2021, we continued to focus on the three main areas that we defined in early 2020 in reaction to the COVID-19 pandemic: Deal with COVID, continue to drive the business and continue to do the right thing in areas such as social responsibility and environmental sustainability.</t>
+  </si>
+  <si>
+    <t>Dealing with COVID first and foremost meant ensuring the health and safety of our people and everyone in our value chain. We continued to adopt and comply with very strict health and safety measures across our operations and rolled out vaccination programs for our employees in countries where this was possible. This helped us achieve a vaccination rate of more than 90% at our headquarters in Herzogenaurach by mid-July. At the end of the year, we followed up with booster vaccinations. I would once again like to thank our People &amp; Organization teams (formerly known as Human Resources) around the world for successfully managing a second year of COVID-19 and supporting our employees in the best way possible.</t>
+  </si>
+  <si>
+    <t>Until around the first quarter 2021, the COVID-19 pandemic mainly impacted the store operations of our own retail organization and of our retail partners due to mandatory store closures and other restrictions. This was followed by significant disruptions in our supply chain due to lockdowns and factory closures in key sourcing countries such as Bangladesh, Cambodia, China and Vietnam. Especially, the lockdown in the third quarter in 2021 in the south of Vietnam, one of our most important sourcing destinations, had a very negative impact on our supply chain. Due to strict local lockdown measures, the production at our footwear, apparel and accessories suppliers in the south of Vietnam was suspended for about ten weeks, affecting approximately 15% of our global sourcing volumes. We tried to minimize delays as much as possible and shifted part of the volumes to other sourcing locations where possible. Thanks to the quick rollout of the vaccination program in the south of Vietnam, the factories gradually reopened during October and ramped up to full production by the end of year. After our suppliers resumed normal operations, we saw fewer and very localized factory closures in some parts of Asia, which did not significantly impact our product supply. We’re very thankful to our suppliers for being a part of the PUMA family. The strong collaboration, long-term partnership and all their incredible support ensured the continued supply of products under very difficult circumstances.</t>
+  </si>
+  <si>
+    <t>The COVID-19 pandemic also had a major impact on other parts of our supply chain, and we had to deal with capacity constraints, container shortages and harbor congestion in ocean freight, but also significant challenges in air freight and land-based transportation. All these constraints led to a strong increase in freight costs, which further fueled inflationary pressures, in addition to rising costs for energy, raw materials and labor.</t>
+  </si>
+  <si>
+    <t>As manifested in our strong sales growth, we also continued to drive the business in 2021. After the end of the COVID-19 related lockdowns, we witnessed a certain “normalization” of buying patterns, with more consumers shopping offline again instead of online. In our Direct-to-Consumer business, we therefore saw a higher growth rate in our brick &amp; mortar stores compared to our eCommerce sites. However, both channels grew by double-digits last year, and we continued to invest in the optimization of our store portfolio, the consumer experience on our existing sites as well as the launch of new eCommerce sites. During a time of limited supply, we continued to prioritize our retail partners in terms of product allocation. We strongly believe in a multi-brand retail environment and will therefore strengthen the relationship with all our retail partners around the world and do everything we can to service them in the best way possible.</t>
+  </si>
+  <si>
+    <t>After a year without any major sporting events in 2020, we were also excited to see sports leagues, tournaments and other competitions resume in the course of 2021, for the most part including live spectators.</t>
+  </si>
+  <si>
+    <t>The summer of 2021 was exceptional for our teams and athletes, who delivered world class performances on track and on the pitch. We underlined our credibility and high ambitions in football with the victory of the PUMA-sponsored national team Italy at UEFA Euro 2020, several league and cup titles of our PUMA-sponsored club teams and great on-pitch visibility of our products. At the Tokyo Olympics and Paralympics, our athletes won more than 70 medals, demonstrating the performance credentials of our products on the world stage, including our new NITRO running shoes that I personally am exceptionally proud of. We also continued our successful re-entry into basketball, especially for the North American market and launched our first signature shoe with LaMelo Ball at the end of the year. The strengthening of our performance credibility has always been important to us and I’m very happy about the great progress that we’ve seen across football, running, fitness, golf, motorsport, basketball and other
+locally relevant sports. In Sportstyle, we also continued to build brand heat through exciting new products and collaborations and by offering a comprehensive collection across all relevant price points, including a strong focus on comfort. We are very happy to see that our classics business is growing strongly. Our PUMA Archive is full of footwear and apparel from the 70s, 80s and 90s, for which there is currently a lot of demand in youth culture. We’re also very satisfied to see the continued momentum in our women’s business, following the launch of our “She Moves Us” brand platform, and we will keep capitalizing on our truly inclusive product offering across genders, age groups etc.!</t>
+  </si>
+  <si>
+    <t>We also continued to focus on what we call “Doing the right thing”. We want to be a good corporate citizen and embed our social responsibility and our environmental sustainability into all our business practices. With regards to social responsibility, we continued with multiple initiatives under our #REFORM platform to promote universal equality. We strongly believe that people should be treated equally irrespective of their gender, age, skin color, religious believes, sexual orientation or any other factor. Together with our brand ambassadors and partner organizations, we want to do our part to promote universal equality and fight any form of discrimination in sports and society as a whole. As part of our ambitious 10FOR25 sustainability targets, we implemented more sustainable business practices in all our business operations from sourcing to retail and further increased the usage of more sustainable materials and the overall share of more sustainable products in our collections. We also increased our focus on circularity, with several pilot projects and strengthened our consumer-facing sustainability communication through our FOREVER BETTER brand platform. I, together with my team, attended the COP26 climate conference in Glasgow to emphasize our commitment in the fight against climate change and to work towards limiting the global temperature rise to 1.5 degrees Celsius above pre-industrial levels. We have all theseinitiatives because we really believe in them, as part of PUMA’s core values, and we will continue to do the right thing.</t>
+  </si>
+  <si>
+    <t>Given our strong performance in 2021 and good momentum in the first months of 2022, we’re also optimistic for the future of our industry in general and for PUMA in particular, despite the external challenges. The underlying dynamics in our sector remain very strong given the increasing participation in sports, the ongoing sneaker trend and the continued casualization among consumers all around the world. We also see PUMA’s brand momentum continuing and we will ensure operational flexibility in an increasingly volatile and unpredictable marketplace. As we have already done during the past years, we will continue to work very closely with all our retail partners to further increase our shelf space and support the sell-through of our products in their stores. We have focused on building strong partnerships with all our key stakeholders such as suppliers, retailers, ambassadors and athletes, helping them as well as us through the ongoing challenges. We will continue to foster these partnerships in the future. We therefore expect 2022 to be another record year for PUMA, with a net sales growth of at least 10%, with upside potential, and an EBIT of EUR 600 – 700 million. The objective is not to maximize short-term EBIT, but to continue to have healthy long-term growth in both sales and EBIT. We will also keep on putting our people first and take care of all our partners.</t>
+  </si>
+  <si>
+    <t>Let’s stay positive and hope that peace in Ukraine will be restored as soon as possible and that the impact of the COVID-19 pandemic will continue to decrease.</t>
+  </si>
+  <si>
+    <t>Thank you for being part of the PUMA family!
+Stay strong, healthy and optimistic!
+Bjørn Gulden
+Chief Executive Officer PUMA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">title </t>
+  </si>
+  <si>
+    <t>DEU21P01-00</t>
+  </si>
+  <si>
+    <t>DEU21P02-00</t>
+  </si>
+  <si>
+    <t>DEU21P03-00</t>
+  </si>
+  <si>
+    <t>DEU21P04-00</t>
+  </si>
+  <si>
+    <t>DEU21P05-00</t>
+  </si>
+  <si>
+    <t>DEU21P06-00</t>
+  </si>
+  <si>
+    <t>DEU21P07-00</t>
+  </si>
+  <si>
+    <t>DEU21P08-00</t>
+  </si>
+  <si>
+    <t>DEU21P09-00</t>
+  </si>
+  <si>
+    <t>DEU21P10-00</t>
+  </si>
+  <si>
+    <t>DEU21P11-00</t>
+  </si>
+  <si>
+    <t>DEU21P12-00</t>
+  </si>
+  <si>
+    <t>DEU21P13-00</t>
+  </si>
+  <si>
+    <t>DEU21P14-00</t>
+  </si>
+  <si>
+    <t>DEU21P15-00</t>
+  </si>
+  <si>
+    <t>Arne Freundt</t>
+  </si>
+  <si>
+    <t>I am honored to write this letter to you for the first time as new CEO of PUMA. I have been part of the PUMA family for more than a decade, but last year has certainly been a very special one. I feel privileged that I am now leading this company with its fantastic people to take PUMA to the next level. Let me share with you the developments and successes of 2022 and give you a brief outlook on the exciting things to come.</t>
+  </si>
+  <si>
+    <t>2022 has been the best year in PUMA's history so far! We achieved record-breaking sales and earnings. Our revenue increased by 18.9% (ca) to € 8,465 million and our operating result (EBIT) increased by 15.0% to € 640.6 million. This success was driven by our continued brand momentum and successful product launches as well as continued trustful relationships with our athletes and partners around the globe. And even more by the dedication and hard work of our incredible PUMA family.</t>
+  </si>
+  <si>
+    <t>As 2022 has brought new challenges for all of us, the PUMA Family once again proved to stand by each other. Despite repeated lockdowns that particularly affected our Chinese colleagues, our people remained dedicated to keeping ourproduction and business running smoothly. And when Russia started the war against Ukraine, we quickly set up a support program for our employees, athletes, and partners in Ukraine. Many employees have also taken initiatives themselves to support our colleagues. This makes me proud. Against this backdrop of crises, I am all the more grateful that we have managed to achieve a seamless transition in our organization and to build on the successes of the past years. On behalf of the entire Board, I would like to thank the PUMA family for this very smooth transition and for all working together every day to ensure PUMA's continued success.</t>
+  </si>
+  <si>
+    <t>Besides our strong team a huge part of the achievements was down to our partners. We continued to focus and to further deepen our partnerships along the whole value chain. Our objective is to build mutual beneficial relationships which create value and innovations and make us more resilient. Under my leadership, PUMA will continue to be the best partner for our retailers, suppliers, and athletes.</t>
+  </si>
+  <si>
+    <t>At PUMA, we also aspire not only to be the best partner, but also to make our contribution towards a more sustainable world. It is important that we continue to make steady progress towards our 10 for 25 sustainability targets. Last year, we made 70% of our products from more sustainable materials. We also achieved important milestones in sourcing and manufacturing. I am particularly proud that PUMA has been able to reduce its emissions despite its strong growth in recent years. For our progress, we have received a lot of awards last year such as Business of Fashion naming us the most sustainable brand. For us this is a great recognition and motivation to continue the journey we have embarked on.</t>
+  </si>
+  <si>
+    <t>Our brand has continued to gain momentum, thanks to our commitment to quality, innovation, and the right collaborations with leading athletes and fashion icons. We have witnessed a steady increase in customer loyalty and engagement, which is a testament to the strength of our brand and the quality of our products.</t>
+  </si>
+  <si>
+    <t>We are proud to sponsor some of the world's leading football clubs like Manchester City and AC Milan, both of whom have had exceptional seasons. Our partnership with these teams has strengthened our brand presence in the world of football and enables us to expand loyalty and affinity with the fans. We were also thrilled to see Morocco become the first African team to reach the semi-finals of the football World Cup. As a brand that values diversity and inclusivity, we were honored to have played a part in this historic moment and look forward to supporting African football in the years to come. At the World Athletics Championships in Eugene, Oregon, USA, our athletes won numerous gold medals and set new records true to our brand mantra FOREVER.FASTER.</t>
+  </si>
+  <si>
+    <t>Besides the sports arenas, we made a successful comeback at the New York Fashion Show. FUTROGRADE showcased a selection of looks - from both current and future seasons, as well as custom pieces - which were curated by PUMA Designer and Creative Director, June Ambrose. We have received great feedback from customers and influencers alike and are confident that our footprint in fashion will continue to grow and evolve.</t>
+  </si>
+  <si>
+    <t>PUMA always aims to team-up with the world’s fastest athletes and most exciting cultural icons of our times to create the best and most innovative products for our athletes and customers. That is why we have also welcomed several key new PUMA ambassadors, including world-renowned athletes like Elain Thompson-Herah, Nalyssa Smith, Emmanuel Korir, Mutaz Essa Barshim, and cultural icons like Skepta and Dixie D'Amelio. These individuals embody our brand values and vision and will inspire every athlete to achieve their goals and live their best lives. We are also proud that Sara Björk made a successful comeback to elite level football following her pregnancy while we closely accompanied her along the way.</t>
+  </si>
+  <si>
+    <t>For 75 years, PUMA has relentlessly advanced sport by creating the best products for the world's fastest athletes. In 2022, we continued to significantly improve our product offering across all business units. Our performance footwear was successful both in terms of innovation and consumer satisfaction, with the award-winning VELOCITY and DEVIATE featuring PUMA's NITRO technology. In addition to running, we saw very strong momentum in football and basketball, also driven by our great innovations, our continued high-profile collaborations and the athletic success of our brand ambassadors in last year's tournaments.</t>
+  </si>
+  <si>
+    <t>In terms of distribution and in line with our partnership strategy, we continued to focus on wholesale first. Wholesale plays a pivotal role in our strategy – not only due to their distribution reach, but also due to their retail and service excellence. I also believe that it is crucial for our consumers to have the best product offering of each brand next to each other in our wholesale partner stores. This allows our consumers to take the best purchasing decision in terms of technology, quality, design and value. I am convinced that PUMA products can compete with any competitor’s product on the shelves.</t>
+  </si>
+  <si>
+    <t>Our owned and operated brick and mortar as well as eCommerce stores are complementing our distribution mix, but we don’t have any ambition to replace wholesale partners with our Direct-to-Consumer channels. In our Direct-to-Consumer channels, we will continue to focus on storytelling to educate our consumers about the strengths and width of our brand and our products.</t>
+  </si>
+  <si>
+    <t>To achieve this objective, we optimized our retail network with new store locations and flagship stores in key markets. We also launched new web shops, extending our online reach to consumers in more than 50 countries. As part of our ongoing commitment to improve the customer experience, we launched a new shopping app for our most loyal customers in selected markets, with plans to roll it out to more markets in the coming months.</t>
+  </si>
+  <si>
+    <t>Our commitment to digitalization is not limited to our channels. As part of our ongoing efforts to modernize our infrastructure, we made significant investments in digitalizing our entire business and modernizing our offices to make our internal processes even more efficient.</t>
+  </si>
+  <si>
+    <t>2022 was a successful year. We achieved the ambitious goals we set for ourselves. But we are not leaning back and continue to be hungry to gain more market share. With the market headwinds and uncertainties in the industry, 2023 will for sure be a transition year. We continued our growth trajectory in the first quarter and recorded double-digit sales growth. For the upcoming quarters, we expect a tougher trading environment and thus a softer growth trajectory. This is fully in line with our initial guidance, and we can confirm our outlook for 2023, expecting a currency-adjusted sales growth in the high single-digit percentage range and operating result (EBIT) in a range of € 590 million to € 670 million (2022: € 641 million).</t>
+  </si>
+  <si>
+    <t>For 2023 and onwards, we will continue to focus on implementing our successful strategy and put further emphasis on three strategic priorities: elevate our brand, win in the U.S., and return to growth in China.</t>
+  </si>
+  <si>
+    <t>I would like to thank all our employees for their continued hard work and dedication to the brand and our shareholders and stakeholders for supporting us on our journey.</t>
+  </si>
+  <si>
+    <t>Together with the entire PUMA family and all our stakeholders, I look forward to continuing our exciting way ahead and achieving even greater success in the future</t>
+  </si>
+  <si>
+    <t>Arne Freundt
+Chief Executive Officer, PUMA</t>
+  </si>
+  <si>
+    <t>DEU22P01-00</t>
+  </si>
+  <si>
+    <t>DEU22P02-00</t>
+  </si>
+  <si>
+    <t>DEU22P03-00</t>
+  </si>
+  <si>
+    <t>DEU22P04-00</t>
+  </si>
+  <si>
+    <t>DEU22P05-00</t>
+  </si>
+  <si>
+    <t>DEU22P06-00</t>
+  </si>
+  <si>
+    <t>DEU22P07-00</t>
+  </si>
+  <si>
+    <t>DEU22P08-00</t>
+  </si>
+  <si>
+    <t>DEU22P09-00</t>
+  </si>
+  <si>
+    <t>DEU22P10-00</t>
+  </si>
+  <si>
+    <t>DEU22P11-00</t>
+  </si>
+  <si>
+    <t>DEU22P12-00</t>
+  </si>
+  <si>
+    <t>DEU22P13-00</t>
+  </si>
+  <si>
+    <t>DEU22P14-00</t>
+  </si>
+  <si>
+    <t>DEU22P15-00</t>
+  </si>
+  <si>
+    <t>DEU22P16-00</t>
+  </si>
+  <si>
+    <t>DEU22P17-00</t>
+  </si>
+  <si>
+    <t>DEU22P18-00</t>
+  </si>
+  <si>
+    <t>DEU22P19-00</t>
   </si>
 </sst>
 </file>
@@ -629,8 +844,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DA7F0E8F-45C6-6043-B094-E3D95B97FF2A}" name="Tableau13" displayName="Tableau13" ref="A1:N2" totalsRowShown="0" headerRowDxfId="81" dataDxfId="80">
-  <autoFilter ref="A1:N2" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DA7F0E8F-45C6-6043-B094-E3D95B97FF2A}" name="Tableau13" displayName="Tableau13" ref="A1:N17" totalsRowShown="0" headerRowDxfId="81" dataDxfId="80">
+  <autoFilter ref="A1:N17" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N2">
     <sortCondition ref="A1:A2"/>
   </sortState>
@@ -655,8 +870,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{C7C650FA-A8BE-374F-A02C-24C279A2D67A}" name="Tableau134" displayName="Tableau134" ref="A1:N2" totalsRowShown="0" headerRowDxfId="67" dataDxfId="66">
-  <autoFilter ref="A1:N2" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{C7C650FA-A8BE-374F-A02C-24C279A2D67A}" name="Tableau134" displayName="Tableau134" ref="A1:N21" totalsRowShown="0" headerRowDxfId="67" dataDxfId="66">
+  <autoFilter ref="A1:N21" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N2">
     <sortCondition ref="A1:A2"/>
   </sortState>
@@ -1753,11 +1968,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAD18CE3-D2D1-DD49-8602-5C2A7C693BA7}">
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="64.1640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="105.33203125" style="1" customWidth="1"/>
     <col min="3" max="3" width="12.5" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18.83203125" style="1" customWidth="1"/>
@@ -1812,11 +2027,16 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="2"/>
+      <c r="B2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>82</v>
+      </c>
       <c r="G2" s="1" t="s">
         <v>25</v>
       </c>
@@ -1831,6 +2051,492 @@
       </c>
       <c r="K2" s="1" t="s">
         <v>10</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="68" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J3" s="1">
+        <v>2021</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="153" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J4" s="1">
+        <v>2021</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="102" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J5" s="1">
+        <v>2021</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="153" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J6" s="1">
+        <v>2021</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="68" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J7" s="1">
+        <v>2021</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="102" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J8" s="1">
+        <v>2021</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="221" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J9" s="1">
+        <v>2021</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="102" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J10" s="1">
+        <v>2021</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="136" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J11" s="1">
+        <v>2021</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="34" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J12" s="1">
+        <v>2021</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="255" x14ac:dyDescent="0.2">
+      <c r="A13" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J13" s="1">
+        <v>2021</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M13" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="221" x14ac:dyDescent="0.2">
+      <c r="A14" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J14" s="1">
+        <v>2021</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M14" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="187" x14ac:dyDescent="0.2">
+      <c r="A15" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J15" s="1">
+        <v>2021</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M15" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="34" x14ac:dyDescent="0.2">
+      <c r="A16" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J16" s="1">
+        <v>2021</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L16" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M16" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="68" x14ac:dyDescent="0.2">
+      <c r="A17" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J17" s="1">
+        <v>2021</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L17" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M17" s="1" t="s">
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -1843,11 +2549,11 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8482D037-842C-3D44-82D2-0DCAF2D2098B}">
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="64.1640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="88.83203125" style="1" customWidth="1"/>
     <col min="3" max="3" width="12.5" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18.83203125" style="1" customWidth="1"/>
@@ -1902,11 +2608,16 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="2"/>
+      <c r="B2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>82</v>
+      </c>
       <c r="G2" s="1" t="s">
         <v>25</v>
       </c>
@@ -1921,6 +2632,620 @@
       </c>
       <c r="K2" s="1" t="s">
         <v>10</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="102" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J3" s="1">
+        <v>2022</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="119" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J4" s="1">
+        <v>2022</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="204" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J5" s="1">
+        <v>2022</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="68" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J6" s="1">
+        <v>2022</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="119" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J7" s="1">
+        <v>2022</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="51" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J8" s="1">
+        <v>2022</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="119" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J9" s="1">
+        <v>2022</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="68" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J10" s="1">
+        <v>2022</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="119" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J11" s="1">
+        <v>2022</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="102" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J12" s="1">
+        <v>2022</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="102" x14ac:dyDescent="0.2">
+      <c r="A13" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J13" s="1">
+        <v>2022</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M13" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="68" x14ac:dyDescent="0.2">
+      <c r="A14" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J14" s="1">
+        <v>2022</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M14" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="68" x14ac:dyDescent="0.2">
+      <c r="A15" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J15" s="1">
+        <v>2022</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M15" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="51" x14ac:dyDescent="0.2">
+      <c r="A16" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J16" s="1">
+        <v>2022</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L16" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M16" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="119" x14ac:dyDescent="0.2">
+      <c r="A17" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J17" s="1">
+        <v>2022</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L17" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M17" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="34" x14ac:dyDescent="0.2">
+      <c r="A18" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J18" s="1">
+        <v>2022</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L18" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M18" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="34" x14ac:dyDescent="0.2">
+      <c r="A19" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J19" s="1">
+        <v>2022</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L19" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M19" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="34" x14ac:dyDescent="0.2">
+      <c r="A20" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J20" s="1">
+        <v>2022</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M20" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="34" x14ac:dyDescent="0.2">
+      <c r="A21" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J21" s="1">
+        <v>2022</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L21" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M21" s="1" t="s">
+        <v>98</v>
       </c>
     </row>
   </sheetData>

--- a/data/input/puma.xlsx
+++ b/data/input/puma.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Saowalak/Desktop/CEOCommunication/data/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{678E623C-AB8D-1C40-977D-5718C03E6851}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0774F66F-9DC4-EB43-8D90-FB97B3E2E9F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="280" yWindow="600" windowWidth="28520" windowHeight="17400" activeTab="2" xr2:uid="{05EFD2A9-923A-834E-A816-A8C1AAE62552}"/>
+    <workbookView xWindow="7580" yWindow="600" windowWidth="21220" windowHeight="17400" activeTab="3" xr2:uid="{05EFD2A9-923A-834E-A816-A8C1AAE62552}"/>
   </bookViews>
   <sheets>
     <sheet name="2020" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1104" uniqueCount="227">
   <si>
     <t>ID</t>
   </si>
@@ -462,6 +462,277 @@
   </si>
   <si>
     <t>DEU22P19-00</t>
+  </si>
+  <si>
+    <t>In 2024, PUMA’s sales increased in a dynamic market environment by 4.4 currency-adjusted to € 8,817 million. We were able to improve our sales growth from quarter to quarter and grew by 9.8%, currency adjusted, in the fourth quarter. For the full year 2024, sales in all regions, product areas and distribution channels improved on a currency-adjusted basis compared to the previous year. This means PUMA has grown faster than the market, which  ecorded currency adjusted growth of 1.8% in 2024 according to Euromonitor.</t>
+  </si>
+  <si>
+    <t>Despite this solid sales growth and the significant progress we made in 2024 in implementing our brand elevation strategy, we are not satisfied with our profitability. The operating result (EBIT) of € 622 million in 2024 was at the level of the previous year. Although this is in line with our outlook, it is below our own expectations. At € 282 million, the net result was below the previous year's level.</t>
+  </si>
+  <si>
+    <t>In 2024, we made good progress in implementing our brand elevation strategy, which is the basis for our long-term growth and further market share gains. The strategy consists of three elements: a distinctive brand DNA, a strong performance business and strengthening our relevance in Sportstyle Prime.</t>
+  </si>
+  <si>
+    <t>We used the Year of Sport 2024 and the many major sports events to launch our first brand campaign in 10 years’ time. This campaign helped PUMA deepen its emotional connection with consumers and further increase its brand equity. As a next step, we have further refined our brand DNA and will we present the next campaign to our consumers in 2025.</t>
+  </si>
+  <si>
+    <t>By further strengthening our performance business, we are demonstrating our role as an innovation-orientated company. One example of this is our leading foam technology NITROTM, which enabled us to gain further market share in 2024. After just four years, we have risen to become one of the top 10 running brands and are one of the fastest growing brands in this segment. In the football category, where we have been pursuing this performance approach for some time with our FUTURE, ULTRA and ING franchises, 2024 was another record year with further market share growth.</t>
+  </si>
+  <si>
+    <t>I am also satisfied with our progress in 2024 when it comes to the third pillar of our strategy, to become more relevant in Sportstyle Prime. We have consistently implemented our new product and marketing strategy and steadily built up demand for our Sportstyle Prime product range in 2024, especially for low-profile and progressive running styles. A good example of the low-profile trend is the Speedcat. It has already been worn by famous actors, musicians and influencers and has been highlighted by many media outlets as one of the most sought-after products on the market. We expect to maximise our opportunities in the low-profile sneaker segment with the Speedcat and other models in the summer of 2025.</t>
+  </si>
+  <si>
+    <t>With an increased focus on translating our sales growth into higher profitability growth, we have initiated nextlevel, a comprehensive efficiency programme to optimise costs and make operational improvements that complement our brand elevation growth strategy. With nextlevel, we will reduce our direct and indirect costs to realise savings, particularly in the areas of sourcing, logistics and IT. At the same time, we will further align our structures and personnel with future growth, with the aim of improving personnel costs in relation to sales. With nextlevel, we will strengthen our overall competitiveness and continue to invest in our brand and employees - the two most important pillars of our success.</t>
+  </si>
+  <si>
+    <t>We are not satisfied with our share price performance, which does not adequately reflect the solid financial position and promising outlook of our company. Our strategic investments are focused on the long-term success and competitiveness of PUMA and we are convinced that this will lead to a better share price performance in the medium to long term. We are convinced of our brand elevation strategy and will continue to implement it consistently to realise the great potential of the PUMA brand.</t>
+  </si>
+  <si>
+    <t>I would like to take this opportunity to thank the PUMA family - our employees, wholesale partners, suppliers, brand ambassadors and athletes - for their commitment and contribution. I am also very grateful to our Supervisory Board for their support in implementing our strategy. I would also like to thank you, our shareholders, for your trust.</t>
+  </si>
+  <si>
+    <t>DEU24P01-00</t>
+  </si>
+  <si>
+    <t>DEU24P02-00</t>
+  </si>
+  <si>
+    <t>DEU24P03-00</t>
+  </si>
+  <si>
+    <t>DEU24P04-00</t>
+  </si>
+  <si>
+    <t>DEU24P05-00</t>
+  </si>
+  <si>
+    <t>DEU24P06-00</t>
+  </si>
+  <si>
+    <t>DEU24P07-00</t>
+  </si>
+  <si>
+    <t>DEU24P08-00</t>
+  </si>
+  <si>
+    <t>DEU24P09-00</t>
+  </si>
+  <si>
+    <t>Arthur Hoeld</t>
+  </si>
+  <si>
+    <t>PUMA has one of the most significant archives in our industry, with more than 77 years of history alongside the world’s most successful athletes. PUMA stands for unforgettable moments in sports and sports culture and many great innovations. PUMA is also one of only a few brands in our industry that is popular in many major global sports.</t>
+  </si>
+  <si>
+    <t>That is why being CEO of PUMA is a fantastic job. I was delighted to take on this position in July 2025 because I see great potential in this sports brand.</t>
+  </si>
+  <si>
+    <t>PUMA creates some of the best technologies and performance products that help our athletes succeed. NITRO™ is the most innovative running technology currently available on the market. In 2025, our athletes used NITRO™ to set records and new personal bests.</t>
+  </si>
+  <si>
+    <t>In addition to the many successes and personal bests our athletes achieved with PUMA’s NITRO™ technology at major marathons around the world, we were also very happy with the many medals won by our athletes and federations at the World Athletics Championships in Tokyo. For example, pole vaulter Armand “Mondo” Duplantis set yet another new world record and was even named World Athlete of the Year at the end of 2025.</t>
+  </si>
+  <si>
+    <t>The collaboration with athletes, federations, clubs and other partners is essential for us as a sports brand, as it aids our credibility in sports and connects us with fans and athletes. That is why I am glad that we were able to further strengthen some of our leading partnerships in 2025. Important examples here are the contract extensions with Manchester City, Borussia Dortmund and HYROX, the world series of fitness racing.</t>
+  </si>
+  <si>
+    <t>Despite the many unforgettable moments in 2025, we also realised that the PUMA brand had become too commercial over the years. This is reflected in low brand heat, poor sales quality and a product range that did not cut through.</t>
+  </si>
+  <si>
+    <t>That is why we made 2025 a year of reset and realigned our strategy. The aim is to establish PUMA as a Top 3 sports brand worldwide, return to above industry growth and create healthy profits in the medium term. PUMA will become one global sports brand with global product ranges and global storytelling across markets.</t>
+  </si>
+  <si>
+    <t>In doing so, we want to follow the winning principles of a leading sports brand. PUMA must be clearly positioned as a brand, the product development and storytelling processes must be better integrated, and the sales and go-to-market processes must be actively managed. With attractive products, exciting product stories and distribution in the right channels, we will be able to once again make our customers and consumers excited about PUMA.</t>
+  </si>
+  <si>
+    <t>To make PUMA less commercial, we have decided to withdraw from wholesale channels that damage our brand’s desirability. In doing so, we are also reducing sales promotion measures such as discounts in our own DTC business. At the same time, we will further develop our sales channel mix to aim for a higher DTC share and bring PUMA closer to the industry average.</t>
+  </si>
+  <si>
+    <t>In our product strategy, PUMA will focus on better positioning its various product icons. We firmly believe that PUMA, with its extensive archive, has a clear opportunity to better establish its product icons, such as the PUMA Suede. Within our categories, we will prioritise Football, Running, Training and Sportstyle Select/Prime. At the same time, we have created a structure for 2025 to better align the processes for product development and storytelling. This will enable us to create authentic and effective product stories that will convince both our wholesale partners and consumers.</t>
+  </si>
+  <si>
+    <t>In 2025, we also took important steps to optimise our cost base, eliminate operational inefficiencies and reduce the number of new items introduced each season. The optimisation of our cost base also includes the decision to cut a further 900 office positions worldwide by the end of 2026, following the reduction of around 500 positions in 2025.</t>
+  </si>
+  <si>
+    <t>Despite the challenges I have just described, I firmly believe in PUMA’s potential and successful future. I am convinced that with the reset in 2025, we have set the right course to return to growth after the transition year of 2026.</t>
+  </si>
+  <si>
+    <t>My thanks go to our employees, wholesale partners, suppliers, brand ambassadors and athletes who have been a part of PUMA in 2025. I’m also very grateful to our Supervisory Board for their support in implementing PUMA’s reset.</t>
+  </si>
+  <si>
+    <t>I would also like to thank you, dear shareholders, for your trust and support for the path we have chosen.</t>
+  </si>
+  <si>
+    <t>DEU25P01-00</t>
+  </si>
+  <si>
+    <t>DEU25P02-00</t>
+  </si>
+  <si>
+    <t>DEU25P03-00</t>
+  </si>
+  <si>
+    <t>DEU25P04-00</t>
+  </si>
+  <si>
+    <t>DEU25P05-00</t>
+  </si>
+  <si>
+    <t>DEU25P06-00</t>
+  </si>
+  <si>
+    <t>DEU25P07-00</t>
+  </si>
+  <si>
+    <t>DEU25P08-00</t>
+  </si>
+  <si>
+    <t>DEU25P09-00</t>
+  </si>
+  <si>
+    <t>DEU25P10-00</t>
+  </si>
+  <si>
+    <t>DEU25P11-00</t>
+  </si>
+  <si>
+    <t>DEU25P12-00</t>
+  </si>
+  <si>
+    <t>DEU25P13-00</t>
+  </si>
+  <si>
+    <t>DEU25P14-00</t>
+  </si>
+  <si>
+    <t>letter</t>
+  </si>
+  <si>
+    <t>2023 was a transition year for our industry. The market environment was challenging, characterized by geopolitical conflicts, volatile currencies, macroeconomic headwinds and muted consumer sentiments as well as elevated inventory levels in the marketplace. Nevertheless, PUMA was able to sustain its strong brand momentum in 2023 and win market shares, leading to another record year with revenues of 8.602 billion euros (+ 6.6% cc) and a profitability fully in line with the outlook. Without the extraordinary devaluation of the Argentinian Peso, which had a significant one-off accounting impact, our results would have been even stronger.</t>
+  </si>
+  <si>
+    <t>For PUMA, 2023 was also a transition year in which we outlined new strategic priorities to create the foundation for the continued strong growth of the company. When I took over as CEO of PUMA in late 2022 after 11 years with the company, I made my immediate strategic priorities clear: we need to elevate the PUMA brand and win in the US and in China.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">On the brand elevation side, PUMA has the opportunity to further increase its relevance with consumers to win more hearts and minds. To increase our brand consideration, we need to focus on building the emotional connection between our brand mantra FOREVER. FASTER. and our consumers and execute our brand and product campaigns more consistently to increase our brand equity.
+</t>
+  </si>
+  <si>
+    <t>In 2023, we laid the organizational foundation by transitioning our brand management team to our global headquarters in Herzogenaurach and by announcing Richard Teyssier as new Vice President Brand &amp; Marketing. These decisions will vastly improve and speed up alignment between the different departments, as global marketing will sit next to product, global go-to-market and our creative direction. In this new setup we are now working on a new brand campaign, which will launch in 2024 and bring to life the emotional benefit for our consumers.</t>
+  </si>
+  <si>
+    <t>Another cornerstone of our brand elevation strategy is our Fewer-Bigger-Better approach. We will focus our efforts on fewer but more impactful Tier 1 brand ambassadors at the top of our full-tier influencer strategy, and bigger marketing campaigns to increase the relevance of our brand with our consumers. We were able to already take the first big steps in 2023, by welcoming Rihanna and A$AP Rocky on the entertainment side as well as Jack Grealish, Kai Havertz, Xavi Simons, Alex Greenwood, Marcell Jacobs, and Scoot Henderson on the performance side.</t>
+  </si>
+  <si>
+    <t>Winning in the United States is another key strategic priority. It’s the biggest and most important global sports market but our market shares are currently too low. On top, the US has been a soft market overall in 2023, caused by macroeconomic headwinds and elevated inventories, in which we saw soft sales. To turn this around and win in the US, we have to elevate the brand and clearly reposition PUMA as a sports brand, create more locally relevant products and improve our distribution quality.</t>
+  </si>
+  <si>
+    <t>We have the foundation to be successful in the US. We have some of the best US athletes like LaMelo Ball, Scoot Henderson, Breanna Stewart, Christian Pulisic, Molly Seidel, Rickie Fowler and Lexi Thompson, who can give us the authenticity as a true performance brand. We have three of our four performance product teams (Basketball, Running/Training and Golf) based in the US and have a Regional Creation Center in Boston to help us cater for the demands of our US consumers. We will further reinforce our commitment to the US market by opening our LA Creative Hub in 2024.</t>
+  </si>
+  <si>
+    <t>On the distribution side, we have great partnerships in place, but we need to become more disciplined and focused on growth with our more desirable wholesale partners going forward. A repositioning of the brand will take some time, but the foundation is there and the first steps have been initiated.</t>
+  </si>
+  <si>
+    <t>To further support our new strategic direction in the US, we strengthened our organisation with the appointments of Andrew “Rudi” Rudolph and Alexa Andersen, who will lead the US sales and merchandising teams.</t>
+  </si>
+  <si>
+    <t>Finally, winning in the Chinese Market is our third strategic priority. The Chinese market was muted in 2023 and even though consumer sentiment has improved, it remained below pre-COVID levels. Nevertheless, we witnessed a gradual recovery of our business.</t>
+  </si>
+  <si>
+    <t>As is the case in the United States, it is a priority to position PUMA as a sports brand in China. Part of this strategy is to also sign the right local ambassadors from sports and entertainment, which complement PUMA’s international portfolio. In 2023, PUMA welcomed actress CC Song, basketball player Zhang Ru, soccer player Yao Wei and breakdancer Qi Xiangyu among others. We will make further exciting announcements in 2024.</t>
+  </si>
+  <si>
+    <t>To cater for Chinese consumers with the right products, PUMA will further build on its local-for-local resources in China both in terms of design and sourcing to bring the right product with local fit at an accelerated speed to the market.</t>
+  </si>
+  <si>
+    <t>PUMA also introduced a new store format, which was developed by a local agency to fit the needs of Chinese consumers and to deliver improved store productivity. After successful pilots, PUMA has started the roll-out of the new store concept in 2023.</t>
+  </si>
+  <si>
+    <t>With Shirley Li as General Manager, David Lu as Commercial Director and Robbie Cai as Marketing Director, we appointed three experienced local Chinese leaders to carry out our strategy in the country.</t>
+  </si>
+  <si>
+    <t>Although brand positioning and rebalancing distribution quality takes time, I’m encouraged by the progress we have already made both in China and the US over the past months.</t>
+  </si>
+  <si>
+    <t>Our people and our partnerships are key to our success as a company. To constantly improve our global distribution quality, we worked closely with our wholesale partners to give them the best possible service and make our products stand out in a multibrand environment. Being the best partner to our retailers was once again crucial in 2023, as we jointly needed to work through elevated inventory levels in this transition year. I am happy with the progress we achieved together in 2023 by cleaning up the marketplace and providing the foundation for a less promotional year in 2024.</t>
+  </si>
+  <si>
+    <t>Our partnership approach also applies to our sourcing strategy, which is based on the long-term cooperation with our suppliers along the entire value chain. This guarantees the consistent high quality of our products, positions us well for future growth and creates a dependable supply chain in times of many global uncertainties. In this context, we were excited to welcome our key suppliers to our first global supplier summit in Herzogenaurach since 2010 to align our strategies and strengthen our partnerships.</t>
+  </si>
+  <si>
+    <t>Putting our people first is an important part of our corporate strategy and we were thrilled to be named a global Top Employer in 2023. We received this award, which follows a comprehensive survey by the Top Employers Institute, for the first time in North America and Latin America and once more in Europe and Asia Pacific. The fact that most of our important senior vacancies are filled with fantastic internal candidates is further proof of the great job we do on people development.</t>
+  </si>
+  <si>
+    <t>Finally, 2023 marked our 75th anniversary. In 1948, our founder Rudolf Dassler founded the company with the idea to create the best products for the athletes, always with a vision that these products would help our athletes to become fast and agile, like a puma. We still live by this vision today. We celebrated that special milestone together with our 20,000 employees worldwide. It was great to see how this anniversary was celebrated in all our offices across the world throughout the global PUMA Family.</t>
+  </si>
+  <si>
+    <t>I would like to thank everybody in the PUMA family – our employees, our wholesale partners, our suppliers, our ambassadors and athletes – for their contribution and dedication to the company. I’m also very grateful to our supervisory board, which has supported us in executing our strategy and position PUMA for future growth. I would also like to thank you, our shareholders, for your continued support and trust.</t>
+  </si>
+  <si>
+    <t>I really look forward to 2024, which will be the Year of Sport with important sports events such as the Olympic Games, Euro 2024 and Copa America which give us great brand visibility. We continue to be the challenger in the market with the ambition to continue our success story and to gain further market share.</t>
+  </si>
+  <si>
+    <t>DEU23P01-00</t>
+  </si>
+  <si>
+    <t>DEU23P02-00</t>
+  </si>
+  <si>
+    <t>DEU23P03-00</t>
+  </si>
+  <si>
+    <t>DEU23P04-00</t>
+  </si>
+  <si>
+    <t>DEU23P05-00</t>
+  </si>
+  <si>
+    <t>DEU23P06-00</t>
+  </si>
+  <si>
+    <t>DEU23P07-00</t>
+  </si>
+  <si>
+    <t>DEU23P08-00</t>
+  </si>
+  <si>
+    <t>DEU23P09-00</t>
+  </si>
+  <si>
+    <t>DEU23P10-00</t>
+  </si>
+  <si>
+    <t>DEU23P11-00</t>
+  </si>
+  <si>
+    <t>DEU23P12-00</t>
+  </si>
+  <si>
+    <t>DEU23P13-00</t>
+  </si>
+  <si>
+    <t>DEU23P14-00</t>
+  </si>
+  <si>
+    <t>DEU23P15-00</t>
+  </si>
+  <si>
+    <t>DEU23P16-00</t>
+  </si>
+  <si>
+    <t>DEU23P17-00</t>
+  </si>
+  <si>
+    <t>DEU23P18-00</t>
+  </si>
+  <si>
+    <t>DEU23P19-00</t>
+  </si>
+  <si>
+    <t>DEU23P20-00</t>
+  </si>
+  <si>
+    <t>DEU23P21-00</t>
   </si>
 </sst>
 </file>
@@ -565,39 +836,6 @@
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -628,6 +866,12 @@
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -667,6 +911,15 @@
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -709,6 +962,12 @@
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -751,6 +1010,12 @@
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -764,6 +1029,12 @@
     </dxf>
     <dxf>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -818,156 +1089,156 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}" name="Tableau1" displayName="Tableau1" ref="A1:N20" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}" name="Tableau1" displayName="Tableau1" ref="A1:N20" totalsRowShown="0" headerRowDxfId="79" dataDxfId="78">
   <autoFilter ref="A1:N20" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N2">
     <sortCondition ref="A1:A2"/>
   </sortState>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{3EB1D0B3-009A-5A47-8B93-8EF6255B1304}" name="ID" dataDxfId="13"/>
-    <tableColumn id="2" xr3:uid="{DA8A41BF-F097-BC45-906C-4BABEC2244DD}" name="Text" dataDxfId="12"/>
-    <tableColumn id="3" xr3:uid="{2EF94B43-4C8E-044F-B78E-77B5B2C749ED}" name="Text_type" dataDxfId="11"/>
-    <tableColumn id="4" xr3:uid="{CCEEA6CD-C218-094D-9E25-C77D75EA7E8B}" name="Leadership_context" dataDxfId="10"/>
-    <tableColumn id="5" xr3:uid="{7597EAEA-F46D-374E-8954-A78718D8A002}" name="Information_valence" dataDxfId="9"/>
-    <tableColumn id="6" xr3:uid="{FAAD26A2-D031-3F47-A9AF-C78AE4508844}" name="Communication_type" dataDxfId="8"/>
-    <tableColumn id="14" xr3:uid="{DC551193-3E78-054D-9E02-55B526E3955D}" name="Source_type" dataDxfId="7"/>
-    <tableColumn id="7" xr3:uid="{0B866C2F-1672-9C45-8132-39C1E3DA8EAF}" name="Company" dataDxfId="6"/>
-    <tableColumn id="8" xr3:uid="{CC5E1A75-8194-974B-BC62-732998981044}" name="Country" dataDxfId="5"/>
-    <tableColumn id="9" xr3:uid="{3B4764F6-42C4-5740-9A0F-8733D2FFE2C1}" name="Year" dataDxfId="4"/>
-    <tableColumn id="10" xr3:uid="{DF6E8D3A-208E-A448-B107-E9C070DE225E}" name="Covid" dataDxfId="3"/>
-    <tableColumn id="13" xr3:uid="{CB3B9ED9-A903-D142-8C47-DBFE1BB21BB9}" name="Communicator_role" dataDxfId="2"/>
-    <tableColumn id="11" xr3:uid="{C327315D-BA1F-BF4E-979D-02C312D440C8}" name="Communicator_name" dataDxfId="1"/>
-    <tableColumn id="12" xr3:uid="{1977CE7B-3E0B-714D-8E54-438D9A354605}" name="Comment" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{3EB1D0B3-009A-5A47-8B93-8EF6255B1304}" name="ID" dataDxfId="77"/>
+    <tableColumn id="2" xr3:uid="{DA8A41BF-F097-BC45-906C-4BABEC2244DD}" name="Text" dataDxfId="76"/>
+    <tableColumn id="3" xr3:uid="{2EF94B43-4C8E-044F-B78E-77B5B2C749ED}" name="Text_type" dataDxfId="75"/>
+    <tableColumn id="4" xr3:uid="{CCEEA6CD-C218-094D-9E25-C77D75EA7E8B}" name="Leadership_context" dataDxfId="74"/>
+    <tableColumn id="5" xr3:uid="{7597EAEA-F46D-374E-8954-A78718D8A002}" name="Information_valence" dataDxfId="73"/>
+    <tableColumn id="6" xr3:uid="{FAAD26A2-D031-3F47-A9AF-C78AE4508844}" name="Communication_type" dataDxfId="72"/>
+    <tableColumn id="14" xr3:uid="{DC551193-3E78-054D-9E02-55B526E3955D}" name="Source_type" dataDxfId="71"/>
+    <tableColumn id="7" xr3:uid="{0B866C2F-1672-9C45-8132-39C1E3DA8EAF}" name="Company" dataDxfId="70"/>
+    <tableColumn id="8" xr3:uid="{CC5E1A75-8194-974B-BC62-732998981044}" name="Country" dataDxfId="69"/>
+    <tableColumn id="9" xr3:uid="{3B4764F6-42C4-5740-9A0F-8733D2FFE2C1}" name="Year" dataDxfId="68"/>
+    <tableColumn id="10" xr3:uid="{DF6E8D3A-208E-A448-B107-E9C070DE225E}" name="Covid" dataDxfId="67"/>
+    <tableColumn id="13" xr3:uid="{CB3B9ED9-A903-D142-8C47-DBFE1BB21BB9}" name="Communicator_role" dataDxfId="66"/>
+    <tableColumn id="11" xr3:uid="{C327315D-BA1F-BF4E-979D-02C312D440C8}" name="Communicator_name" dataDxfId="65"/>
+    <tableColumn id="12" xr3:uid="{1977CE7B-3E0B-714D-8E54-438D9A354605}" name="Comment" dataDxfId="64"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DA7F0E8F-45C6-6043-B094-E3D95B97FF2A}" name="Tableau13" displayName="Tableau13" ref="A1:N17" totalsRowShown="0" headerRowDxfId="81" dataDxfId="80">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DA7F0E8F-45C6-6043-B094-E3D95B97FF2A}" name="Tableau13" displayName="Tableau13" ref="A1:N17" totalsRowShown="0" headerRowDxfId="63" dataDxfId="62">
   <autoFilter ref="A1:N17" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N2">
     <sortCondition ref="A1:A2"/>
   </sortState>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{CEF716DC-F71C-F64A-9417-BFA8F7223C3C}" name="ID" dataDxfId="79"/>
-    <tableColumn id="2" xr3:uid="{E18EF473-8BB2-B249-A671-AEC1D227D58C}" name="Text" dataDxfId="78"/>
-    <tableColumn id="3" xr3:uid="{43ED120E-0AAC-5B48-BFFE-E2FEDCE871CC}" name="Text_type" dataDxfId="77"/>
-    <tableColumn id="4" xr3:uid="{C80CD8E5-01BF-A441-83A4-5AD3DB190355}" name="Leadership_context" dataDxfId="76"/>
-    <tableColumn id="5" xr3:uid="{923FAB0A-F1C7-8C4E-9079-3F151BDD8845}" name="Information_valence" dataDxfId="75"/>
-    <tableColumn id="6" xr3:uid="{68020A6C-474C-354D-9F87-DDFAD6E6FCBF}" name="Communication_type" dataDxfId="74"/>
-    <tableColumn id="13" xr3:uid="{DD700407-60FC-C348-A601-E8685620E07F}" name="Source_type" dataDxfId="17"/>
-    <tableColumn id="7" xr3:uid="{BE35D812-E006-C241-B735-D50938782E5F}" name="Company" dataDxfId="73"/>
-    <tableColumn id="8" xr3:uid="{D7B81200-66AC-0046-9542-315523411E25}" name="Country" dataDxfId="72"/>
-    <tableColumn id="9" xr3:uid="{79CD73A8-8993-8248-A866-07B7E35F6DCB}" name="Year" dataDxfId="71"/>
-    <tableColumn id="10" xr3:uid="{9CEEE324-6A65-1042-8C7C-96F54D0F2756}" name="Covid" dataDxfId="70"/>
-    <tableColumn id="14" xr3:uid="{18CC61B1-AC23-BA4F-B2B3-2D2FB5AC969E}" name="Communicator_role" dataDxfId="16"/>
-    <tableColumn id="11" xr3:uid="{64EE7B30-27FC-9945-8BF4-F74D9FF6D07C}" name="Communicator_name" dataDxfId="69"/>
-    <tableColumn id="12" xr3:uid="{5C43064B-4CDF-ED4E-B988-64FD2F0806AA}" name="Comment" dataDxfId="68"/>
+    <tableColumn id="1" xr3:uid="{CEF716DC-F71C-F64A-9417-BFA8F7223C3C}" name="ID" dataDxfId="61"/>
+    <tableColumn id="2" xr3:uid="{E18EF473-8BB2-B249-A671-AEC1D227D58C}" name="Text" dataDxfId="60"/>
+    <tableColumn id="3" xr3:uid="{43ED120E-0AAC-5B48-BFFE-E2FEDCE871CC}" name="Text_type" dataDxfId="59"/>
+    <tableColumn id="4" xr3:uid="{C80CD8E5-01BF-A441-83A4-5AD3DB190355}" name="Leadership_context" dataDxfId="58"/>
+    <tableColumn id="5" xr3:uid="{923FAB0A-F1C7-8C4E-9079-3F151BDD8845}" name="Information_valence" dataDxfId="57"/>
+    <tableColumn id="6" xr3:uid="{68020A6C-474C-354D-9F87-DDFAD6E6FCBF}" name="Communication_type" dataDxfId="56"/>
+    <tableColumn id="13" xr3:uid="{DD700407-60FC-C348-A601-E8685620E07F}" name="Source_type" dataDxfId="55"/>
+    <tableColumn id="7" xr3:uid="{BE35D812-E006-C241-B735-D50938782E5F}" name="Company" dataDxfId="54"/>
+    <tableColumn id="8" xr3:uid="{D7B81200-66AC-0046-9542-315523411E25}" name="Country" dataDxfId="53"/>
+    <tableColumn id="9" xr3:uid="{79CD73A8-8993-8248-A866-07B7E35F6DCB}" name="Year" dataDxfId="52"/>
+    <tableColumn id="10" xr3:uid="{9CEEE324-6A65-1042-8C7C-96F54D0F2756}" name="Covid" dataDxfId="51"/>
+    <tableColumn id="14" xr3:uid="{18CC61B1-AC23-BA4F-B2B3-2D2FB5AC969E}" name="Communicator_role" dataDxfId="50"/>
+    <tableColumn id="11" xr3:uid="{64EE7B30-27FC-9945-8BF4-F74D9FF6D07C}" name="Communicator_name" dataDxfId="49"/>
+    <tableColumn id="12" xr3:uid="{5C43064B-4CDF-ED4E-B988-64FD2F0806AA}" name="Comment" dataDxfId="48"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{C7C650FA-A8BE-374F-A02C-24C279A2D67A}" name="Tableau134" displayName="Tableau134" ref="A1:N21" totalsRowShown="0" headerRowDxfId="67" dataDxfId="66">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{C7C650FA-A8BE-374F-A02C-24C279A2D67A}" name="Tableau134" displayName="Tableau134" ref="A1:N21" totalsRowShown="0" headerRowDxfId="95" dataDxfId="94">
   <autoFilter ref="A1:N21" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N2">
     <sortCondition ref="A1:A2"/>
   </sortState>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{E398D18F-D9B1-8C4A-B81C-4F23A58404BA}" name="ID" dataDxfId="65"/>
-    <tableColumn id="2" xr3:uid="{41682781-F3C4-A842-B6E4-CD72DE688AF5}" name="Text" dataDxfId="64"/>
-    <tableColumn id="3" xr3:uid="{C1B517F2-40CD-8F40-9B4C-E34FFCCE3881}" name="Text_type" dataDxfId="63"/>
-    <tableColumn id="4" xr3:uid="{74E0C65C-5577-A146-9EE5-20C594C4316D}" name="Leadership_context" dataDxfId="62"/>
-    <tableColumn id="5" xr3:uid="{DDC33EC8-2DCC-DF43-9A08-EC991A2EA183}" name="Information_valence" dataDxfId="61"/>
-    <tableColumn id="6" xr3:uid="{C7BBAC6F-3D8E-B149-B9F0-D0A909FCC061}" name="Communication_type" dataDxfId="60"/>
-    <tableColumn id="14" xr3:uid="{DA857B5E-985B-B946-AB84-87E571EEF3AB}" name="Source_type" dataDxfId="18"/>
-    <tableColumn id="7" xr3:uid="{3FFDDD67-7E94-CE4D-B56E-DFAC9F1681E3}" name="Company" dataDxfId="59"/>
-    <tableColumn id="8" xr3:uid="{342E13F5-266B-7B42-BD6B-BB868EA49B97}" name="Country" dataDxfId="58"/>
-    <tableColumn id="9" xr3:uid="{69240109-8B46-AB43-AD07-1F40DB5F9C94}" name="Year" dataDxfId="57"/>
-    <tableColumn id="10" xr3:uid="{5ED27922-9168-D142-BBEF-32C7AE06ABD3}" name="Covid" dataDxfId="56"/>
-    <tableColumn id="13" xr3:uid="{0563ACCB-80F5-4F46-ADA0-9040F1D87085}" name="Communicator_role" dataDxfId="19"/>
-    <tableColumn id="11" xr3:uid="{C38872CB-C9B9-1249-9741-B341922B9857}" name="Communicator_name" dataDxfId="55"/>
-    <tableColumn id="12" xr3:uid="{DBF7903A-F082-FB40-B41C-987ABF6BC279}" name="Comment" dataDxfId="54"/>
+    <tableColumn id="1" xr3:uid="{E398D18F-D9B1-8C4A-B81C-4F23A58404BA}" name="ID" dataDxfId="93"/>
+    <tableColumn id="2" xr3:uid="{41682781-F3C4-A842-B6E4-CD72DE688AF5}" name="Text" dataDxfId="92"/>
+    <tableColumn id="3" xr3:uid="{C1B517F2-40CD-8F40-9B4C-E34FFCCE3881}" name="Text_type" dataDxfId="91"/>
+    <tableColumn id="4" xr3:uid="{74E0C65C-5577-A146-9EE5-20C594C4316D}" name="Leadership_context" dataDxfId="90"/>
+    <tableColumn id="5" xr3:uid="{DDC33EC8-2DCC-DF43-9A08-EC991A2EA183}" name="Information_valence" dataDxfId="89"/>
+    <tableColumn id="6" xr3:uid="{C7BBAC6F-3D8E-B149-B9F0-D0A909FCC061}" name="Communication_type" dataDxfId="88"/>
+    <tableColumn id="14" xr3:uid="{DA857B5E-985B-B946-AB84-87E571EEF3AB}" name="Source_type" dataDxfId="87"/>
+    <tableColumn id="7" xr3:uid="{3FFDDD67-7E94-CE4D-B56E-DFAC9F1681E3}" name="Company" dataDxfId="86"/>
+    <tableColumn id="8" xr3:uid="{342E13F5-266B-7B42-BD6B-BB868EA49B97}" name="Country" dataDxfId="85"/>
+    <tableColumn id="9" xr3:uid="{69240109-8B46-AB43-AD07-1F40DB5F9C94}" name="Year" dataDxfId="84"/>
+    <tableColumn id="10" xr3:uid="{5ED27922-9168-D142-BBEF-32C7AE06ABD3}" name="Covid" dataDxfId="83"/>
+    <tableColumn id="13" xr3:uid="{0563ACCB-80F5-4F46-ADA0-9040F1D87085}" name="Communicator_role" dataDxfId="82"/>
+    <tableColumn id="11" xr3:uid="{C38872CB-C9B9-1249-9741-B341922B9857}" name="Communicator_name" dataDxfId="81"/>
+    <tableColumn id="12" xr3:uid="{DBF7903A-F082-FB40-B41C-987ABF6BC279}" name="Comment" dataDxfId="80"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{49AA2418-AB03-1149-B07A-3CC5FF67C997}" name="Tableau1345" displayName="Tableau1345" ref="A1:N2" totalsRowShown="0" headerRowDxfId="53" dataDxfId="52">
-  <autoFilter ref="A1:N2" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{49AA2418-AB03-1149-B07A-3CC5FF67C997}" name="Tableau1345" displayName="Tableau1345" ref="A1:N23" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14">
+  <autoFilter ref="A1:N23" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N2">
     <sortCondition ref="A1:A2"/>
   </sortState>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{E88F34DD-82B0-AD49-8C17-D8E9CFF03D07}" name="ID" dataDxfId="51"/>
-    <tableColumn id="2" xr3:uid="{88FC91F1-83E8-1B40-AC59-24D584573CCF}" name="Text" dataDxfId="50"/>
-    <tableColumn id="3" xr3:uid="{15432912-C615-E748-A229-EAA1D750204D}" name="Text_type" dataDxfId="49"/>
-    <tableColumn id="4" xr3:uid="{1025B200-F152-0B42-88C1-A31B3C27DB9E}" name="Leadership_context" dataDxfId="48"/>
-    <tableColumn id="5" xr3:uid="{D41F3D09-61AB-B841-88C7-5242CDC613BF}" name="Information_valence" dataDxfId="47"/>
-    <tableColumn id="6" xr3:uid="{CE749A1F-4ED8-1C40-9BE6-FB737E09C230}" name="Communication_type" dataDxfId="46"/>
-    <tableColumn id="13" xr3:uid="{BDC21215-E7B5-5C4C-B5AB-80E86EA24E05}" name="Source_type" dataDxfId="22"/>
-    <tableColumn id="7" xr3:uid="{A6F61E0C-8D32-F54F-8B88-CFAABE31D5B0}" name="Company" dataDxfId="45"/>
-    <tableColumn id="8" xr3:uid="{84CFAC4D-579E-AA4B-9DFE-FB605F75FBA9}" name="Country" dataDxfId="44"/>
-    <tableColumn id="9" xr3:uid="{1BA4063C-1918-624B-9757-FC2F3E5A7EE2}" name="Year" dataDxfId="43"/>
-    <tableColumn id="10" xr3:uid="{82840B5F-FD1C-614B-9755-28207407D6E2}" name="Covid" dataDxfId="42"/>
-    <tableColumn id="14" xr3:uid="{3F460577-A4A9-C947-8FBE-832A71AF2E55}" name="Communicator_role" dataDxfId="20"/>
-    <tableColumn id="11" xr3:uid="{3C67D01C-1B28-EB45-A3B2-FA7774BA5A24}" name="Communicator_name" dataDxfId="21"/>
-    <tableColumn id="12" xr3:uid="{7581B405-4702-5B40-9BBE-C98F342B9125}" name="Comment" dataDxfId="41"/>
+    <tableColumn id="1" xr3:uid="{E88F34DD-82B0-AD49-8C17-D8E9CFF03D07}" name="ID" dataDxfId="13"/>
+    <tableColumn id="2" xr3:uid="{88FC91F1-83E8-1B40-AC59-24D584573CCF}" name="Text" dataDxfId="12"/>
+    <tableColumn id="3" xr3:uid="{15432912-C615-E748-A229-EAA1D750204D}" name="Text_type" dataDxfId="11"/>
+    <tableColumn id="4" xr3:uid="{1025B200-F152-0B42-88C1-A31B3C27DB9E}" name="Leadership_context" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{D41F3D09-61AB-B841-88C7-5242CDC613BF}" name="Information_valence" dataDxfId="9"/>
+    <tableColumn id="6" xr3:uid="{CE749A1F-4ED8-1C40-9BE6-FB737E09C230}" name="Communication_type" dataDxfId="8"/>
+    <tableColumn id="13" xr3:uid="{BDC21215-E7B5-5C4C-B5AB-80E86EA24E05}" name="Source_type" dataDxfId="7"/>
+    <tableColumn id="7" xr3:uid="{A6F61E0C-8D32-F54F-8B88-CFAABE31D5B0}" name="Company" dataDxfId="6"/>
+    <tableColumn id="8" xr3:uid="{84CFAC4D-579E-AA4B-9DFE-FB605F75FBA9}" name="Country" dataDxfId="5"/>
+    <tableColumn id="9" xr3:uid="{1BA4063C-1918-624B-9757-FC2F3E5A7EE2}" name="Year" dataDxfId="4"/>
+    <tableColumn id="10" xr3:uid="{82840B5F-FD1C-614B-9755-28207407D6E2}" name="Covid" dataDxfId="3"/>
+    <tableColumn id="14" xr3:uid="{3F460577-A4A9-C947-8FBE-832A71AF2E55}" name="Communicator_role" dataDxfId="2"/>
+    <tableColumn id="11" xr3:uid="{3C67D01C-1B28-EB45-A3B2-FA7774BA5A24}" name="Communicator_name" dataDxfId="1"/>
+    <tableColumn id="12" xr3:uid="{7581B405-4702-5B40-9BBE-C98F342B9125}" name="Comment" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{3E6C7F84-1A88-2149-AAB1-B94EF8830151}" name="Tableau13456" displayName="Tableau13456" ref="A1:N2" totalsRowShown="0" headerRowDxfId="40" dataDxfId="39">
-  <autoFilter ref="A1:N2" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{3E6C7F84-1A88-2149-AAB1-B94EF8830151}" name="Tableau13456" displayName="Tableau13456" ref="A1:N11" totalsRowShown="0" headerRowDxfId="47" dataDxfId="46">
+  <autoFilter ref="A1:N11" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N2">
     <sortCondition ref="A1:A2"/>
   </sortState>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{86F19330-6E72-0543-BBCC-6D193B41E96F}" name="ID" dataDxfId="38"/>
-    <tableColumn id="2" xr3:uid="{6C469BD5-B4CF-8D4F-A2F6-F0E834902E4A}" name="Text" dataDxfId="37"/>
-    <tableColumn id="3" xr3:uid="{FE673CA5-CBC5-A34F-8A0C-C1CD6D144617}" name="Text_type" dataDxfId="36"/>
-    <tableColumn id="4" xr3:uid="{4248AFAD-ABBE-A942-8BC5-6258F7CF5E07}" name="Leadership_context" dataDxfId="35"/>
-    <tableColumn id="5" xr3:uid="{9D393B8E-A5EB-6240-B5FD-D449006530E5}" name="Information_valence" dataDxfId="34"/>
-    <tableColumn id="6" xr3:uid="{9677B29B-2D61-544A-85E3-A9C0FF7FBFCF}" name="Communication_type" dataDxfId="33"/>
-    <tableColumn id="14" xr3:uid="{5175FC7C-275C-FB4E-8512-D7A2B81AEEA9}" name="Source_type" dataDxfId="23"/>
-    <tableColumn id="7" xr3:uid="{9949BF20-7E90-2D45-A547-C4EF102C2AF9}" name="Company" dataDxfId="32"/>
-    <tableColumn id="8" xr3:uid="{5676BCFB-C3B1-444F-8A31-FAE43C2412E4}" name="Country" dataDxfId="31"/>
-    <tableColumn id="9" xr3:uid="{065AECA5-A4C6-784E-B897-9C586B53EEC2}" name="Year" dataDxfId="30"/>
-    <tableColumn id="10" xr3:uid="{9FE554FC-C9E9-BD44-8CBB-7E5AF11D1DDA}" name="Covid" dataDxfId="29"/>
-    <tableColumn id="13" xr3:uid="{93285A16-1AFB-F940-A523-560D3B0D9284}" name="Communicator_role" dataDxfId="24"/>
-    <tableColumn id="11" xr3:uid="{3C88AB16-0597-6246-B1EA-CED5E74629EC}" name="Communicator_name" dataDxfId="28"/>
-    <tableColumn id="12" xr3:uid="{75A6A75A-B89A-C341-99C3-8E0AF84308E5}" name="Comment" dataDxfId="27"/>
+    <tableColumn id="1" xr3:uid="{86F19330-6E72-0543-BBCC-6D193B41E96F}" name="ID" dataDxfId="45"/>
+    <tableColumn id="2" xr3:uid="{6C469BD5-B4CF-8D4F-A2F6-F0E834902E4A}" name="Text" dataDxfId="44"/>
+    <tableColumn id="3" xr3:uid="{FE673CA5-CBC5-A34F-8A0C-C1CD6D144617}" name="Text_type" dataDxfId="43"/>
+    <tableColumn id="4" xr3:uid="{4248AFAD-ABBE-A942-8BC5-6258F7CF5E07}" name="Leadership_context" dataDxfId="42"/>
+    <tableColumn id="5" xr3:uid="{9D393B8E-A5EB-6240-B5FD-D449006530E5}" name="Information_valence" dataDxfId="41"/>
+    <tableColumn id="6" xr3:uid="{9677B29B-2D61-544A-85E3-A9C0FF7FBFCF}" name="Communication_type" dataDxfId="40"/>
+    <tableColumn id="14" xr3:uid="{5175FC7C-275C-FB4E-8512-D7A2B81AEEA9}" name="Source_type" dataDxfId="39"/>
+    <tableColumn id="7" xr3:uid="{9949BF20-7E90-2D45-A547-C4EF102C2AF9}" name="Company" dataDxfId="38"/>
+    <tableColumn id="8" xr3:uid="{5676BCFB-C3B1-444F-8A31-FAE43C2412E4}" name="Country" dataDxfId="37"/>
+    <tableColumn id="9" xr3:uid="{065AECA5-A4C6-784E-B897-9C586B53EEC2}" name="Year" dataDxfId="36"/>
+    <tableColumn id="10" xr3:uid="{9FE554FC-C9E9-BD44-8CBB-7E5AF11D1DDA}" name="Covid" dataDxfId="35"/>
+    <tableColumn id="13" xr3:uid="{93285A16-1AFB-F940-A523-560D3B0D9284}" name="Communicator_role" dataDxfId="34"/>
+    <tableColumn id="11" xr3:uid="{3C88AB16-0597-6246-B1EA-CED5E74629EC}" name="Communicator_name" dataDxfId="33"/>
+    <tableColumn id="12" xr3:uid="{75A6A75A-B89A-C341-99C3-8E0AF84308E5}" name="Comment" dataDxfId="32"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{4E11BC3F-0045-1646-B076-F2B520D6852E}" name="Tableau134567" displayName="Tableau134567" ref="A1:N2" totalsRowShown="0" headerRowDxfId="95" dataDxfId="94">
-  <autoFilter ref="A1:N2" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{4E11BC3F-0045-1646-B076-F2B520D6852E}" name="Tableau134567" displayName="Tableau134567" ref="A1:N16" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30">
+  <autoFilter ref="A1:N16" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N2">
     <sortCondition ref="A1:A2"/>
   </sortState>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{31CE9BA4-76C4-7243-9CC4-2D69B48697C4}" name="ID" dataDxfId="93"/>
-    <tableColumn id="2" xr3:uid="{E9507622-53C7-7C46-AD19-75B0C284C739}" name="Text" dataDxfId="92"/>
-    <tableColumn id="3" xr3:uid="{B61A97EA-38E3-824E-AFFF-6DA5B0F5F799}" name="Text_type" dataDxfId="91"/>
-    <tableColumn id="4" xr3:uid="{C4A6AEE0-93C2-654B-AED8-9DFE0C336FBC}" name="Leadership_context" dataDxfId="90"/>
-    <tableColumn id="5" xr3:uid="{8B799C91-B83E-4740-8FF8-D018A500B838}" name="Information_valence" dataDxfId="89"/>
-    <tableColumn id="6" xr3:uid="{66E32C8C-3CF0-FF4A-8434-3DDE14801826}" name="Communication_type" dataDxfId="88"/>
-    <tableColumn id="13" xr3:uid="{0421BDDD-F24B-E84B-BE66-A9572A63BB7E}" name="Source_type" dataDxfId="26"/>
-    <tableColumn id="7" xr3:uid="{BB1E2451-7FCA-A546-B2ED-629286E517B1}" name="Company" dataDxfId="87"/>
-    <tableColumn id="8" xr3:uid="{A7D9EB9F-21C3-A443-AA66-25E92544A3D1}" name="Country" dataDxfId="86"/>
-    <tableColumn id="9" xr3:uid="{B9243626-106E-F940-9214-C16A4B219151}" name="Year" dataDxfId="85"/>
-    <tableColumn id="10" xr3:uid="{F1B3134A-8772-B940-A033-7567227076E7}" name="Covid" dataDxfId="84"/>
-    <tableColumn id="14" xr3:uid="{2561A683-C0E9-A44B-9AEB-9C3356F44833}" name="Communicator_role" dataDxfId="25"/>
-    <tableColumn id="11" xr3:uid="{AB9A4529-C11B-2A4B-9D39-3BBE9A62DD87}" name="Communicator_name" dataDxfId="83"/>
-    <tableColumn id="12" xr3:uid="{A2188241-51A1-7D40-927A-99ACD6E9501D}" name="Comment" dataDxfId="82"/>
+    <tableColumn id="1" xr3:uid="{31CE9BA4-76C4-7243-9CC4-2D69B48697C4}" name="ID" dataDxfId="29"/>
+    <tableColumn id="2" xr3:uid="{E9507622-53C7-7C46-AD19-75B0C284C739}" name="Text" dataDxfId="28"/>
+    <tableColumn id="3" xr3:uid="{B61A97EA-38E3-824E-AFFF-6DA5B0F5F799}" name="Text_type" dataDxfId="27"/>
+    <tableColumn id="4" xr3:uid="{C4A6AEE0-93C2-654B-AED8-9DFE0C336FBC}" name="Leadership_context" dataDxfId="26"/>
+    <tableColumn id="5" xr3:uid="{8B799C91-B83E-4740-8FF8-D018A500B838}" name="Information_valence" dataDxfId="25"/>
+    <tableColumn id="6" xr3:uid="{66E32C8C-3CF0-FF4A-8434-3DDE14801826}" name="Communication_type" dataDxfId="24"/>
+    <tableColumn id="13" xr3:uid="{0421BDDD-F24B-E84B-BE66-A9572A63BB7E}" name="Source_type" dataDxfId="23"/>
+    <tableColumn id="7" xr3:uid="{BB1E2451-7FCA-A546-B2ED-629286E517B1}" name="Company" dataDxfId="22"/>
+    <tableColumn id="8" xr3:uid="{A7D9EB9F-21C3-A443-AA66-25E92544A3D1}" name="Country" dataDxfId="21"/>
+    <tableColumn id="9" xr3:uid="{B9243626-106E-F940-9214-C16A4B219151}" name="Year" dataDxfId="20"/>
+    <tableColumn id="10" xr3:uid="{F1B3134A-8772-B940-A033-7567227076E7}" name="Covid" dataDxfId="19"/>
+    <tableColumn id="14" xr3:uid="{2561A683-C0E9-A44B-9AEB-9C3356F44833}" name="Communicator_role" dataDxfId="18"/>
+    <tableColumn id="11" xr3:uid="{AB9A4529-C11B-2A4B-9D39-3BBE9A62DD87}" name="Communicator_name" dataDxfId="17"/>
+    <tableColumn id="12" xr3:uid="{A2188241-51A1-7D40-927A-99ACD6E9501D}" name="Comment" dataDxfId="16"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1359,6 +1630,9 @@
       <c r="C2" s="1" t="s">
         <v>45</v>
       </c>
+      <c r="F2" s="1" t="s">
+        <v>184</v>
+      </c>
       <c r="G2" s="1" t="s">
         <v>25</v>
       </c>
@@ -1381,7 +1655,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="51" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:14" ht="34" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>47</v>
       </c>
@@ -1391,6 +1665,9 @@
       <c r="C3" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="F3" s="1" t="s">
+        <v>184</v>
+      </c>
       <c r="G3" s="1" t="s">
         <v>25</v>
       </c>
@@ -1413,7 +1690,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="51" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:14" ht="34" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>48</v>
       </c>
@@ -1422,6 +1699,9 @@
       </c>
       <c r="C4" s="1" t="s">
         <v>46</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>184</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>25</v>
@@ -1455,6 +1735,9 @@
       <c r="C5" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="F5" s="1" t="s">
+        <v>184</v>
+      </c>
       <c r="G5" s="1" t="s">
         <v>25</v>
       </c>
@@ -1487,6 +1770,9 @@
       <c r="C6" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="F6" s="1" t="s">
+        <v>184</v>
+      </c>
       <c r="G6" s="1" t="s">
         <v>25</v>
       </c>
@@ -1509,7 +1795,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="51" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" ht="34" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>51</v>
       </c>
@@ -1519,6 +1805,9 @@
       <c r="C7" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="F7" s="1" t="s">
+        <v>184</v>
+      </c>
       <c r="G7" s="1" t="s">
         <v>25</v>
       </c>
@@ -1541,7 +1830,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="170" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" ht="153" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>52</v>
       </c>
@@ -1551,6 +1840,9 @@
       <c r="C8" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="F8" s="1" t="s">
+        <v>184</v>
+      </c>
       <c r="G8" s="1" t="s">
         <v>25</v>
       </c>
@@ -1573,7 +1865,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="136" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:14" ht="119" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>53</v>
       </c>
@@ -1583,6 +1875,9 @@
       <c r="C9" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="F9" s="1" t="s">
+        <v>184</v>
+      </c>
       <c r="G9" s="1" t="s">
         <v>25</v>
       </c>
@@ -1605,7 +1900,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="136" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:14" ht="119" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>54</v>
       </c>
@@ -1614,6 +1909,9 @@
       </c>
       <c r="C10" s="1" t="s">
         <v>46</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>184</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>25</v>
@@ -1647,6 +1945,9 @@
       <c r="C11" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="F11" s="1" t="s">
+        <v>184</v>
+      </c>
       <c r="G11" s="1" t="s">
         <v>25</v>
       </c>
@@ -1679,6 +1980,9 @@
       <c r="C12" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="F12" s="1" t="s">
+        <v>184</v>
+      </c>
       <c r="G12" s="1" t="s">
         <v>25</v>
       </c>
@@ -1711,6 +2015,9 @@
       <c r="C13" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="F13" s="1" t="s">
+        <v>184</v>
+      </c>
       <c r="G13" s="1" t="s">
         <v>25</v>
       </c>
@@ -1743,6 +2050,9 @@
       <c r="C14" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="F14" s="1" t="s">
+        <v>184</v>
+      </c>
       <c r="G14" s="1" t="s">
         <v>25</v>
       </c>
@@ -1775,6 +2085,9 @@
       <c r="C15" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="F15" s="1" t="s">
+        <v>184</v>
+      </c>
       <c r="G15" s="1" t="s">
         <v>25</v>
       </c>
@@ -1807,6 +2120,9 @@
       <c r="C16" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="F16" s="1" t="s">
+        <v>184</v>
+      </c>
       <c r="G16" s="1" t="s">
         <v>25</v>
       </c>
@@ -1839,6 +2155,9 @@
       <c r="C17" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="F17" s="1" t="s">
+        <v>184</v>
+      </c>
       <c r="G17" s="1" t="s">
         <v>25</v>
       </c>
@@ -1871,6 +2190,9 @@
       <c r="C18" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="F18" s="1" t="s">
+        <v>184</v>
+      </c>
       <c r="G18" s="1" t="s">
         <v>25</v>
       </c>
@@ -1903,6 +2225,9 @@
       <c r="C19" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="F19" s="1" t="s">
+        <v>184</v>
+      </c>
       <c r="G19" s="1" t="s">
         <v>25</v>
       </c>
@@ -1934,6 +2259,9 @@
       </c>
       <c r="C20" s="1" t="s">
         <v>46</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>184</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>25</v>
@@ -2037,6 +2365,9 @@
       <c r="C2" s="1" t="s">
         <v>82</v>
       </c>
+      <c r="F2" s="1" t="s">
+        <v>184</v>
+      </c>
       <c r="G2" s="1" t="s">
         <v>25</v>
       </c>
@@ -2059,7 +2390,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="68" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>83</v>
       </c>
@@ -2068,6 +2399,9 @@
       </c>
       <c r="C3" s="1" t="s">
         <v>46</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>184</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>25</v>
@@ -2101,6 +2435,9 @@
       <c r="C4" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="F4" s="1" t="s">
+        <v>184</v>
+      </c>
       <c r="G4" s="1" t="s">
         <v>25</v>
       </c>
@@ -2133,6 +2470,9 @@
       <c r="C5" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="F5" s="1" t="s">
+        <v>184</v>
+      </c>
       <c r="G5" s="1" t="s">
         <v>25</v>
       </c>
@@ -2165,6 +2505,9 @@
       <c r="C6" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="F6" s="1" t="s">
+        <v>184</v>
+      </c>
       <c r="G6" s="1" t="s">
         <v>25</v>
       </c>
@@ -2187,7 +2530,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="68" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>87</v>
       </c>
@@ -2196,6 +2539,9 @@
       </c>
       <c r="C7" s="1" t="s">
         <v>46</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>184</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>25</v>
@@ -2229,6 +2575,9 @@
       <c r="C8" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="F8" s="1" t="s">
+        <v>184</v>
+      </c>
       <c r="G8" s="1" t="s">
         <v>25</v>
       </c>
@@ -2261,6 +2610,9 @@
       <c r="C9" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="F9" s="1" t="s">
+        <v>184</v>
+      </c>
       <c r="G9" s="1" t="s">
         <v>25</v>
       </c>
@@ -2283,7 +2635,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="102" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:14" ht="68" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>90</v>
       </c>
@@ -2292,6 +2644,9 @@
       </c>
       <c r="C10" s="1" t="s">
         <v>46</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>184</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>25</v>
@@ -2325,6 +2680,9 @@
       <c r="C11" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="F11" s="1" t="s">
+        <v>184</v>
+      </c>
       <c r="G11" s="1" t="s">
         <v>25</v>
       </c>
@@ -2357,6 +2715,9 @@
       <c r="C12" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="F12" s="1" t="s">
+        <v>184</v>
+      </c>
       <c r="G12" s="1" t="s">
         <v>25</v>
       </c>
@@ -2389,6 +2750,9 @@
       <c r="C13" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="F13" s="1" t="s">
+        <v>184</v>
+      </c>
       <c r="G13" s="1" t="s">
         <v>25</v>
       </c>
@@ -2421,6 +2785,9 @@
       <c r="C14" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="F14" s="1" t="s">
+        <v>184</v>
+      </c>
       <c r="G14" s="1" t="s">
         <v>25</v>
       </c>
@@ -2453,6 +2820,9 @@
       <c r="C15" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="F15" s="1" t="s">
+        <v>184</v>
+      </c>
       <c r="G15" s="1" t="s">
         <v>25</v>
       </c>
@@ -2485,6 +2855,9 @@
       <c r="C16" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="F16" s="1" t="s">
+        <v>184</v>
+      </c>
       <c r="G16" s="1" t="s">
         <v>25</v>
       </c>
@@ -2516,6 +2889,9 @@
       </c>
       <c r="C17" s="1" t="s">
         <v>46</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>184</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>25</v>
@@ -2618,6 +2994,9 @@
       <c r="C2" s="1" t="s">
         <v>82</v>
       </c>
+      <c r="F2" s="1" t="s">
+        <v>184</v>
+      </c>
       <c r="G2" s="1" t="s">
         <v>25</v>
       </c>
@@ -2650,6 +3029,9 @@
       <c r="C3" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="F3" s="1" t="s">
+        <v>184</v>
+      </c>
       <c r="G3" s="1" t="s">
         <v>25</v>
       </c>
@@ -2672,7 +3054,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="119" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:14" ht="85" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>119</v>
       </c>
@@ -2681,6 +3063,9 @@
       </c>
       <c r="C4" s="1" t="s">
         <v>46</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>184</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>25</v>
@@ -2714,6 +3099,9 @@
       <c r="C5" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="F5" s="1" t="s">
+        <v>184</v>
+      </c>
       <c r="G5" s="1" t="s">
         <v>25</v>
       </c>
@@ -2746,6 +3134,9 @@
       <c r="C6" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="F6" s="1" t="s">
+        <v>184</v>
+      </c>
       <c r="G6" s="1" t="s">
         <v>25</v>
       </c>
@@ -2778,6 +3169,9 @@
       <c r="C7" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="F7" s="1" t="s">
+        <v>184</v>
+      </c>
       <c r="G7" s="1" t="s">
         <v>25</v>
       </c>
@@ -2810,6 +3204,9 @@
       <c r="C8" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="F8" s="1" t="s">
+        <v>184</v>
+      </c>
       <c r="G8" s="1" t="s">
         <v>25</v>
       </c>
@@ -2842,6 +3239,9 @@
       <c r="C9" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="F9" s="1" t="s">
+        <v>184</v>
+      </c>
       <c r="G9" s="1" t="s">
         <v>25</v>
       </c>
@@ -2874,6 +3274,9 @@
       <c r="C10" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="F10" s="1" t="s">
+        <v>184</v>
+      </c>
       <c r="G10" s="1" t="s">
         <v>25</v>
       </c>
@@ -2906,6 +3309,9 @@
       <c r="C11" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="F11" s="1" t="s">
+        <v>184</v>
+      </c>
       <c r="G11" s="1" t="s">
         <v>25</v>
       </c>
@@ -2938,6 +3344,9 @@
       <c r="C12" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="F12" s="1" t="s">
+        <v>184</v>
+      </c>
       <c r="G12" s="1" t="s">
         <v>25</v>
       </c>
@@ -2970,6 +3379,9 @@
       <c r="C13" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="F13" s="1" t="s">
+        <v>184</v>
+      </c>
       <c r="G13" s="1" t="s">
         <v>25</v>
       </c>
@@ -3002,6 +3414,9 @@
       <c r="C14" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="F14" s="1" t="s">
+        <v>184</v>
+      </c>
       <c r="G14" s="1" t="s">
         <v>25</v>
       </c>
@@ -3034,6 +3449,9 @@
       <c r="C15" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="F15" s="1" t="s">
+        <v>184</v>
+      </c>
       <c r="G15" s="1" t="s">
         <v>25</v>
       </c>
@@ -3066,6 +3484,9 @@
       <c r="C16" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="F16" s="1" t="s">
+        <v>184</v>
+      </c>
       <c r="G16" s="1" t="s">
         <v>25</v>
       </c>
@@ -3098,6 +3519,9 @@
       <c r="C17" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="F17" s="1" t="s">
+        <v>184</v>
+      </c>
       <c r="G17" s="1" t="s">
         <v>25</v>
       </c>
@@ -3130,6 +3554,9 @@
       <c r="C18" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="F18" s="1" t="s">
+        <v>184</v>
+      </c>
       <c r="G18" s="1" t="s">
         <v>25</v>
       </c>
@@ -3162,6 +3589,9 @@
       <c r="C19" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="F19" s="1" t="s">
+        <v>184</v>
+      </c>
       <c r="G19" s="1" t="s">
         <v>25</v>
       </c>
@@ -3194,6 +3624,9 @@
       <c r="C20" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="F20" s="1" t="s">
+        <v>184</v>
+      </c>
       <c r="G20" s="1" t="s">
         <v>25</v>
       </c>
@@ -3225,6 +3658,9 @@
       </c>
       <c r="C21" s="1" t="s">
         <v>46</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>184</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>25</v>
@@ -3258,7 +3694,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C026E3D-BA89-8B46-8C08-84D4DE3BA69B}">
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
@@ -3317,11 +3753,19 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="2"/>
+      <c r="B2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>184</v>
+      </c>
       <c r="G2" s="1" t="s">
         <v>25</v>
       </c>
@@ -3336,6 +3780,747 @@
       </c>
       <c r="K2" s="1" t="s">
         <v>10</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="153" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J3" s="1">
+        <v>2024</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="85" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J4" s="1">
+        <v>2024</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="119" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J5" s="1">
+        <v>2024</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="136" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J6" s="1">
+        <v>2024</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="136" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J7" s="1">
+        <v>2024</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="119" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J8" s="1">
+        <v>2024</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="136" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J9" s="1">
+        <v>2024</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="68" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J10" s="1">
+        <v>2024</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="51" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J11" s="1">
+        <v>2024</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="68" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J12" s="1">
+        <v>2024</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="102" x14ac:dyDescent="0.2">
+      <c r="A13" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J13" s="1">
+        <v>2024</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M13" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="68" x14ac:dyDescent="0.2">
+      <c r="A14" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J14" s="1">
+        <v>2024</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M14" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="68" x14ac:dyDescent="0.2">
+      <c r="A15" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J15" s="1">
+        <v>2024</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M15" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="51" x14ac:dyDescent="0.2">
+      <c r="A16" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J16" s="1">
+        <v>2024</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L16" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M16" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="51" x14ac:dyDescent="0.2">
+      <c r="A17" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J17" s="1">
+        <v>2024</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L17" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M17" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="136" x14ac:dyDescent="0.2">
+      <c r="A18" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J18" s="1">
+        <v>2024</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L18" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M18" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="119" x14ac:dyDescent="0.2">
+      <c r="A19" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J19" s="1">
+        <v>2024</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L19" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M19" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="119" x14ac:dyDescent="0.2">
+      <c r="A20" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J20" s="1">
+        <v>2024</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M20" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="119" x14ac:dyDescent="0.2">
+      <c r="A21" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J21" s="1">
+        <v>2024</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L21" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M21" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="102" x14ac:dyDescent="0.2">
+      <c r="A22" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J22" s="1">
+        <v>2024</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L22" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M22" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" ht="85" x14ac:dyDescent="0.2">
+      <c r="A23" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J23" s="1">
+        <v>2024</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L23" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M23" s="1" t="s">
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -3348,11 +4533,11 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46F01D49-A94C-464D-86C0-23DAAD0A1777}">
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="64.1640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="84.83203125" style="1" customWidth="1"/>
     <col min="3" max="3" width="12.5" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18.83203125" style="1" customWidth="1"/>
@@ -3407,11 +4592,19 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B2" s="2"/>
+      <c r="B2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>184</v>
+      </c>
       <c r="G2" s="1" t="s">
         <v>25</v>
       </c>
@@ -3426,6 +4619,327 @@
       </c>
       <c r="K2" s="1" t="s">
         <v>19</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="119" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J3" s="1">
+        <v>2024</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="102" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J4" s="1">
+        <v>2024</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="85" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J5" s="1">
+        <v>2024</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="85" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J6" s="1">
+        <v>2024</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="102" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J7" s="1">
+        <v>2024</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="170" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J8" s="1">
+        <v>2024</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="170" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J9" s="1">
+        <v>2024</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="119" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J10" s="1">
+        <v>2024</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="85" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J11" s="1">
+        <v>2024</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -3438,11 +4952,11 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F043F7F6-3A06-0B46-BD8B-5A267CD4419E}">
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="64.1640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="106.33203125" style="1" customWidth="1"/>
     <col min="3" max="3" width="12.5" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18.83203125" style="1" customWidth="1"/>
@@ -3497,11 +5011,19 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="2"/>
+      <c r="B2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>184</v>
+      </c>
       <c r="G2" s="1" t="s">
         <v>25</v>
       </c>
@@ -3516,6 +5038,502 @@
       </c>
       <c r="K2" s="1" t="s">
         <v>21</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="85" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J3" s="1">
+        <v>2025</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="34" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J4" s="1">
+        <v>2025</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="68" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J5" s="1">
+        <v>2025</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="102" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J6" s="1">
+        <v>2025</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="102" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J7" s="1">
+        <v>2025</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="68" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J8" s="1">
+        <v>2025</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="85" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J9" s="1">
+        <v>2025</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="102" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J10" s="1">
+        <v>2025</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="85" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J11" s="1">
+        <v>2025</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="136" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J12" s="1">
+        <v>2025</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="85" x14ac:dyDescent="0.2">
+      <c r="A13" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J13" s="1">
+        <v>2025</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M13" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="68" x14ac:dyDescent="0.2">
+      <c r="A14" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J14" s="1">
+        <v>2025</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M14" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="68" x14ac:dyDescent="0.2">
+      <c r="A15" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J15" s="1">
+        <v>2025</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M15" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="34" x14ac:dyDescent="0.2">
+      <c r="A16" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J16" s="1">
+        <v>2025</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L16" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M16" s="1" t="s">
+        <v>155</v>
       </c>
     </row>
   </sheetData>

--- a/data/input/puma.xlsx
+++ b/data/input/puma.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Saowalak/Desktop/CEOCommunication/data/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0774F66F-9DC4-EB43-8D90-FB97B3E2E9F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE527377-EEA1-E646-A135-7B30D63A2467}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7580" yWindow="600" windowWidth="21220" windowHeight="17400" activeTab="3" xr2:uid="{05EFD2A9-923A-834E-A816-A8C1AAE62552}"/>
+    <workbookView xWindow="7580" yWindow="600" windowWidth="21220" windowHeight="17400" activeTab="5" xr2:uid="{05EFD2A9-923A-834E-A816-A8C1AAE62552}"/>
   </bookViews>
   <sheets>
     <sheet name="2020" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1104" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1134" uniqueCount="232">
   <si>
     <t>ID</t>
   </si>
@@ -187,60 +187,6 @@
   </si>
   <si>
     <t>body_text</t>
-  </si>
-  <si>
-    <t>JPN20P01-00</t>
-  </si>
-  <si>
-    <t>JPN20P02-00</t>
-  </si>
-  <si>
-    <t>JPN20P03-00</t>
-  </si>
-  <si>
-    <t>JPN20P04-00</t>
-  </si>
-  <si>
-    <t>JPN20P05-00</t>
-  </si>
-  <si>
-    <t>JPN20P06-00</t>
-  </si>
-  <si>
-    <t>JPN20P07-00</t>
-  </si>
-  <si>
-    <t>JPN20P08-00</t>
-  </si>
-  <si>
-    <t>JPN20P09-00</t>
-  </si>
-  <si>
-    <t>JPN20P10-00</t>
-  </si>
-  <si>
-    <t>JPN20P11-00</t>
-  </si>
-  <si>
-    <t>JPN20P12-00</t>
-  </si>
-  <si>
-    <t>JPN20P13-00</t>
-  </si>
-  <si>
-    <t>JPN20P15-00</t>
-  </si>
-  <si>
-    <t>JPN20P16-00</t>
-  </si>
-  <si>
-    <t>JPN20P17-00</t>
-  </si>
-  <si>
-    <t>JPN20P18-00</t>
-  </si>
-  <si>
-    <t>JPN20P19-00</t>
   </si>
   <si>
     <t>Bjørn Gulden</t>
@@ -301,51 +247,6 @@
     <t xml:space="preserve">title </t>
   </si>
   <si>
-    <t>DEU21P01-00</t>
-  </si>
-  <si>
-    <t>DEU21P02-00</t>
-  </si>
-  <si>
-    <t>DEU21P03-00</t>
-  </si>
-  <si>
-    <t>DEU21P04-00</t>
-  </si>
-  <si>
-    <t>DEU21P05-00</t>
-  </si>
-  <si>
-    <t>DEU21P06-00</t>
-  </si>
-  <si>
-    <t>DEU21P07-00</t>
-  </si>
-  <si>
-    <t>DEU21P08-00</t>
-  </si>
-  <si>
-    <t>DEU21P09-00</t>
-  </si>
-  <si>
-    <t>DEU21P10-00</t>
-  </si>
-  <si>
-    <t>DEU21P11-00</t>
-  </si>
-  <si>
-    <t>DEU21P12-00</t>
-  </si>
-  <si>
-    <t>DEU21P13-00</t>
-  </si>
-  <si>
-    <t>DEU21P14-00</t>
-  </si>
-  <si>
-    <t>DEU21P15-00</t>
-  </si>
-  <si>
     <t>Arne Freundt</t>
   </si>
   <si>
@@ -407,63 +308,6 @@
 Chief Executive Officer, PUMA</t>
   </si>
   <si>
-    <t>DEU22P01-00</t>
-  </si>
-  <si>
-    <t>DEU22P02-00</t>
-  </si>
-  <si>
-    <t>DEU22P03-00</t>
-  </si>
-  <si>
-    <t>DEU22P04-00</t>
-  </si>
-  <si>
-    <t>DEU22P05-00</t>
-  </si>
-  <si>
-    <t>DEU22P06-00</t>
-  </si>
-  <si>
-    <t>DEU22P07-00</t>
-  </si>
-  <si>
-    <t>DEU22P08-00</t>
-  </si>
-  <si>
-    <t>DEU22P09-00</t>
-  </si>
-  <si>
-    <t>DEU22P10-00</t>
-  </si>
-  <si>
-    <t>DEU22P11-00</t>
-  </si>
-  <si>
-    <t>DEU22P12-00</t>
-  </si>
-  <si>
-    <t>DEU22P13-00</t>
-  </si>
-  <si>
-    <t>DEU22P14-00</t>
-  </si>
-  <si>
-    <t>DEU22P15-00</t>
-  </si>
-  <si>
-    <t>DEU22P16-00</t>
-  </si>
-  <si>
-    <t>DEU22P17-00</t>
-  </si>
-  <si>
-    <t>DEU22P18-00</t>
-  </si>
-  <si>
-    <t>DEU22P19-00</t>
-  </si>
-  <si>
     <t>In 2024, PUMA’s sales increased in a dynamic market environment by 4.4 currency-adjusted to € 8,817 million. We were able to improve our sales growth from quarter to quarter and grew by 9.8%, currency adjusted, in the fourth quarter. For the full year 2024, sales in all regions, product areas and distribution channels improved on a currency-adjusted basis compared to the previous year. This means PUMA has grown faster than the market, which  ecorded currency adjusted growth of 1.8% in 2024 according to Euromonitor.</t>
   </si>
   <si>
@@ -491,33 +335,6 @@
     <t>I would like to take this opportunity to thank the PUMA family - our employees, wholesale partners, suppliers, brand ambassadors and athletes - for their commitment and contribution. I am also very grateful to our Supervisory Board for their support in implementing our strategy. I would also like to thank you, our shareholders, for your trust.</t>
   </si>
   <si>
-    <t>DEU24P01-00</t>
-  </si>
-  <si>
-    <t>DEU24P02-00</t>
-  </si>
-  <si>
-    <t>DEU24P03-00</t>
-  </si>
-  <si>
-    <t>DEU24P04-00</t>
-  </si>
-  <si>
-    <t>DEU24P05-00</t>
-  </si>
-  <si>
-    <t>DEU24P06-00</t>
-  </si>
-  <si>
-    <t>DEU24P07-00</t>
-  </si>
-  <si>
-    <t>DEU24P08-00</t>
-  </si>
-  <si>
-    <t>DEU24P09-00</t>
-  </si>
-  <si>
     <t>Arthur Hoeld</t>
   </si>
   <si>
@@ -561,48 +378,6 @@
   </si>
   <si>
     <t>I would also like to thank you, dear shareholders, for your trust and support for the path we have chosen.</t>
-  </si>
-  <si>
-    <t>DEU25P01-00</t>
-  </si>
-  <si>
-    <t>DEU25P02-00</t>
-  </si>
-  <si>
-    <t>DEU25P03-00</t>
-  </si>
-  <si>
-    <t>DEU25P04-00</t>
-  </si>
-  <si>
-    <t>DEU25P05-00</t>
-  </si>
-  <si>
-    <t>DEU25P06-00</t>
-  </si>
-  <si>
-    <t>DEU25P07-00</t>
-  </si>
-  <si>
-    <t>DEU25P08-00</t>
-  </si>
-  <si>
-    <t>DEU25P09-00</t>
-  </si>
-  <si>
-    <t>DEU25P10-00</t>
-  </si>
-  <si>
-    <t>DEU25P11-00</t>
-  </si>
-  <si>
-    <t>DEU25P12-00</t>
-  </si>
-  <si>
-    <t>DEU25P13-00</t>
-  </si>
-  <si>
-    <t>DEU25P14-00</t>
   </si>
   <si>
     <t>letter</t>
@@ -672,67 +447,309 @@
     <t>I really look forward to 2024, which will be the Year of Sport with important sports events such as the Olympic Games, Euro 2024 and Copa America which give us great brand visibility. We continue to be the challenger in the market with the ambition to continue our success story and to gain further market share.</t>
   </si>
   <si>
-    <t>DEU23P01-00</t>
-  </si>
-  <si>
-    <t>DEU23P02-00</t>
-  </si>
-  <si>
-    <t>DEU23P03-00</t>
-  </si>
-  <si>
-    <t>DEU23P04-00</t>
-  </si>
-  <si>
-    <t>DEU23P05-00</t>
-  </si>
-  <si>
-    <t>DEU23P06-00</t>
-  </si>
-  <si>
-    <t>DEU23P07-00</t>
-  </si>
-  <si>
-    <t>DEU23P08-00</t>
-  </si>
-  <si>
-    <t>DEU23P09-00</t>
-  </si>
-  <si>
-    <t>DEU23P10-00</t>
-  </si>
-  <si>
-    <t>DEU23P11-00</t>
-  </si>
-  <si>
-    <t>DEU23P12-00</t>
-  </si>
-  <si>
-    <t>DEU23P13-00</t>
-  </si>
-  <si>
-    <t>DEU23P14-00</t>
-  </si>
-  <si>
-    <t>DEU23P15-00</t>
-  </si>
-  <si>
-    <t>DEU23P16-00</t>
-  </si>
-  <si>
-    <t>DEU23P17-00</t>
-  </si>
-  <si>
-    <t>DEU23P18-00</t>
-  </si>
-  <si>
-    <t>DEU23P19-00</t>
-  </si>
-  <si>
-    <t>DEU23P20-00</t>
-  </si>
-  <si>
-    <t>DEU23P21-00</t>
+    <t>DEU24P00-01</t>
+  </si>
+  <si>
+    <t>DEU24P00-02</t>
+  </si>
+  <si>
+    <t>DEU24P00-03</t>
+  </si>
+  <si>
+    <t>DEU24P00-04</t>
+  </si>
+  <si>
+    <t>DEU24P00-05</t>
+  </si>
+  <si>
+    <t>DEU24P00-06</t>
+  </si>
+  <si>
+    <t>DEU24P00-07</t>
+  </si>
+  <si>
+    <t>DEU24P00-08</t>
+  </si>
+  <si>
+    <t>DEU24P00-09</t>
+  </si>
+  <si>
+    <t>DEU25P00-01</t>
+  </si>
+  <si>
+    <t>DEU25P00-02</t>
+  </si>
+  <si>
+    <t>DEU25P00-03</t>
+  </si>
+  <si>
+    <t>DEU25P00-04</t>
+  </si>
+  <si>
+    <t>DEU25P00-05</t>
+  </si>
+  <si>
+    <t>DEU25P00-06</t>
+  </si>
+  <si>
+    <t>DEU25P00-07</t>
+  </si>
+  <si>
+    <t>DEU25P00-08</t>
+  </si>
+  <si>
+    <t>DEU25P00-09</t>
+  </si>
+  <si>
+    <t>DEU25P00-10</t>
+  </si>
+  <si>
+    <t>DEU25P00-11</t>
+  </si>
+  <si>
+    <t>DEU25P00-12</t>
+  </si>
+  <si>
+    <t>DEU25P00-13</t>
+  </si>
+  <si>
+    <t>DEU25P00-14</t>
+  </si>
+  <si>
+    <t>DEU23P00-01</t>
+  </si>
+  <si>
+    <t>DEU23P00-02</t>
+  </si>
+  <si>
+    <t>DEU23P00-03</t>
+  </si>
+  <si>
+    <t>DEU23P00-04</t>
+  </si>
+  <si>
+    <t>DEU23P00-05</t>
+  </si>
+  <si>
+    <t>DEU23P00-06</t>
+  </si>
+  <si>
+    <t>DEU23P00-07</t>
+  </si>
+  <si>
+    <t>DEU23P00-08</t>
+  </si>
+  <si>
+    <t>DEU23P00-09</t>
+  </si>
+  <si>
+    <t>DEU23P00-10</t>
+  </si>
+  <si>
+    <t>DEU23P00-11</t>
+  </si>
+  <si>
+    <t>DEU23P00-12</t>
+  </si>
+  <si>
+    <t>DEU23P00-13</t>
+  </si>
+  <si>
+    <t>DEU23P00-14</t>
+  </si>
+  <si>
+    <t>DEU23P00-15</t>
+  </si>
+  <si>
+    <t>DEU23P00-16</t>
+  </si>
+  <si>
+    <t>DEU23P00-17</t>
+  </si>
+  <si>
+    <t>DEU23P00-18</t>
+  </si>
+  <si>
+    <t>DEU23P00-19</t>
+  </si>
+  <si>
+    <t>DEU23P00-20</t>
+  </si>
+  <si>
+    <t>DEU23P00-21</t>
+  </si>
+  <si>
+    <t>DEU22P00-01</t>
+  </si>
+  <si>
+    <t>DEU22P00-02</t>
+  </si>
+  <si>
+    <t>DEU22P00-03</t>
+  </si>
+  <si>
+    <t>DEU22P00-04</t>
+  </si>
+  <si>
+    <t>DEU22P00-05</t>
+  </si>
+  <si>
+    <t>DEU22P00-06</t>
+  </si>
+  <si>
+    <t>DEU22P00-07</t>
+  </si>
+  <si>
+    <t>DEU22P00-08</t>
+  </si>
+  <si>
+    <t>DEU22P00-09</t>
+  </si>
+  <si>
+    <t>DEU22P00-10</t>
+  </si>
+  <si>
+    <t>DEU22P00-11</t>
+  </si>
+  <si>
+    <t>DEU22P00-12</t>
+  </si>
+  <si>
+    <t>DEU22P00-13</t>
+  </si>
+  <si>
+    <t>DEU22P00-14</t>
+  </si>
+  <si>
+    <t>DEU22P00-15</t>
+  </si>
+  <si>
+    <t>DEU22P00-16</t>
+  </si>
+  <si>
+    <t>DEU22P00-17</t>
+  </si>
+  <si>
+    <t>DEU22P00-18</t>
+  </si>
+  <si>
+    <t>DEU22P00-19</t>
+  </si>
+  <si>
+    <t>DEU21P00-01</t>
+  </si>
+  <si>
+    <t>DEU21P00-02</t>
+  </si>
+  <si>
+    <t>DEU21P00-03</t>
+  </si>
+  <si>
+    <t>DEU21P00-04</t>
+  </si>
+  <si>
+    <t>DEU21P00-05</t>
+  </si>
+  <si>
+    <t>DEU21P00-06</t>
+  </si>
+  <si>
+    <t>DEU21P00-07</t>
+  </si>
+  <si>
+    <t>DEU21P00-08</t>
+  </si>
+  <si>
+    <t>DEU21P00-09</t>
+  </si>
+  <si>
+    <t>DEU21P00-10</t>
+  </si>
+  <si>
+    <t>DEU21P00-11</t>
+  </si>
+  <si>
+    <t>DEU21P00-12</t>
+  </si>
+  <si>
+    <t>DEU21P00-13</t>
+  </si>
+  <si>
+    <t>DEU21P00-14</t>
+  </si>
+  <si>
+    <t>DEU21P00-15</t>
+  </si>
+  <si>
+    <t>JPN20P00-01</t>
+  </si>
+  <si>
+    <t>JPN20P00-02</t>
+  </si>
+  <si>
+    <t>JPN20P00-03</t>
+  </si>
+  <si>
+    <t>JPN20P00-04</t>
+  </si>
+  <si>
+    <t>JPN20P00-05</t>
+  </si>
+  <si>
+    <t>JPN20P00-06</t>
+  </si>
+  <si>
+    <t>JPN20P00-07</t>
+  </si>
+  <si>
+    <t>JPN20P00-08</t>
+  </si>
+  <si>
+    <t>JPN20P00-09</t>
+  </si>
+  <si>
+    <t>JPN20P00-10</t>
+  </si>
+  <si>
+    <t>JPN20P00-11</t>
+  </si>
+  <si>
+    <t>JPN20P00-12</t>
+  </si>
+  <si>
+    <t>JPN20P00-13</t>
+  </si>
+  <si>
+    <t>JPN20P00-14</t>
+  </si>
+  <si>
+    <t>JPN20P00-15</t>
+  </si>
+  <si>
+    <t>JPN20P00-16</t>
+  </si>
+  <si>
+    <t>JPN20P00-17</t>
+  </si>
+  <si>
+    <t>JPN20P00-18</t>
+  </si>
+  <si>
+    <t>Arne Freudt
+Chief Executive Officer PUMA</t>
+  </si>
+  <si>
+    <t>DEU23P00-22</t>
+  </si>
+  <si>
+    <t>DEU24P00-10</t>
+  </si>
+  <si>
+    <t>Arthur Hoeld
+Chief Executive Officer PUMA</t>
+  </si>
+  <si>
+    <t>DEU25P00-15</t>
   </si>
 </sst>
 </file>
@@ -1089,156 +1106,156 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}" name="Tableau1" displayName="Tableau1" ref="A1:N20" totalsRowShown="0" headerRowDxfId="79" dataDxfId="78">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}" name="Tableau1" displayName="Tableau1" ref="A1:N20" totalsRowShown="0" headerRowDxfId="95" dataDxfId="94">
   <autoFilter ref="A1:N20" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N2">
     <sortCondition ref="A1:A2"/>
   </sortState>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{3EB1D0B3-009A-5A47-8B93-8EF6255B1304}" name="ID" dataDxfId="77"/>
-    <tableColumn id="2" xr3:uid="{DA8A41BF-F097-BC45-906C-4BABEC2244DD}" name="Text" dataDxfId="76"/>
-    <tableColumn id="3" xr3:uid="{2EF94B43-4C8E-044F-B78E-77B5B2C749ED}" name="Text_type" dataDxfId="75"/>
-    <tableColumn id="4" xr3:uid="{CCEEA6CD-C218-094D-9E25-C77D75EA7E8B}" name="Leadership_context" dataDxfId="74"/>
-    <tableColumn id="5" xr3:uid="{7597EAEA-F46D-374E-8954-A78718D8A002}" name="Information_valence" dataDxfId="73"/>
-    <tableColumn id="6" xr3:uid="{FAAD26A2-D031-3F47-A9AF-C78AE4508844}" name="Communication_type" dataDxfId="72"/>
-    <tableColumn id="14" xr3:uid="{DC551193-3E78-054D-9E02-55B526E3955D}" name="Source_type" dataDxfId="71"/>
-    <tableColumn id="7" xr3:uid="{0B866C2F-1672-9C45-8132-39C1E3DA8EAF}" name="Company" dataDxfId="70"/>
-    <tableColumn id="8" xr3:uid="{CC5E1A75-8194-974B-BC62-732998981044}" name="Country" dataDxfId="69"/>
-    <tableColumn id="9" xr3:uid="{3B4764F6-42C4-5740-9A0F-8733D2FFE2C1}" name="Year" dataDxfId="68"/>
-    <tableColumn id="10" xr3:uid="{DF6E8D3A-208E-A448-B107-E9C070DE225E}" name="Covid" dataDxfId="67"/>
-    <tableColumn id="13" xr3:uid="{CB3B9ED9-A903-D142-8C47-DBFE1BB21BB9}" name="Communicator_role" dataDxfId="66"/>
-    <tableColumn id="11" xr3:uid="{C327315D-BA1F-BF4E-979D-02C312D440C8}" name="Communicator_name" dataDxfId="65"/>
-    <tableColumn id="12" xr3:uid="{1977CE7B-3E0B-714D-8E54-438D9A354605}" name="Comment" dataDxfId="64"/>
+    <tableColumn id="1" xr3:uid="{3EB1D0B3-009A-5A47-8B93-8EF6255B1304}" name="ID" dataDxfId="93"/>
+    <tableColumn id="2" xr3:uid="{DA8A41BF-F097-BC45-906C-4BABEC2244DD}" name="Text" dataDxfId="92"/>
+    <tableColumn id="3" xr3:uid="{2EF94B43-4C8E-044F-B78E-77B5B2C749ED}" name="Text_type" dataDxfId="91"/>
+    <tableColumn id="4" xr3:uid="{CCEEA6CD-C218-094D-9E25-C77D75EA7E8B}" name="Leadership_context" dataDxfId="90"/>
+    <tableColumn id="5" xr3:uid="{7597EAEA-F46D-374E-8954-A78718D8A002}" name="Information_valence" dataDxfId="89"/>
+    <tableColumn id="6" xr3:uid="{FAAD26A2-D031-3F47-A9AF-C78AE4508844}" name="Communication_type" dataDxfId="88"/>
+    <tableColumn id="14" xr3:uid="{DC551193-3E78-054D-9E02-55B526E3955D}" name="Source_type" dataDxfId="87"/>
+    <tableColumn id="7" xr3:uid="{0B866C2F-1672-9C45-8132-39C1E3DA8EAF}" name="Company" dataDxfId="86"/>
+    <tableColumn id="8" xr3:uid="{CC5E1A75-8194-974B-BC62-732998981044}" name="Country" dataDxfId="85"/>
+    <tableColumn id="9" xr3:uid="{3B4764F6-42C4-5740-9A0F-8733D2FFE2C1}" name="Year" dataDxfId="84"/>
+    <tableColumn id="10" xr3:uid="{DF6E8D3A-208E-A448-B107-E9C070DE225E}" name="Covid" dataDxfId="83"/>
+    <tableColumn id="13" xr3:uid="{CB3B9ED9-A903-D142-8C47-DBFE1BB21BB9}" name="Communicator_role" dataDxfId="82"/>
+    <tableColumn id="11" xr3:uid="{C327315D-BA1F-BF4E-979D-02C312D440C8}" name="Communicator_name" dataDxfId="81"/>
+    <tableColumn id="12" xr3:uid="{1977CE7B-3E0B-714D-8E54-438D9A354605}" name="Comment" dataDxfId="80"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DA7F0E8F-45C6-6043-B094-E3D95B97FF2A}" name="Tableau13" displayName="Tableau13" ref="A1:N17" totalsRowShown="0" headerRowDxfId="63" dataDxfId="62">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DA7F0E8F-45C6-6043-B094-E3D95B97FF2A}" name="Tableau13" displayName="Tableau13" ref="A1:N17" totalsRowShown="0" headerRowDxfId="79" dataDxfId="78">
   <autoFilter ref="A1:N17" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N2">
     <sortCondition ref="A1:A2"/>
   </sortState>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{CEF716DC-F71C-F64A-9417-BFA8F7223C3C}" name="ID" dataDxfId="61"/>
-    <tableColumn id="2" xr3:uid="{E18EF473-8BB2-B249-A671-AEC1D227D58C}" name="Text" dataDxfId="60"/>
-    <tableColumn id="3" xr3:uid="{43ED120E-0AAC-5B48-BFFE-E2FEDCE871CC}" name="Text_type" dataDxfId="59"/>
-    <tableColumn id="4" xr3:uid="{C80CD8E5-01BF-A441-83A4-5AD3DB190355}" name="Leadership_context" dataDxfId="58"/>
-    <tableColumn id="5" xr3:uid="{923FAB0A-F1C7-8C4E-9079-3F151BDD8845}" name="Information_valence" dataDxfId="57"/>
-    <tableColumn id="6" xr3:uid="{68020A6C-474C-354D-9F87-DDFAD6E6FCBF}" name="Communication_type" dataDxfId="56"/>
-    <tableColumn id="13" xr3:uid="{DD700407-60FC-C348-A601-E8685620E07F}" name="Source_type" dataDxfId="55"/>
-    <tableColumn id="7" xr3:uid="{BE35D812-E006-C241-B735-D50938782E5F}" name="Company" dataDxfId="54"/>
-    <tableColumn id="8" xr3:uid="{D7B81200-66AC-0046-9542-315523411E25}" name="Country" dataDxfId="53"/>
-    <tableColumn id="9" xr3:uid="{79CD73A8-8993-8248-A866-07B7E35F6DCB}" name="Year" dataDxfId="52"/>
-    <tableColumn id="10" xr3:uid="{9CEEE324-6A65-1042-8C7C-96F54D0F2756}" name="Covid" dataDxfId="51"/>
-    <tableColumn id="14" xr3:uid="{18CC61B1-AC23-BA4F-B2B3-2D2FB5AC969E}" name="Communicator_role" dataDxfId="50"/>
-    <tableColumn id="11" xr3:uid="{64EE7B30-27FC-9945-8BF4-F74D9FF6D07C}" name="Communicator_name" dataDxfId="49"/>
-    <tableColumn id="12" xr3:uid="{5C43064B-4CDF-ED4E-B988-64FD2F0806AA}" name="Comment" dataDxfId="48"/>
+    <tableColumn id="1" xr3:uid="{CEF716DC-F71C-F64A-9417-BFA8F7223C3C}" name="ID" dataDxfId="77"/>
+    <tableColumn id="2" xr3:uid="{E18EF473-8BB2-B249-A671-AEC1D227D58C}" name="Text" dataDxfId="76"/>
+    <tableColumn id="3" xr3:uid="{43ED120E-0AAC-5B48-BFFE-E2FEDCE871CC}" name="Text_type" dataDxfId="75"/>
+    <tableColumn id="4" xr3:uid="{C80CD8E5-01BF-A441-83A4-5AD3DB190355}" name="Leadership_context" dataDxfId="74"/>
+    <tableColumn id="5" xr3:uid="{923FAB0A-F1C7-8C4E-9079-3F151BDD8845}" name="Information_valence" dataDxfId="73"/>
+    <tableColumn id="6" xr3:uid="{68020A6C-474C-354D-9F87-DDFAD6E6FCBF}" name="Communication_type" dataDxfId="72"/>
+    <tableColumn id="13" xr3:uid="{DD700407-60FC-C348-A601-E8685620E07F}" name="Source_type" dataDxfId="71"/>
+    <tableColumn id="7" xr3:uid="{BE35D812-E006-C241-B735-D50938782E5F}" name="Company" dataDxfId="70"/>
+    <tableColumn id="8" xr3:uid="{D7B81200-66AC-0046-9542-315523411E25}" name="Country" dataDxfId="69"/>
+    <tableColumn id="9" xr3:uid="{79CD73A8-8993-8248-A866-07B7E35F6DCB}" name="Year" dataDxfId="68"/>
+    <tableColumn id="10" xr3:uid="{9CEEE324-6A65-1042-8C7C-96F54D0F2756}" name="Covid" dataDxfId="67"/>
+    <tableColumn id="14" xr3:uid="{18CC61B1-AC23-BA4F-B2B3-2D2FB5AC969E}" name="Communicator_role" dataDxfId="66"/>
+    <tableColumn id="11" xr3:uid="{64EE7B30-27FC-9945-8BF4-F74D9FF6D07C}" name="Communicator_name" dataDxfId="65"/>
+    <tableColumn id="12" xr3:uid="{5C43064B-4CDF-ED4E-B988-64FD2F0806AA}" name="Comment" dataDxfId="64"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{C7C650FA-A8BE-374F-A02C-24C279A2D67A}" name="Tableau134" displayName="Tableau134" ref="A1:N21" totalsRowShown="0" headerRowDxfId="95" dataDxfId="94">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{C7C650FA-A8BE-374F-A02C-24C279A2D67A}" name="Tableau134" displayName="Tableau134" ref="A1:N21" totalsRowShown="0" headerRowDxfId="63" dataDxfId="62">
   <autoFilter ref="A1:N21" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N2">
     <sortCondition ref="A1:A2"/>
   </sortState>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{E398D18F-D9B1-8C4A-B81C-4F23A58404BA}" name="ID" dataDxfId="93"/>
-    <tableColumn id="2" xr3:uid="{41682781-F3C4-A842-B6E4-CD72DE688AF5}" name="Text" dataDxfId="92"/>
-    <tableColumn id="3" xr3:uid="{C1B517F2-40CD-8F40-9B4C-E34FFCCE3881}" name="Text_type" dataDxfId="91"/>
-    <tableColumn id="4" xr3:uid="{74E0C65C-5577-A146-9EE5-20C594C4316D}" name="Leadership_context" dataDxfId="90"/>
-    <tableColumn id="5" xr3:uid="{DDC33EC8-2DCC-DF43-9A08-EC991A2EA183}" name="Information_valence" dataDxfId="89"/>
-    <tableColumn id="6" xr3:uid="{C7BBAC6F-3D8E-B149-B9F0-D0A909FCC061}" name="Communication_type" dataDxfId="88"/>
-    <tableColumn id="14" xr3:uid="{DA857B5E-985B-B946-AB84-87E571EEF3AB}" name="Source_type" dataDxfId="87"/>
-    <tableColumn id="7" xr3:uid="{3FFDDD67-7E94-CE4D-B56E-DFAC9F1681E3}" name="Company" dataDxfId="86"/>
-    <tableColumn id="8" xr3:uid="{342E13F5-266B-7B42-BD6B-BB868EA49B97}" name="Country" dataDxfId="85"/>
-    <tableColumn id="9" xr3:uid="{69240109-8B46-AB43-AD07-1F40DB5F9C94}" name="Year" dataDxfId="84"/>
-    <tableColumn id="10" xr3:uid="{5ED27922-9168-D142-BBEF-32C7AE06ABD3}" name="Covid" dataDxfId="83"/>
-    <tableColumn id="13" xr3:uid="{0563ACCB-80F5-4F46-ADA0-9040F1D87085}" name="Communicator_role" dataDxfId="82"/>
-    <tableColumn id="11" xr3:uid="{C38872CB-C9B9-1249-9741-B341922B9857}" name="Communicator_name" dataDxfId="81"/>
-    <tableColumn id="12" xr3:uid="{DBF7903A-F082-FB40-B41C-987ABF6BC279}" name="Comment" dataDxfId="80"/>
+    <tableColumn id="1" xr3:uid="{E398D18F-D9B1-8C4A-B81C-4F23A58404BA}" name="ID" dataDxfId="61"/>
+    <tableColumn id="2" xr3:uid="{41682781-F3C4-A842-B6E4-CD72DE688AF5}" name="Text" dataDxfId="60"/>
+    <tableColumn id="3" xr3:uid="{C1B517F2-40CD-8F40-9B4C-E34FFCCE3881}" name="Text_type" dataDxfId="59"/>
+    <tableColumn id="4" xr3:uid="{74E0C65C-5577-A146-9EE5-20C594C4316D}" name="Leadership_context" dataDxfId="58"/>
+    <tableColumn id="5" xr3:uid="{DDC33EC8-2DCC-DF43-9A08-EC991A2EA183}" name="Information_valence" dataDxfId="57"/>
+    <tableColumn id="6" xr3:uid="{C7BBAC6F-3D8E-B149-B9F0-D0A909FCC061}" name="Communication_type" dataDxfId="56"/>
+    <tableColumn id="14" xr3:uid="{DA857B5E-985B-B946-AB84-87E571EEF3AB}" name="Source_type" dataDxfId="55"/>
+    <tableColumn id="7" xr3:uid="{3FFDDD67-7E94-CE4D-B56E-DFAC9F1681E3}" name="Company" dataDxfId="54"/>
+    <tableColumn id="8" xr3:uid="{342E13F5-266B-7B42-BD6B-BB868EA49B97}" name="Country" dataDxfId="53"/>
+    <tableColumn id="9" xr3:uid="{69240109-8B46-AB43-AD07-1F40DB5F9C94}" name="Year" dataDxfId="52"/>
+    <tableColumn id="10" xr3:uid="{5ED27922-9168-D142-BBEF-32C7AE06ABD3}" name="Covid" dataDxfId="51"/>
+    <tableColumn id="13" xr3:uid="{0563ACCB-80F5-4F46-ADA0-9040F1D87085}" name="Communicator_role" dataDxfId="50"/>
+    <tableColumn id="11" xr3:uid="{C38872CB-C9B9-1249-9741-B341922B9857}" name="Communicator_name" dataDxfId="49"/>
+    <tableColumn id="12" xr3:uid="{DBF7903A-F082-FB40-B41C-987ABF6BC279}" name="Comment" dataDxfId="48"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{49AA2418-AB03-1149-B07A-3CC5FF67C997}" name="Tableau1345" displayName="Tableau1345" ref="A1:N23" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14">
-  <autoFilter ref="A1:N23" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{49AA2418-AB03-1149-B07A-3CC5FF67C997}" name="Tableau1345" displayName="Tableau1345" ref="A1:N24" totalsRowShown="0" headerRowDxfId="47" dataDxfId="46">
+  <autoFilter ref="A1:N24" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N2">
     <sortCondition ref="A1:A2"/>
   </sortState>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{E88F34DD-82B0-AD49-8C17-D8E9CFF03D07}" name="ID" dataDxfId="13"/>
-    <tableColumn id="2" xr3:uid="{88FC91F1-83E8-1B40-AC59-24D584573CCF}" name="Text" dataDxfId="12"/>
-    <tableColumn id="3" xr3:uid="{15432912-C615-E748-A229-EAA1D750204D}" name="Text_type" dataDxfId="11"/>
-    <tableColumn id="4" xr3:uid="{1025B200-F152-0B42-88C1-A31B3C27DB9E}" name="Leadership_context" dataDxfId="10"/>
-    <tableColumn id="5" xr3:uid="{D41F3D09-61AB-B841-88C7-5242CDC613BF}" name="Information_valence" dataDxfId="9"/>
-    <tableColumn id="6" xr3:uid="{CE749A1F-4ED8-1C40-9BE6-FB737E09C230}" name="Communication_type" dataDxfId="8"/>
-    <tableColumn id="13" xr3:uid="{BDC21215-E7B5-5C4C-B5AB-80E86EA24E05}" name="Source_type" dataDxfId="7"/>
-    <tableColumn id="7" xr3:uid="{A6F61E0C-8D32-F54F-8B88-CFAABE31D5B0}" name="Company" dataDxfId="6"/>
-    <tableColumn id="8" xr3:uid="{84CFAC4D-579E-AA4B-9DFE-FB605F75FBA9}" name="Country" dataDxfId="5"/>
-    <tableColumn id="9" xr3:uid="{1BA4063C-1918-624B-9757-FC2F3E5A7EE2}" name="Year" dataDxfId="4"/>
-    <tableColumn id="10" xr3:uid="{82840B5F-FD1C-614B-9755-28207407D6E2}" name="Covid" dataDxfId="3"/>
-    <tableColumn id="14" xr3:uid="{3F460577-A4A9-C947-8FBE-832A71AF2E55}" name="Communicator_role" dataDxfId="2"/>
-    <tableColumn id="11" xr3:uid="{3C67D01C-1B28-EB45-A3B2-FA7774BA5A24}" name="Communicator_name" dataDxfId="1"/>
-    <tableColumn id="12" xr3:uid="{7581B405-4702-5B40-9BBE-C98F342B9125}" name="Comment" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{E88F34DD-82B0-AD49-8C17-D8E9CFF03D07}" name="ID" dataDxfId="45"/>
+    <tableColumn id="2" xr3:uid="{88FC91F1-83E8-1B40-AC59-24D584573CCF}" name="Text" dataDxfId="44"/>
+    <tableColumn id="3" xr3:uid="{15432912-C615-E748-A229-EAA1D750204D}" name="Text_type" dataDxfId="43"/>
+    <tableColumn id="4" xr3:uid="{1025B200-F152-0B42-88C1-A31B3C27DB9E}" name="Leadership_context" dataDxfId="42"/>
+    <tableColumn id="5" xr3:uid="{D41F3D09-61AB-B841-88C7-5242CDC613BF}" name="Information_valence" dataDxfId="41"/>
+    <tableColumn id="6" xr3:uid="{CE749A1F-4ED8-1C40-9BE6-FB737E09C230}" name="Communication_type" dataDxfId="40"/>
+    <tableColumn id="13" xr3:uid="{BDC21215-E7B5-5C4C-B5AB-80E86EA24E05}" name="Source_type" dataDxfId="39"/>
+    <tableColumn id="7" xr3:uid="{A6F61E0C-8D32-F54F-8B88-CFAABE31D5B0}" name="Company" dataDxfId="38"/>
+    <tableColumn id="8" xr3:uid="{84CFAC4D-579E-AA4B-9DFE-FB605F75FBA9}" name="Country" dataDxfId="37"/>
+    <tableColumn id="9" xr3:uid="{1BA4063C-1918-624B-9757-FC2F3E5A7EE2}" name="Year" dataDxfId="36"/>
+    <tableColumn id="10" xr3:uid="{82840B5F-FD1C-614B-9755-28207407D6E2}" name="Covid" dataDxfId="35"/>
+    <tableColumn id="14" xr3:uid="{3F460577-A4A9-C947-8FBE-832A71AF2E55}" name="Communicator_role" dataDxfId="34"/>
+    <tableColumn id="11" xr3:uid="{3C67D01C-1B28-EB45-A3B2-FA7774BA5A24}" name="Communicator_name" dataDxfId="33"/>
+    <tableColumn id="12" xr3:uid="{7581B405-4702-5B40-9BBE-C98F342B9125}" name="Comment" dataDxfId="32"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{3E6C7F84-1A88-2149-AAB1-B94EF8830151}" name="Tableau13456" displayName="Tableau13456" ref="A1:N11" totalsRowShown="0" headerRowDxfId="47" dataDxfId="46">
-  <autoFilter ref="A1:N11" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{3E6C7F84-1A88-2149-AAB1-B94EF8830151}" name="Tableau13456" displayName="Tableau13456" ref="A1:N12" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30">
+  <autoFilter ref="A1:N12" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N2">
     <sortCondition ref="A1:A2"/>
   </sortState>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{86F19330-6E72-0543-BBCC-6D193B41E96F}" name="ID" dataDxfId="45"/>
-    <tableColumn id="2" xr3:uid="{6C469BD5-B4CF-8D4F-A2F6-F0E834902E4A}" name="Text" dataDxfId="44"/>
-    <tableColumn id="3" xr3:uid="{FE673CA5-CBC5-A34F-8A0C-C1CD6D144617}" name="Text_type" dataDxfId="43"/>
-    <tableColumn id="4" xr3:uid="{4248AFAD-ABBE-A942-8BC5-6258F7CF5E07}" name="Leadership_context" dataDxfId="42"/>
-    <tableColumn id="5" xr3:uid="{9D393B8E-A5EB-6240-B5FD-D449006530E5}" name="Information_valence" dataDxfId="41"/>
-    <tableColumn id="6" xr3:uid="{9677B29B-2D61-544A-85E3-A9C0FF7FBFCF}" name="Communication_type" dataDxfId="40"/>
-    <tableColumn id="14" xr3:uid="{5175FC7C-275C-FB4E-8512-D7A2B81AEEA9}" name="Source_type" dataDxfId="39"/>
-    <tableColumn id="7" xr3:uid="{9949BF20-7E90-2D45-A547-C4EF102C2AF9}" name="Company" dataDxfId="38"/>
-    <tableColumn id="8" xr3:uid="{5676BCFB-C3B1-444F-8A31-FAE43C2412E4}" name="Country" dataDxfId="37"/>
-    <tableColumn id="9" xr3:uid="{065AECA5-A4C6-784E-B897-9C586B53EEC2}" name="Year" dataDxfId="36"/>
-    <tableColumn id="10" xr3:uid="{9FE554FC-C9E9-BD44-8CBB-7E5AF11D1DDA}" name="Covid" dataDxfId="35"/>
-    <tableColumn id="13" xr3:uid="{93285A16-1AFB-F940-A523-560D3B0D9284}" name="Communicator_role" dataDxfId="34"/>
-    <tableColumn id="11" xr3:uid="{3C88AB16-0597-6246-B1EA-CED5E74629EC}" name="Communicator_name" dataDxfId="33"/>
-    <tableColumn id="12" xr3:uid="{75A6A75A-B89A-C341-99C3-8E0AF84308E5}" name="Comment" dataDxfId="32"/>
+    <tableColumn id="1" xr3:uid="{86F19330-6E72-0543-BBCC-6D193B41E96F}" name="ID" dataDxfId="29"/>
+    <tableColumn id="2" xr3:uid="{6C469BD5-B4CF-8D4F-A2F6-F0E834902E4A}" name="Text" dataDxfId="28"/>
+    <tableColumn id="3" xr3:uid="{FE673CA5-CBC5-A34F-8A0C-C1CD6D144617}" name="Text_type" dataDxfId="27"/>
+    <tableColumn id="4" xr3:uid="{4248AFAD-ABBE-A942-8BC5-6258F7CF5E07}" name="Leadership_context" dataDxfId="26"/>
+    <tableColumn id="5" xr3:uid="{9D393B8E-A5EB-6240-B5FD-D449006530E5}" name="Information_valence" dataDxfId="25"/>
+    <tableColumn id="6" xr3:uid="{9677B29B-2D61-544A-85E3-A9C0FF7FBFCF}" name="Communication_type" dataDxfId="24"/>
+    <tableColumn id="14" xr3:uid="{5175FC7C-275C-FB4E-8512-D7A2B81AEEA9}" name="Source_type" dataDxfId="23"/>
+    <tableColumn id="7" xr3:uid="{9949BF20-7E90-2D45-A547-C4EF102C2AF9}" name="Company" dataDxfId="22"/>
+    <tableColumn id="8" xr3:uid="{5676BCFB-C3B1-444F-8A31-FAE43C2412E4}" name="Country" dataDxfId="21"/>
+    <tableColumn id="9" xr3:uid="{065AECA5-A4C6-784E-B897-9C586B53EEC2}" name="Year" dataDxfId="20"/>
+    <tableColumn id="10" xr3:uid="{9FE554FC-C9E9-BD44-8CBB-7E5AF11D1DDA}" name="Covid" dataDxfId="19"/>
+    <tableColumn id="13" xr3:uid="{93285A16-1AFB-F940-A523-560D3B0D9284}" name="Communicator_role" dataDxfId="18"/>
+    <tableColumn id="11" xr3:uid="{3C88AB16-0597-6246-B1EA-CED5E74629EC}" name="Communicator_name" dataDxfId="17"/>
+    <tableColumn id="12" xr3:uid="{75A6A75A-B89A-C341-99C3-8E0AF84308E5}" name="Comment" dataDxfId="16"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{4E11BC3F-0045-1646-B076-F2B520D6852E}" name="Tableau134567" displayName="Tableau134567" ref="A1:N16" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30">
-  <autoFilter ref="A1:N16" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{4E11BC3F-0045-1646-B076-F2B520D6852E}" name="Tableau134567" displayName="Tableau134567" ref="A1:N17" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14">
+  <autoFilter ref="A1:N17" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N2">
     <sortCondition ref="A1:A2"/>
   </sortState>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{31CE9BA4-76C4-7243-9CC4-2D69B48697C4}" name="ID" dataDxfId="29"/>
-    <tableColumn id="2" xr3:uid="{E9507622-53C7-7C46-AD19-75B0C284C739}" name="Text" dataDxfId="28"/>
-    <tableColumn id="3" xr3:uid="{B61A97EA-38E3-824E-AFFF-6DA5B0F5F799}" name="Text_type" dataDxfId="27"/>
-    <tableColumn id="4" xr3:uid="{C4A6AEE0-93C2-654B-AED8-9DFE0C336FBC}" name="Leadership_context" dataDxfId="26"/>
-    <tableColumn id="5" xr3:uid="{8B799C91-B83E-4740-8FF8-D018A500B838}" name="Information_valence" dataDxfId="25"/>
-    <tableColumn id="6" xr3:uid="{66E32C8C-3CF0-FF4A-8434-3DDE14801826}" name="Communication_type" dataDxfId="24"/>
-    <tableColumn id="13" xr3:uid="{0421BDDD-F24B-E84B-BE66-A9572A63BB7E}" name="Source_type" dataDxfId="23"/>
-    <tableColumn id="7" xr3:uid="{BB1E2451-7FCA-A546-B2ED-629286E517B1}" name="Company" dataDxfId="22"/>
-    <tableColumn id="8" xr3:uid="{A7D9EB9F-21C3-A443-AA66-25E92544A3D1}" name="Country" dataDxfId="21"/>
-    <tableColumn id="9" xr3:uid="{B9243626-106E-F940-9214-C16A4B219151}" name="Year" dataDxfId="20"/>
-    <tableColumn id="10" xr3:uid="{F1B3134A-8772-B940-A033-7567227076E7}" name="Covid" dataDxfId="19"/>
-    <tableColumn id="14" xr3:uid="{2561A683-C0E9-A44B-9AEB-9C3356F44833}" name="Communicator_role" dataDxfId="18"/>
-    <tableColumn id="11" xr3:uid="{AB9A4529-C11B-2A4B-9D39-3BBE9A62DD87}" name="Communicator_name" dataDxfId="17"/>
-    <tableColumn id="12" xr3:uid="{A2188241-51A1-7D40-927A-99ACD6E9501D}" name="Comment" dataDxfId="16"/>
+    <tableColumn id="1" xr3:uid="{31CE9BA4-76C4-7243-9CC4-2D69B48697C4}" name="ID" dataDxfId="13"/>
+    <tableColumn id="2" xr3:uid="{E9507622-53C7-7C46-AD19-75B0C284C739}" name="Text" dataDxfId="12"/>
+    <tableColumn id="3" xr3:uid="{B61A97EA-38E3-824E-AFFF-6DA5B0F5F799}" name="Text_type" dataDxfId="11"/>
+    <tableColumn id="4" xr3:uid="{C4A6AEE0-93C2-654B-AED8-9DFE0C336FBC}" name="Leadership_context" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{8B799C91-B83E-4740-8FF8-D018A500B838}" name="Information_valence" dataDxfId="9"/>
+    <tableColumn id="6" xr3:uid="{66E32C8C-3CF0-FF4A-8434-3DDE14801826}" name="Communication_type" dataDxfId="8"/>
+    <tableColumn id="13" xr3:uid="{0421BDDD-F24B-E84B-BE66-A9572A63BB7E}" name="Source_type" dataDxfId="7"/>
+    <tableColumn id="7" xr3:uid="{BB1E2451-7FCA-A546-B2ED-629286E517B1}" name="Company" dataDxfId="6"/>
+    <tableColumn id="8" xr3:uid="{A7D9EB9F-21C3-A443-AA66-25E92544A3D1}" name="Country" dataDxfId="5"/>
+    <tableColumn id="9" xr3:uid="{B9243626-106E-F940-9214-C16A4B219151}" name="Year" dataDxfId="4"/>
+    <tableColumn id="10" xr3:uid="{F1B3134A-8772-B940-A033-7567227076E7}" name="Covid" dataDxfId="3"/>
+    <tableColumn id="14" xr3:uid="{2561A683-C0E9-A44B-9AEB-9C3356F44833}" name="Communicator_role" dataDxfId="2"/>
+    <tableColumn id="11" xr3:uid="{AB9A4529-C11B-2A4B-9D39-3BBE9A62DD87}" name="Communicator_name" dataDxfId="1"/>
+    <tableColumn id="12" xr3:uid="{A2188241-51A1-7D40-927A-99ACD6E9501D}" name="Comment" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1631,7 +1648,7 @@
         <v>45</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>25</v>
@@ -1649,15 +1666,15 @@
         <v>10</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="34" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>47</v>
+        <v>209</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>27</v>
@@ -1666,7 +1683,7 @@
         <v>46</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>25</v>
@@ -1684,15 +1701,15 @@
         <v>10</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="34" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>48</v>
+        <v>210</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>28</v>
@@ -1701,7 +1718,7 @@
         <v>46</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>25</v>
@@ -1719,15 +1736,15 @@
         <v>10</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="68" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>49</v>
+        <v>211</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>29</v>
@@ -1736,7 +1753,7 @@
         <v>46</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>25</v>
@@ -1754,15 +1771,15 @@
         <v>10</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="68" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>50</v>
+        <v>212</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>30</v>
@@ -1771,7 +1788,7 @@
         <v>46</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>25</v>
@@ -1789,15 +1806,15 @@
         <v>10</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="34" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>51</v>
+        <v>213</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>31</v>
@@ -1806,7 +1823,7 @@
         <v>46</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>25</v>
@@ -1824,15 +1841,15 @@
         <v>10</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="153" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>52</v>
+        <v>214</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>32</v>
@@ -1841,7 +1858,7 @@
         <v>46</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>25</v>
@@ -1859,15 +1876,15 @@
         <v>10</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="119" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>53</v>
+        <v>215</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>33</v>
@@ -1876,7 +1893,7 @@
         <v>46</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>25</v>
@@ -1894,15 +1911,15 @@
         <v>10</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="119" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>54</v>
+        <v>216</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>34</v>
@@ -1911,7 +1928,7 @@
         <v>46</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>25</v>
@@ -1929,15 +1946,15 @@
         <v>10</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="170" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>55</v>
+        <v>217</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>35</v>
@@ -1946,7 +1963,7 @@
         <v>46</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>25</v>
@@ -1964,15 +1981,15 @@
         <v>10</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="119" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>56</v>
+        <v>218</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>36</v>
@@ -1981,7 +1998,7 @@
         <v>46</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>25</v>
@@ -1999,15 +2016,15 @@
         <v>10</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="170" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>57</v>
+        <v>219</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>37</v>
@@ -2016,7 +2033,7 @@
         <v>46</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>25</v>
@@ -2034,15 +2051,15 @@
         <v>10</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="34" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>58</v>
+        <v>220</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>38</v>
@@ -2051,7 +2068,7 @@
         <v>46</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>25</v>
@@ -2069,15 +2086,15 @@
         <v>10</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="204" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>59</v>
+        <v>221</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>39</v>
@@ -2086,7 +2103,7 @@
         <v>46</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>25</v>
@@ -2104,15 +2121,15 @@
         <v>10</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="119" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>60</v>
+        <v>222</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>40</v>
@@ -2121,7 +2138,7 @@
         <v>46</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>25</v>
@@ -2139,15 +2156,15 @@
         <v>10</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="136" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>61</v>
+        <v>223</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>41</v>
@@ -2156,7 +2173,7 @@
         <v>46</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>25</v>
@@ -2174,15 +2191,15 @@
         <v>10</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="102" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>62</v>
+        <v>224</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>42</v>
@@ -2191,7 +2208,7 @@
         <v>46</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>25</v>
@@ -2209,15 +2226,15 @@
         <v>10</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>63</v>
+        <v>225</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>43</v>
@@ -2226,7 +2243,7 @@
         <v>46</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>25</v>
@@ -2244,15 +2261,15 @@
         <v>10</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="51" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>64</v>
+        <v>226</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>44</v>
@@ -2261,7 +2278,7 @@
         <v>46</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>25</v>
@@ -2279,10 +2296,10 @@
         <v>10</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -2363,10 +2380,10 @@
         <v>26</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>25</v>
@@ -2384,24 +2401,24 @@
         <v>10</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>83</v>
+        <v>194</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>46</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>25</v>
@@ -2419,24 +2436,24 @@
         <v>10</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="153" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>84</v>
+        <v>195</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>46</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>25</v>
@@ -2454,24 +2471,24 @@
         <v>10</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>85</v>
+        <v>196</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>46</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>25</v>
@@ -2489,24 +2506,24 @@
         <v>10</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="153" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>86</v>
+        <v>197</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>46</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>25</v>
@@ -2524,24 +2541,24 @@
         <v>10</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>87</v>
+        <v>198</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>46</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>25</v>
@@ -2559,24 +2576,24 @@
         <v>10</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>88</v>
+        <v>199</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>46</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>25</v>
@@ -2594,24 +2611,24 @@
         <v>10</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="221" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>89</v>
+        <v>200</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>46</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>25</v>
@@ -2629,24 +2646,24 @@
         <v>10</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="68" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>90</v>
+        <v>201</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>46</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>25</v>
@@ -2664,24 +2681,24 @@
         <v>10</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="136" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>91</v>
+        <v>202</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>46</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>25</v>
@@ -2699,24 +2716,24 @@
         <v>10</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="34" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>92</v>
+        <v>203</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>46</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>25</v>
@@ -2734,24 +2751,24 @@
         <v>10</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="255" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>93</v>
+        <v>204</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>46</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>25</v>
@@ -2769,24 +2786,24 @@
         <v>10</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="221" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>94</v>
+        <v>205</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>46</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>25</v>
@@ -2804,24 +2821,24 @@
         <v>10</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="187" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>95</v>
+        <v>206</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>46</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>25</v>
@@ -2839,24 +2856,24 @@
         <v>10</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="34" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>96</v>
+        <v>207</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>46</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>25</v>
@@ -2874,24 +2891,24 @@
         <v>10</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="68" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>97</v>
+        <v>208</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>46</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>25</v>
@@ -2909,13 +2926,14 @@
         <v>10</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
@@ -2992,10 +3010,10 @@
         <v>26</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>25</v>
@@ -3013,24 +3031,24 @@
         <v>10</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>98</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>118</v>
+        <v>175</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>99</v>
+        <v>66</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>46</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>25</v>
@@ -3048,24 +3066,24 @@
         <v>10</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>98</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="85" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>119</v>
+        <v>176</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>100</v>
+        <v>67</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>46</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>25</v>
@@ -3083,24 +3101,24 @@
         <v>10</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>98</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="204" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>120</v>
+        <v>177</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>101</v>
+        <v>68</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>46</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>25</v>
@@ -3118,24 +3136,24 @@
         <v>10</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>98</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="68" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>121</v>
+        <v>178</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>102</v>
+        <v>69</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>46</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>25</v>
@@ -3153,24 +3171,24 @@
         <v>10</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>98</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="119" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>122</v>
+        <v>179</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>103</v>
+        <v>70</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>46</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>25</v>
@@ -3188,24 +3206,24 @@
         <v>10</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>98</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>123</v>
+        <v>180</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>46</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>25</v>
@@ -3223,24 +3241,24 @@
         <v>10</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>98</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="119" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>124</v>
+        <v>181</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>105</v>
+        <v>72</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>46</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>25</v>
@@ -3258,24 +3276,24 @@
         <v>10</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>98</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="68" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>125</v>
+        <v>182</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>106</v>
+        <v>73</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>46</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>25</v>
@@ -3293,24 +3311,24 @@
         <v>10</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>98</v>
+        <v>65</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="119" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>126</v>
+        <v>183</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>107</v>
+        <v>74</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>46</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>25</v>
@@ -3328,24 +3346,24 @@
         <v>10</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>98</v>
+        <v>65</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>127</v>
+        <v>184</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>108</v>
+        <v>75</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>46</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>25</v>
@@ -3363,24 +3381,24 @@
         <v>10</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>98</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>128</v>
+        <v>185</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>109</v>
+        <v>76</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>46</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>25</v>
@@ -3398,24 +3416,24 @@
         <v>10</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>98</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="68" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>129</v>
+        <v>186</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>110</v>
+        <v>77</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>46</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>25</v>
@@ -3433,24 +3451,24 @@
         <v>10</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>98</v>
+        <v>65</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="68" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>130</v>
+        <v>187</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>111</v>
+        <v>78</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>46</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>25</v>
@@ -3468,24 +3486,24 @@
         <v>10</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>98</v>
+        <v>65</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>131</v>
+        <v>188</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>112</v>
+        <v>79</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>46</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>25</v>
@@ -3503,24 +3521,24 @@
         <v>10</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>98</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="119" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>132</v>
+        <v>189</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>113</v>
+        <v>80</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>46</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>25</v>
@@ -3538,24 +3556,24 @@
         <v>10</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>98</v>
+        <v>65</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="34" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>133</v>
+        <v>190</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>114</v>
+        <v>81</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>46</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>25</v>
@@ -3573,24 +3591,24 @@
         <v>10</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>98</v>
+        <v>65</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="34" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>134</v>
+        <v>191</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>115</v>
+        <v>82</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>46</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>25</v>
@@ -3608,24 +3626,24 @@
         <v>10</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>98</v>
+        <v>65</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="34" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>135</v>
+        <v>192</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>116</v>
+        <v>83</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>46</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>25</v>
@@ -3643,24 +3661,24 @@
         <v>10</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>98</v>
+        <v>65</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="34" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>136</v>
+        <v>193</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>117</v>
+        <v>84</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>46</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>25</v>
@@ -3678,13 +3696,14 @@
         <v>10</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>98</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
@@ -3694,7 +3713,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C026E3D-BA89-8B46-8C08-84D4DE3BA69B}">
-  <dimension ref="A1:N23"/>
+  <dimension ref="A1:N24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
@@ -3761,10 +3780,10 @@
         <v>26</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>25</v>
@@ -3782,24 +3801,24 @@
         <v>10</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>98</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="153" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>206</v>
+        <v>154</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>185</v>
+        <v>110</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>46</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>25</v>
@@ -3811,30 +3830,30 @@
         <v>13</v>
       </c>
       <c r="J3" s="1">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>10</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>98</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="85" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>207</v>
+        <v>155</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>186</v>
+        <v>111</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>46</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>25</v>
@@ -3846,30 +3865,30 @@
         <v>13</v>
       </c>
       <c r="J4" s="1">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="K4" s="1" t="s">
         <v>10</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>98</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="119" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>208</v>
+        <v>156</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>187</v>
+        <v>112</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>46</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>25</v>
@@ -3881,30 +3900,30 @@
         <v>13</v>
       </c>
       <c r="J5" s="1">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>10</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>98</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="136" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>209</v>
+        <v>157</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>188</v>
+        <v>113</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>46</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>25</v>
@@ -3916,30 +3935,30 @@
         <v>13</v>
       </c>
       <c r="J6" s="1">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>10</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>98</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="136" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>210</v>
+        <v>158</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>189</v>
+        <v>114</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>46</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>25</v>
@@ -3951,30 +3970,30 @@
         <v>13</v>
       </c>
       <c r="J7" s="1">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="K7" s="1" t="s">
         <v>10</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>98</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="119" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>211</v>
+        <v>159</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>190</v>
+        <v>115</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>46</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>25</v>
@@ -3986,30 +4005,30 @@
         <v>13</v>
       </c>
       <c r="J8" s="1">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="K8" s="1" t="s">
         <v>10</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>98</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="136" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>212</v>
+        <v>160</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>191</v>
+        <v>116</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>46</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>25</v>
@@ -4021,30 +4040,30 @@
         <v>13</v>
       </c>
       <c r="J9" s="1">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>10</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>98</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="68" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>213</v>
+        <v>161</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>192</v>
+        <v>117</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>46</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>25</v>
@@ -4056,30 +4075,30 @@
         <v>13</v>
       </c>
       <c r="J10" s="1">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="K10" s="1" t="s">
         <v>10</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>98</v>
+        <v>65</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>214</v>
+        <v>162</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>193</v>
+        <v>118</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>46</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>25</v>
@@ -4091,30 +4110,30 @@
         <v>13</v>
       </c>
       <c r="J11" s="1">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="K11" s="1" t="s">
         <v>10</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>98</v>
+        <v>65</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="68" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>215</v>
+        <v>163</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>194</v>
+        <v>119</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>46</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>25</v>
@@ -4126,30 +4145,30 @@
         <v>13</v>
       </c>
       <c r="J12" s="1">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="K12" s="1" t="s">
         <v>10</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>98</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>216</v>
+        <v>164</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>195</v>
+        <v>120</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>46</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>25</v>
@@ -4161,30 +4180,30 @@
         <v>13</v>
       </c>
       <c r="J13" s="1">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="K13" s="1" t="s">
         <v>10</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>98</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="68" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>217</v>
+        <v>165</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>196</v>
+        <v>121</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>46</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>25</v>
@@ -4196,30 +4215,30 @@
         <v>13</v>
       </c>
       <c r="J14" s="1">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="K14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>98</v>
+        <v>65</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="68" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>218</v>
+        <v>166</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>197</v>
+        <v>122</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>46</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>25</v>
@@ -4231,30 +4250,30 @@
         <v>13</v>
       </c>
       <c r="J15" s="1">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="K15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>98</v>
+        <v>65</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>219</v>
+        <v>167</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>198</v>
+        <v>123</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>46</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>25</v>
@@ -4266,30 +4285,30 @@
         <v>13</v>
       </c>
       <c r="J16" s="1">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="K16" s="1" t="s">
         <v>10</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>98</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="51" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>220</v>
+        <v>168</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>199</v>
+        <v>124</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>46</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>25</v>
@@ -4301,30 +4320,30 @@
         <v>13</v>
       </c>
       <c r="J17" s="1">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="K17" s="1" t="s">
         <v>10</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>98</v>
+        <v>65</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="136" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>221</v>
+        <v>169</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>200</v>
+        <v>125</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>46</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>25</v>
@@ -4336,30 +4355,30 @@
         <v>13</v>
       </c>
       <c r="J18" s="1">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="K18" s="1" t="s">
         <v>10</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>98</v>
+        <v>65</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="119" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>222</v>
+        <v>170</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>201</v>
+        <v>126</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>46</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>25</v>
@@ -4371,30 +4390,30 @@
         <v>13</v>
       </c>
       <c r="J19" s="1">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="K19" s="1" t="s">
         <v>10</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>98</v>
+        <v>65</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="119" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>223</v>
+        <v>171</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>202</v>
+        <v>127</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>46</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>25</v>
@@ -4406,30 +4425,30 @@
         <v>13</v>
       </c>
       <c r="J20" s="1">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="K20" s="1" t="s">
         <v>10</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>98</v>
+        <v>65</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="119" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>224</v>
+        <v>172</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>203</v>
+        <v>128</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>46</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>25</v>
@@ -4441,30 +4460,30 @@
         <v>13</v>
       </c>
       <c r="J21" s="1">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="K21" s="1" t="s">
         <v>10</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>98</v>
+        <v>65</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="102" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>225</v>
+        <v>173</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>204</v>
+        <v>129</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>46</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="G22" s="1" t="s">
         <v>25</v>
@@ -4476,30 +4495,30 @@
         <v>13</v>
       </c>
       <c r="J22" s="1">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="K22" s="1" t="s">
         <v>10</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>98</v>
+        <v>65</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="85" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>226</v>
+        <v>174</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>205</v>
+        <v>130</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>46</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="G23" s="1" t="s">
         <v>25</v>
@@ -4511,19 +4530,55 @@
         <v>13</v>
       </c>
       <c r="J23" s="1">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="K23" s="1" t="s">
         <v>10</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>98</v>
+        <v>65</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="34" x14ac:dyDescent="0.2">
+      <c r="A24" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J24" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K24" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L24" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="M24" s="1" t="s">
+        <v>65</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
@@ -4533,7 +4588,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46F01D49-A94C-464D-86C0-23DAAD0A1777}">
-  <dimension ref="A1:N11"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
@@ -4603,7 +4658,7 @@
         <v>45</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>25</v>
@@ -4621,24 +4676,24 @@
         <v>19</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" ht="119" x14ac:dyDescent="0.2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>146</v>
+        <v>131</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>137</v>
+        <v>85</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>46</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>25</v>
@@ -4656,24 +4711,24 @@
         <v>19</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" ht="102" x14ac:dyDescent="0.2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="68" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>147</v>
+        <v>132</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>138</v>
+        <v>86</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>46</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>25</v>
@@ -4691,24 +4746,24 @@
         <v>19</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>98</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="85" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>139</v>
+        <v>87</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>46</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>25</v>
@@ -4726,24 +4781,24 @@
         <v>19</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" ht="85" x14ac:dyDescent="0.2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="68" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>149</v>
+        <v>134</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>140</v>
+        <v>88</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>46</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>25</v>
@@ -4761,24 +4816,24 @@
         <v>19</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>98</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>141</v>
+        <v>89</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>46</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>25</v>
@@ -4796,24 +4851,24 @@
         <v>19</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>98</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="170" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>151</v>
+        <v>136</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>142</v>
+        <v>90</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>46</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>25</v>
@@ -4831,24 +4886,24 @@
         <v>19</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>98</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="170" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>152</v>
+        <v>137</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>143</v>
+        <v>91</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>46</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>25</v>
@@ -4866,24 +4921,24 @@
         <v>19</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>98</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="119" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>153</v>
+        <v>138</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>144</v>
+        <v>92</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>46</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>25</v>
@@ -4901,24 +4956,24 @@
         <v>19</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>98</v>
+        <v>65</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="85" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>145</v>
+        <v>93</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>46</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>25</v>
@@ -4936,13 +4991,49 @@
         <v>19</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>98</v>
+        <v>65</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="34" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J12" s="1">
+        <v>2025</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>65</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
@@ -4952,7 +5043,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F043F7F6-3A06-0B46-BD8B-5A267CD4419E}">
-  <dimension ref="A1:N16"/>
+  <dimension ref="A1:N17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
@@ -5019,10 +5110,10 @@
         <v>26</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>25</v>
@@ -5040,24 +5131,24 @@
         <v>21</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" ht="85" x14ac:dyDescent="0.2">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>170</v>
+        <v>140</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>156</v>
+        <v>95</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>46</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>25</v>
@@ -5075,24 +5166,24 @@
         <v>21</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>155</v>
+        <v>94</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="34" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>171</v>
+        <v>141</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>157</v>
+        <v>96</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>46</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>25</v>
@@ -5110,24 +5201,24 @@
         <v>21</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" ht="68" x14ac:dyDescent="0.2">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>172</v>
+        <v>142</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>158</v>
+        <v>97</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>46</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>25</v>
@@ -5145,24 +5236,24 @@
         <v>21</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" ht="102" x14ac:dyDescent="0.2">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="68" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>173</v>
+        <v>143</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>159</v>
+        <v>98</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>46</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>25</v>
@@ -5180,24 +5271,24 @@
         <v>21</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>155</v>
+        <v>94</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>174</v>
+        <v>144</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>160</v>
+        <v>99</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>46</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>25</v>
@@ -5215,24 +5306,24 @@
         <v>21</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>155</v>
+        <v>94</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="68" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>175</v>
+        <v>145</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>161</v>
+        <v>100</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>46</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>25</v>
@@ -5250,24 +5341,24 @@
         <v>21</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>155</v>
+        <v>94</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="85" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>176</v>
+        <v>146</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>162</v>
+        <v>101</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>46</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>25</v>
@@ -5285,24 +5376,24 @@
         <v>21</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>155</v>
+        <v>94</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>177</v>
+        <v>147</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>163</v>
+        <v>102</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>46</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>25</v>
@@ -5320,24 +5411,24 @@
         <v>21</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" ht="85" x14ac:dyDescent="0.2">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>178</v>
+        <v>148</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>164</v>
+        <v>103</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>46</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>25</v>
@@ -5355,24 +5446,24 @@
         <v>21</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>155</v>
+        <v>94</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="136" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>179</v>
+        <v>149</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>165</v>
+        <v>104</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>46</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>25</v>
@@ -5390,24 +5481,24 @@
         <v>21</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>155</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="85" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>166</v>
+        <v>105</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>46</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>25</v>
@@ -5425,24 +5516,24 @@
         <v>21</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" ht="68" x14ac:dyDescent="0.2">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="34" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>181</v>
+        <v>151</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>167</v>
+        <v>106</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>46</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>25</v>
@@ -5460,24 +5551,24 @@
         <v>21</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" ht="68" x14ac:dyDescent="0.2">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="34" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>182</v>
+        <v>152</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>168</v>
+        <v>107</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>46</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>25</v>
@@ -5495,24 +5586,24 @@
         <v>21</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>155</v>
+        <v>94</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="34" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>183</v>
+        <v>153</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>169</v>
+        <v>108</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>46</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>25</v>
@@ -5530,13 +5621,49 @@
         <v>21</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>155</v>
+        <v>94</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="34" x14ac:dyDescent="0.2">
+      <c r="A17" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J17" s="1">
+        <v>2026</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L17" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="M17" s="1" t="s">
+        <v>94</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>

--- a/data/input/puma.xlsx
+++ b/data/input/puma.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11020"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Saowalak/Desktop/CEOCommunication/data/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1EC71AB-7B05-0F49-AE66-B4BEBF1638CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBE43DD4-3883-4C46-819C-C3B428421F21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="23780" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="16720" yWindow="600" windowWidth="21660" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1276" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1407" uniqueCount="251">
   <si>
     <t>ID</t>
   </si>
@@ -655,9 +655,6 @@
     <t>DEU25P00-00</t>
   </si>
   <si>
-    <t xml:space="preserve">False </t>
-  </si>
-  <si>
     <t>Arthur Hoeld</t>
   </si>
   <si>
@@ -755,7 +752,37 @@
     <t>Leadership_context_human</t>
   </si>
   <si>
-    <t>True</t>
+    <t>false</t>
+  </si>
+  <si>
+    <t>true</t>
+  </si>
+  <si>
+    <t>Salutation addressed to shareholders, although it contains no substantive information.</t>
+  </si>
+  <si>
+    <t>CHALL primary becuase it describes the disruption caused by store closures and the operational adaptation toward e-commerce, marketing, and logistics. MARKET is an alternative because channels and distribution are discussed;</t>
+  </si>
+  <si>
+    <t>Expresses appreciation for the supervisory board’s trust and support as an external governance stakeholder. The investments are context, not the primary communicative purpose.</t>
+  </si>
+  <si>
+    <t>CHALL primary because the passage focuses on COVID-related factory closures, supply-chain disruption, and production suspension. MARKET as an alternative because product supply is affected.</t>
+  </si>
+  <si>
+    <t>STAKE primary because it  focuses on equality, anti-discrimination, environmental sustainability, circularity, climate action, and social responsibility.</t>
+  </si>
+  <si>
+    <t>PERF primary because it reports realized product and commercial achievements. MARKET is an alternative because products and consumers are discussed, but achieved results dominate.</t>
+  </si>
+  <si>
+    <t>Closing goodwill and health message addressed to the PUMA audience, followed by the CEO signature. No substantive business context.</t>
+  </si>
+  <si>
+    <t>CEO signature. No substantive business context.</t>
+  </si>
+  <si>
+    <t>PERF is primary because the passage opens with realized 2020 business performance. MARKET is an alternative because consumer and sports-market trends are also discussed. CHALL is only background context.</t>
   </si>
 </sst>
 </file>
@@ -1123,6 +1150,8 @@
   <dimension ref="A1:P106"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
+    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="2" max="2" width="54" customWidth="1"/>
     <col min="3" max="3" width="10.83203125" customWidth="1"/>
     <col min="4" max="4" width="11.6640625" customWidth="1"/>
     <col min="5" max="5" width="25.33203125" customWidth="1"/>
@@ -1148,7 +1177,7 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E1" t="s">
         <v>3</v>
@@ -1201,7 +1230,7 @@
         <v>18</v>
       </c>
       <c r="E2" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="F2" t="s">
         <v>20</v>
@@ -1226,6 +1255,12 @@
       </c>
       <c r="M2" t="s">
         <v>25</v>
+      </c>
+      <c r="N2" t="s">
+        <v>242</v>
+      </c>
+      <c r="O2" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.2">
@@ -1268,6 +1303,9 @@
       <c r="M3" t="s">
         <v>25</v>
       </c>
+      <c r="O3" t="s">
+        <v>240</v>
+      </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
@@ -1309,6 +1347,9 @@
       <c r="M4" t="s">
         <v>25</v>
       </c>
+      <c r="O4" t="s">
+        <v>240</v>
+      </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
@@ -1350,6 +1391,9 @@
       <c r="M5" t="s">
         <v>25</v>
       </c>
+      <c r="O5" t="s">
+        <v>240</v>
+      </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
@@ -1391,6 +1435,9 @@
       <c r="M6" t="s">
         <v>25</v>
       </c>
+      <c r="O6" t="s">
+        <v>240</v>
+      </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
@@ -1406,7 +1453,7 @@
         <v>36</v>
       </c>
       <c r="E7" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="F7" t="s">
         <v>20</v>
@@ -1431,6 +1478,9 @@
       </c>
       <c r="M7" t="s">
         <v>25</v>
+      </c>
+      <c r="O7" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.2">
@@ -1473,6 +1523,9 @@
       <c r="M8" t="s">
         <v>25</v>
       </c>
+      <c r="O8" t="s">
+        <v>240</v>
+      </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
@@ -1485,10 +1538,10 @@
         <v>28</v>
       </c>
       <c r="D9" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="E9" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="F9" t="s">
         <v>20</v>
@@ -1513,6 +1566,9 @@
       </c>
       <c r="M9" t="s">
         <v>25</v>
+      </c>
+      <c r="O9" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.2">
@@ -1555,6 +1611,9 @@
       <c r="M10" t="s">
         <v>25</v>
       </c>
+      <c r="O10" t="s">
+        <v>240</v>
+      </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
@@ -1567,7 +1626,7 @@
         <v>28</v>
       </c>
       <c r="D11" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="E11" t="s">
         <v>19</v>
@@ -1595,6 +1654,9 @@
       </c>
       <c r="M11" t="s">
         <v>25</v>
+      </c>
+      <c r="O11" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.2">
@@ -1637,6 +1699,15 @@
       <c r="M12" t="s">
         <v>25</v>
       </c>
+      <c r="N12" t="s">
+        <v>243</v>
+      </c>
+      <c r="O12" t="s">
+        <v>241</v>
+      </c>
+      <c r="P12" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
@@ -1649,7 +1720,7 @@
         <v>28</v>
       </c>
       <c r="D13" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E13" t="s">
         <v>19</v>
@@ -1677,6 +1748,9 @@
       </c>
       <c r="M13" t="s">
         <v>25</v>
+      </c>
+      <c r="O13" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.2">
@@ -1719,6 +1793,12 @@
       <c r="M14" t="s">
         <v>25</v>
       </c>
+      <c r="N14" t="s">
+        <v>244</v>
+      </c>
+      <c r="O14" t="s">
+        <v>240</v>
+      </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
@@ -1760,6 +1840,9 @@
       <c r="M15" t="s">
         <v>25</v>
       </c>
+      <c r="O15" t="s">
+        <v>240</v>
+      </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
@@ -1801,8 +1884,11 @@
       <c r="M16" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O16" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>63</v>
       </c>
@@ -1813,10 +1899,10 @@
         <v>28</v>
       </c>
       <c r="D17" t="s">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="E17" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="F17" t="s">
         <v>20</v>
@@ -1842,8 +1928,17 @@
       <c r="M17" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N17" t="s">
+        <v>250</v>
+      </c>
+      <c r="O17" t="s">
+        <v>241</v>
+      </c>
+      <c r="P17" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>65</v>
       </c>
@@ -1883,8 +1978,11 @@
       <c r="M18" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O18" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>67</v>
       </c>
@@ -1924,8 +2022,11 @@
       <c r="M19" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O19" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>69</v>
       </c>
@@ -1965,8 +2066,14 @@
       <c r="M20" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N20" t="s">
+        <v>248</v>
+      </c>
+      <c r="O20" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>71</v>
       </c>
@@ -1980,7 +2087,7 @@
         <v>18</v>
       </c>
       <c r="E21" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="F21" t="s">
         <v>20</v>
@@ -2006,8 +2113,14 @@
       <c r="M21" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N21" t="s">
+        <v>242</v>
+      </c>
+      <c r="O21" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>72</v>
       </c>
@@ -2047,8 +2160,11 @@
       <c r="M22" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O22" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>74</v>
       </c>
@@ -2088,8 +2204,11 @@
       <c r="M23" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O23" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>76</v>
       </c>
@@ -2129,8 +2248,11 @@
       <c r="M24" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O24" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>78</v>
       </c>
@@ -2170,8 +2292,11 @@
       <c r="M25" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O25" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>80</v>
       </c>
@@ -2211,8 +2336,11 @@
       <c r="M26" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O26" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>82</v>
       </c>
@@ -2252,8 +2380,11 @@
       <c r="M27" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O27" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>84</v>
       </c>
@@ -2264,10 +2395,10 @@
         <v>28</v>
       </c>
       <c r="D28" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E28" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="F28" t="s">
         <v>20</v>
@@ -2293,8 +2424,17 @@
       <c r="M28" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N28" t="s">
+        <v>245</v>
+      </c>
+      <c r="O28" t="s">
+        <v>241</v>
+      </c>
+      <c r="P28" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>86</v>
       </c>
@@ -2334,8 +2474,11 @@
       <c r="M29" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O29" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>88</v>
       </c>
@@ -2375,8 +2518,11 @@
       <c r="M30" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O30" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>90</v>
       </c>
@@ -2416,8 +2562,11 @@
       <c r="M31" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O31" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>92</v>
       </c>
@@ -2457,8 +2606,11 @@
       <c r="M32" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O32" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>94</v>
       </c>
@@ -2469,7 +2621,7 @@
         <v>28</v>
       </c>
       <c r="D33" t="s">
-        <v>49</v>
+        <v>18</v>
       </c>
       <c r="E33" t="s">
         <v>19</v>
@@ -2498,8 +2650,14 @@
       <c r="M33" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N33" t="s">
+        <v>246</v>
+      </c>
+      <c r="O33" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>96</v>
       </c>
@@ -2539,8 +2697,11 @@
       <c r="M34" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O34" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>98</v>
       </c>
@@ -2551,10 +2712,10 @@
         <v>28</v>
       </c>
       <c r="D35" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="E35" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="F35" t="s">
         <v>20</v>
@@ -2580,8 +2741,11 @@
       <c r="M35" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O35" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>100</v>
       </c>
@@ -2592,7 +2756,7 @@
         <v>28</v>
       </c>
       <c r="D36" t="s">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="E36" t="s">
         <v>37</v>
@@ -2621,8 +2785,14 @@
       <c r="M36" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N36" t="s">
+        <v>248</v>
+      </c>
+      <c r="O36" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>102</v>
       </c>
@@ -2636,7 +2806,7 @@
         <v>18</v>
       </c>
       <c r="E37" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="F37" t="s">
         <v>20</v>
@@ -2662,8 +2832,14 @@
       <c r="M37" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N37" t="s">
+        <v>242</v>
+      </c>
+      <c r="O37" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>104</v>
       </c>
@@ -2703,8 +2879,11 @@
       <c r="M38" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O38" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>106</v>
       </c>
@@ -2744,8 +2923,11 @@
       <c r="M39" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O39" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>108</v>
       </c>
@@ -2785,8 +2967,11 @@
       <c r="M40" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O40" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>110</v>
       </c>
@@ -2826,8 +3011,11 @@
       <c r="M41" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O41" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>112</v>
       </c>
@@ -2867,8 +3055,11 @@
       <c r="M42" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O42" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>114</v>
       </c>
@@ -2908,8 +3099,11 @@
       <c r="M43" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O43" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>116</v>
       </c>
@@ -2949,8 +3143,11 @@
       <c r="M44" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O44" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>118</v>
       </c>
@@ -2990,8 +3187,11 @@
       <c r="M45" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O45" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>120</v>
       </c>
@@ -3031,8 +3231,11 @@
       <c r="M46" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O46" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>122</v>
       </c>
@@ -3072,8 +3275,17 @@
       <c r="M47" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N47" t="s">
+        <v>247</v>
+      </c>
+      <c r="O47" t="s">
+        <v>241</v>
+      </c>
+      <c r="P47" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>124</v>
       </c>
@@ -3113,8 +3325,11 @@
       <c r="M48" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O48" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>126</v>
       </c>
@@ -3128,7 +3343,7 @@
         <v>33</v>
       </c>
       <c r="E49" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="F49" t="s">
         <v>20</v>
@@ -3154,8 +3369,11 @@
       <c r="M49" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O49" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>128</v>
       </c>
@@ -3195,8 +3413,11 @@
       <c r="M50" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O50" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>130</v>
       </c>
@@ -3236,8 +3457,11 @@
       <c r="M51" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O51" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>132</v>
       </c>
@@ -3277,8 +3501,11 @@
       <c r="M52" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O52" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>134</v>
       </c>
@@ -3292,7 +3519,7 @@
         <v>36</v>
       </c>
       <c r="E53" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="F53" t="s">
         <v>20</v>
@@ -3318,8 +3545,11 @@
       <c r="M53" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O53" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>136</v>
       </c>
@@ -3359,8 +3589,11 @@
       <c r="M54" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O54" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>138</v>
       </c>
@@ -3374,7 +3607,7 @@
         <v>49</v>
       </c>
       <c r="E55" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="F55" t="s">
         <v>20</v>
@@ -3400,8 +3633,11 @@
       <c r="M55" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O55" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>140</v>
       </c>
@@ -3412,7 +3648,7 @@
         <v>28</v>
       </c>
       <c r="D56" t="s">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="E56" t="s">
         <v>37</v>
@@ -3441,8 +3677,14 @@
       <c r="M56" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N56" t="s">
+        <v>249</v>
+      </c>
+      <c r="O56" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>142</v>
       </c>
@@ -3456,7 +3698,7 @@
         <v>18</v>
       </c>
       <c r="E57" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="F57" t="s">
         <v>20</v>
@@ -3482,8 +3724,14 @@
       <c r="M57" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N57" t="s">
+        <v>242</v>
+      </c>
+      <c r="O57" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="58" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>143</v>
       </c>
@@ -3523,8 +3771,11 @@
       <c r="M58" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O58" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="59" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>145</v>
       </c>
@@ -3538,7 +3789,7 @@
         <v>36</v>
       </c>
       <c r="E59" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="F59" t="s">
         <v>20</v>
@@ -3564,8 +3815,11 @@
       <c r="M59" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O59" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="60" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>147</v>
       </c>
@@ -3579,7 +3833,7 @@
         <v>36</v>
       </c>
       <c r="E60" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="F60" t="s">
         <v>20</v>
@@ -3605,8 +3859,14 @@
       <c r="M60" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O60" t="s">
+        <v>241</v>
+      </c>
+      <c r="P60" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>149</v>
       </c>
@@ -3620,7 +3880,7 @@
         <v>36</v>
       </c>
       <c r="E61" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="F61" t="s">
         <v>20</v>
@@ -3646,8 +3906,14 @@
       <c r="M61" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O61" t="s">
+        <v>241</v>
+      </c>
+      <c r="P61" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="62" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>151</v>
       </c>
@@ -3658,10 +3924,10 @@
         <v>28</v>
       </c>
       <c r="D62" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E62" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="F62" t="s">
         <v>20</v>
@@ -3687,8 +3953,11 @@
       <c r="M62" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O62" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="63" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>153</v>
       </c>
@@ -3728,8 +3997,11 @@
       <c r="M63" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O63" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="64" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>155</v>
       </c>
@@ -3769,8 +4041,11 @@
       <c r="M64" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O64" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>157</v>
       </c>
@@ -3810,8 +4085,11 @@
       <c r="M65" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O65" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>159</v>
       </c>
@@ -3851,8 +4129,11 @@
       <c r="M66" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O66" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>161</v>
       </c>
@@ -3892,8 +4173,11 @@
       <c r="M67" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O67" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="68" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>163</v>
       </c>
@@ -3904,10 +4188,10 @@
         <v>28</v>
       </c>
       <c r="D68" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E68" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="F68" t="s">
         <v>20</v>
@@ -3933,8 +4217,11 @@
       <c r="M68" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O68" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>165</v>
       </c>
@@ -3948,7 +4235,7 @@
         <v>36</v>
       </c>
       <c r="E69" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="F69" t="s">
         <v>20</v>
@@ -3974,8 +4261,11 @@
       <c r="M69" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O69" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="70" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>167</v>
       </c>
@@ -3986,7 +4276,7 @@
         <v>28</v>
       </c>
       <c r="D70" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E70" t="s">
         <v>19</v>
@@ -4015,8 +4305,11 @@
       <c r="M70" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O70" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="71" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>169</v>
       </c>
@@ -4056,8 +4349,11 @@
       <c r="M71" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O71" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="72" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>171</v>
       </c>
@@ -4097,8 +4393,11 @@
       <c r="M72" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O72" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="73" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>173</v>
       </c>
@@ -4138,8 +4437,11 @@
       <c r="M73" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O73" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="74" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>175</v>
       </c>
@@ -4179,8 +4481,11 @@
       <c r="M74" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O74" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="75" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>177</v>
       </c>
@@ -4220,8 +4525,11 @@
       <c r="M75" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O75" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="76" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>179</v>
       </c>
@@ -4261,8 +4569,11 @@
       <c r="M76" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O76" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="77" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>181</v>
       </c>
@@ -4302,8 +4613,11 @@
       <c r="M77" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O77" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="78" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>183</v>
       </c>
@@ -4343,8 +4657,11 @@
       <c r="M78" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O78" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="79" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>185</v>
       </c>
@@ -4355,7 +4672,7 @@
         <v>28</v>
       </c>
       <c r="D79" t="s">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="E79" t="s">
         <v>37</v>
@@ -4384,8 +4701,14 @@
       <c r="M79" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N79" t="s">
+        <v>249</v>
+      </c>
+      <c r="O79" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="80" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>187</v>
       </c>
@@ -4399,7 +4722,7 @@
         <v>18</v>
       </c>
       <c r="E80" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="F80" t="s">
         <v>20</v>
@@ -4417,7 +4740,7 @@
         <v>2024</v>
       </c>
       <c r="K80" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="L80" t="s">
         <v>24</v>
@@ -4425,8 +4748,14 @@
       <c r="M80" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N80" t="s">
+        <v>242</v>
+      </c>
+      <c r="O80" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="81" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>188</v>
       </c>
@@ -4458,7 +4787,7 @@
         <v>2024</v>
       </c>
       <c r="K81" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="L81" t="s">
         <v>24</v>
@@ -4466,8 +4795,11 @@
       <c r="M81" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O81" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="82" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>190</v>
       </c>
@@ -4499,7 +4831,7 @@
         <v>2024</v>
       </c>
       <c r="K82" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="L82" t="s">
         <v>24</v>
@@ -4507,8 +4839,11 @@
       <c r="M82" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O82" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="83" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>192</v>
       </c>
@@ -4519,7 +4854,7 @@
         <v>28</v>
       </c>
       <c r="D83" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E83" t="s">
         <v>19</v>
@@ -4540,7 +4875,7 @@
         <v>2024</v>
       </c>
       <c r="K83" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="L83" t="s">
         <v>24</v>
@@ -4548,8 +4883,14 @@
       <c r="M83" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O83" t="s">
+        <v>241</v>
+      </c>
+      <c r="P83" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="84" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>194</v>
       </c>
@@ -4581,7 +4922,7 @@
         <v>2024</v>
       </c>
       <c r="K84" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="L84" t="s">
         <v>24</v>
@@ -4589,8 +4930,11 @@
       <c r="M84" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O84" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="85" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>196</v>
       </c>
@@ -4622,7 +4966,7 @@
         <v>2024</v>
       </c>
       <c r="K85" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="L85" t="s">
         <v>24</v>
@@ -4630,8 +4974,11 @@
       <c r="M85" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O85" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="86" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>198</v>
       </c>
@@ -4642,7 +4989,7 @@
         <v>28</v>
       </c>
       <c r="D86" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E86" t="s">
         <v>19</v>
@@ -4663,7 +5010,7 @@
         <v>2024</v>
       </c>
       <c r="K86" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="L86" t="s">
         <v>24</v>
@@ -4671,8 +5018,11 @@
       <c r="M86" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O86" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="87" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>200</v>
       </c>
@@ -4704,7 +5054,7 @@
         <v>2024</v>
       </c>
       <c r="K87" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="L87" t="s">
         <v>24</v>
@@ -4712,8 +5062,11 @@
       <c r="M87" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O87" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="88" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>202</v>
       </c>
@@ -4745,7 +5098,7 @@
         <v>2024</v>
       </c>
       <c r="K88" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="L88" t="s">
         <v>24</v>
@@ -4753,8 +5106,11 @@
       <c r="M88" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O88" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="89" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>204</v>
       </c>
@@ -4786,7 +5142,7 @@
         <v>2024</v>
       </c>
       <c r="K89" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="L89" t="s">
         <v>24</v>
@@ -4794,8 +5150,11 @@
       <c r="M89" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O89" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="90" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>206</v>
       </c>
@@ -4806,7 +5165,7 @@
         <v>28</v>
       </c>
       <c r="D90" t="s">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="E90" t="s">
         <v>37</v>
@@ -4827,7 +5186,7 @@
         <v>2025</v>
       </c>
       <c r="K90" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="L90" t="s">
         <v>24</v>
@@ -4835,8 +5194,14 @@
       <c r="M90" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N90" t="s">
+        <v>249</v>
+      </c>
+      <c r="O90" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="91" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>207</v>
       </c>
@@ -4850,7 +5215,7 @@
         <v>18</v>
       </c>
       <c r="E91" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="F91" t="s">
         <v>20</v>
@@ -4868,21 +5233,27 @@
         <v>2025</v>
       </c>
       <c r="K91" t="s">
+        <v>240</v>
+      </c>
+      <c r="L91" t="s">
+        <v>24</v>
+      </c>
+      <c r="M91" t="s">
         <v>208</v>
       </c>
-      <c r="L91" t="s">
-        <v>24</v>
-      </c>
-      <c r="M91" t="s">
+      <c r="N91" t="s">
+        <v>242</v>
+      </c>
+      <c r="O91" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="92" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A92" t="s">
         <v>209</v>
       </c>
-    </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A92" t="s">
+      <c r="B92" t="s">
         <v>210</v>
-      </c>
-      <c r="B92" t="s">
-        <v>211</v>
       </c>
       <c r="C92" t="s">
         <v>28</v>
@@ -4909,21 +5280,24 @@
         <v>2025</v>
       </c>
       <c r="K92" t="s">
+        <v>240</v>
+      </c>
+      <c r="L92" t="s">
+        <v>24</v>
+      </c>
+      <c r="M92" t="s">
         <v>208</v>
       </c>
-      <c r="L92" t="s">
-        <v>24</v>
-      </c>
-      <c r="M92" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O92" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="93" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
+        <v>211</v>
+      </c>
+      <c r="B93" t="s">
         <v>212</v>
-      </c>
-      <c r="B93" t="s">
-        <v>213</v>
       </c>
       <c r="C93" t="s">
         <v>28</v>
@@ -4950,21 +5324,24 @@
         <v>2025</v>
       </c>
       <c r="K93" t="s">
+        <v>240</v>
+      </c>
+      <c r="L93" t="s">
+        <v>24</v>
+      </c>
+      <c r="M93" t="s">
         <v>208</v>
       </c>
-      <c r="L93" t="s">
-        <v>24</v>
-      </c>
-      <c r="M93" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O93" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="94" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
+        <v>213</v>
+      </c>
+      <c r="B94" t="s">
         <v>214</v>
-      </c>
-      <c r="B94" t="s">
-        <v>215</v>
       </c>
       <c r="C94" t="s">
         <v>28</v>
@@ -4991,21 +5368,24 @@
         <v>2025</v>
       </c>
       <c r="K94" t="s">
+        <v>240</v>
+      </c>
+      <c r="L94" t="s">
+        <v>24</v>
+      </c>
+      <c r="M94" t="s">
         <v>208</v>
       </c>
-      <c r="L94" t="s">
-        <v>24</v>
-      </c>
-      <c r="M94" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O94" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="95" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
+        <v>215</v>
+      </c>
+      <c r="B95" t="s">
         <v>216</v>
-      </c>
-      <c r="B95" t="s">
-        <v>217</v>
       </c>
       <c r="C95" t="s">
         <v>28</v>
@@ -5032,21 +5412,24 @@
         <v>2025</v>
       </c>
       <c r="K95" t="s">
+        <v>240</v>
+      </c>
+      <c r="L95" t="s">
+        <v>24</v>
+      </c>
+      <c r="M95" t="s">
         <v>208</v>
       </c>
-      <c r="L95" t="s">
-        <v>24</v>
-      </c>
-      <c r="M95" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O95" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="96" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
+        <v>217</v>
+      </c>
+      <c r="B96" t="s">
         <v>218</v>
-      </c>
-      <c r="B96" t="s">
-        <v>219</v>
       </c>
       <c r="C96" t="s">
         <v>28</v>
@@ -5073,21 +5456,24 @@
         <v>2025</v>
       </c>
       <c r="K96" t="s">
+        <v>240</v>
+      </c>
+      <c r="L96" t="s">
+        <v>24</v>
+      </c>
+      <c r="M96" t="s">
         <v>208</v>
       </c>
-      <c r="L96" t="s">
-        <v>24</v>
-      </c>
-      <c r="M96" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O96" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="97" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
+        <v>219</v>
+      </c>
+      <c r="B97" t="s">
         <v>220</v>
-      </c>
-      <c r="B97" t="s">
-        <v>221</v>
       </c>
       <c r="C97" t="s">
         <v>28</v>
@@ -5114,21 +5500,24 @@
         <v>2025</v>
       </c>
       <c r="K97" t="s">
+        <v>240</v>
+      </c>
+      <c r="L97" t="s">
+        <v>24</v>
+      </c>
+      <c r="M97" t="s">
         <v>208</v>
       </c>
-      <c r="L97" t="s">
-        <v>24</v>
-      </c>
-      <c r="M97" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O97" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="98" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
+        <v>221</v>
+      </c>
+      <c r="B98" t="s">
         <v>222</v>
-      </c>
-      <c r="B98" t="s">
-        <v>223</v>
       </c>
       <c r="C98" t="s">
         <v>28</v>
@@ -5137,7 +5526,7 @@
         <v>36</v>
       </c>
       <c r="E98" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="F98" t="s">
         <v>20</v>
@@ -5155,21 +5544,24 @@
         <v>2025</v>
       </c>
       <c r="K98" t="s">
+        <v>240</v>
+      </c>
+      <c r="L98" t="s">
+        <v>24</v>
+      </c>
+      <c r="M98" t="s">
         <v>208</v>
       </c>
-      <c r="L98" t="s">
-        <v>24</v>
-      </c>
-      <c r="M98" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O98" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="99" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
+        <v>223</v>
+      </c>
+      <c r="B99" t="s">
         <v>224</v>
-      </c>
-      <c r="B99" t="s">
-        <v>225</v>
       </c>
       <c r="C99" t="s">
         <v>28</v>
@@ -5178,7 +5570,7 @@
         <v>36</v>
       </c>
       <c r="E99" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="F99" t="s">
         <v>20</v>
@@ -5196,21 +5588,24 @@
         <v>2025</v>
       </c>
       <c r="K99" t="s">
+        <v>240</v>
+      </c>
+      <c r="L99" t="s">
+        <v>24</v>
+      </c>
+      <c r="M99" t="s">
         <v>208</v>
       </c>
-      <c r="L99" t="s">
-        <v>24</v>
-      </c>
-      <c r="M99" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O99" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="100" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
+        <v>225</v>
+      </c>
+      <c r="B100" t="s">
         <v>226</v>
-      </c>
-      <c r="B100" t="s">
-        <v>227</v>
       </c>
       <c r="C100" t="s">
         <v>28</v>
@@ -5219,7 +5614,7 @@
         <v>36</v>
       </c>
       <c r="E100" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="F100" t="s">
         <v>20</v>
@@ -5237,21 +5632,27 @@
         <v>2025</v>
       </c>
       <c r="K100" t="s">
+        <v>240</v>
+      </c>
+      <c r="L100" t="s">
+        <v>24</v>
+      </c>
+      <c r="M100" t="s">
         <v>208</v>
       </c>
-      <c r="L100" t="s">
-        <v>24</v>
-      </c>
-      <c r="M100" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O100" t="s">
+        <v>241</v>
+      </c>
+      <c r="P100" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="101" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
+        <v>227</v>
+      </c>
+      <c r="B101" t="s">
         <v>228</v>
-      </c>
-      <c r="B101" t="s">
-        <v>229</v>
       </c>
       <c r="C101" t="s">
         <v>28</v>
@@ -5260,7 +5661,7 @@
         <v>36</v>
       </c>
       <c r="E101" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="F101" t="s">
         <v>20</v>
@@ -5278,21 +5679,24 @@
         <v>2025</v>
       </c>
       <c r="K101" t="s">
+        <v>240</v>
+      </c>
+      <c r="L101" t="s">
+        <v>24</v>
+      </c>
+      <c r="M101" t="s">
         <v>208</v>
       </c>
-      <c r="L101" t="s">
-        <v>24</v>
-      </c>
-      <c r="M101" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O101" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="102" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
+        <v>229</v>
+      </c>
+      <c r="B102" t="s">
         <v>230</v>
-      </c>
-      <c r="B102" t="s">
-        <v>231</v>
       </c>
       <c r="C102" t="s">
         <v>28</v>
@@ -5319,21 +5723,24 @@
         <v>2025</v>
       </c>
       <c r="K102" t="s">
+        <v>240</v>
+      </c>
+      <c r="L102" t="s">
+        <v>24</v>
+      </c>
+      <c r="M102" t="s">
         <v>208</v>
       </c>
-      <c r="L102" t="s">
-        <v>24</v>
-      </c>
-      <c r="M102" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O102" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="103" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
+        <v>231</v>
+      </c>
+      <c r="B103" t="s">
         <v>232</v>
-      </c>
-      <c r="B103" t="s">
-        <v>233</v>
       </c>
       <c r="C103" t="s">
         <v>28</v>
@@ -5360,21 +5767,24 @@
         <v>2025</v>
       </c>
       <c r="K103" t="s">
+        <v>240</v>
+      </c>
+      <c r="L103" t="s">
+        <v>24</v>
+      </c>
+      <c r="M103" t="s">
         <v>208</v>
       </c>
-      <c r="L103" t="s">
-        <v>24</v>
-      </c>
-      <c r="M103" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="104" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O103" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="104" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
+        <v>233</v>
+      </c>
+      <c r="B104" t="s">
         <v>234</v>
-      </c>
-      <c r="B104" t="s">
-        <v>235</v>
       </c>
       <c r="C104" t="s">
         <v>28</v>
@@ -5401,21 +5811,24 @@
         <v>2025</v>
       </c>
       <c r="K104" t="s">
+        <v>240</v>
+      </c>
+      <c r="L104" t="s">
+        <v>24</v>
+      </c>
+      <c r="M104" t="s">
         <v>208</v>
       </c>
-      <c r="L104" t="s">
-        <v>24</v>
-      </c>
-      <c r="M104" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="105" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O104" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="105" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
+        <v>235</v>
+      </c>
+      <c r="B105" t="s">
         <v>236</v>
-      </c>
-      <c r="B105" t="s">
-        <v>237</v>
       </c>
       <c r="C105" t="s">
         <v>28</v>
@@ -5442,27 +5855,30 @@
         <v>2025</v>
       </c>
       <c r="K105" t="s">
+        <v>240</v>
+      </c>
+      <c r="L105" t="s">
+        <v>24</v>
+      </c>
+      <c r="M105" t="s">
         <v>208</v>
       </c>
-      <c r="L105" t="s">
-        <v>24</v>
-      </c>
-      <c r="M105" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="106" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O105" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="106" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
+        <v>237</v>
+      </c>
+      <c r="B106" t="s">
         <v>238</v>
       </c>
-      <c r="B106" t="s">
-        <v>239</v>
-      </c>
       <c r="C106" t="s">
         <v>28</v>
       </c>
       <c r="D106" t="s">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="E106" t="s">
         <v>37</v>
@@ -5483,13 +5899,19 @@
         <v>2025</v>
       </c>
       <c r="K106" t="s">
+        <v>240</v>
+      </c>
+      <c r="L106" t="s">
+        <v>24</v>
+      </c>
+      <c r="M106" t="s">
         <v>208</v>
       </c>
-      <c r="L106" t="s">
-        <v>24</v>
-      </c>
-      <c r="M106" t="s">
-        <v>209</v>
+      <c r="N106" t="s">
+        <v>249</v>
+      </c>
+      <c r="O106" t="s">
+        <v>240</v>
       </c>
     </row>
   </sheetData>

--- a/data/input/puma.xlsx
+++ b/data/input/puma.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Saowalak/Desktop/CEOCommunication/data/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBE43DD4-3883-4C46-819C-C3B428421F21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6838BB07-43FA-EF4D-A0D7-00635D98BA43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="16720" yWindow="600" windowWidth="21660" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,9 +31,6 @@
     <t>Text_type</t>
   </si>
   <si>
-    <t>Information_valence_human</t>
-  </si>
-  <si>
     <t>Communication_type</t>
   </si>
   <si>
@@ -749,9 +746,6 @@
 Chief Executive Officer PUMA</t>
   </si>
   <si>
-    <t>Leadership_context_human</t>
-  </si>
-  <si>
     <t>false</t>
   </si>
   <si>
@@ -783,6 +777,12 @@
   </si>
   <si>
     <t>PERF is primary because the passage opens with realized 2020 business performance. MARKET is an alternative because consumer and sports-market trends are also discussed. CHALL is only background context.</t>
+  </si>
+  <si>
+    <t>Leadership_context</t>
+  </si>
+  <si>
+    <t>Information_valence</t>
   </si>
 </sst>
 </file>
@@ -844,8 +844,8 @@
     <tableColumn id="1" xr3:uid="{E8A8D83A-A86A-A94B-AFEE-08514B4230E0}" name="ID"/>
     <tableColumn id="2" xr3:uid="{A9F908E3-1D86-A949-90D7-505471164303}" name="Text"/>
     <tableColumn id="3" xr3:uid="{DE3C30CF-F4CF-4440-91CD-FCEF94F5B1FB}" name="Text_type"/>
-    <tableColumn id="4" xr3:uid="{402C0041-0966-5A49-A2DB-CBB74E82038D}" name="Leadership_context_human"/>
-    <tableColumn id="5" xr3:uid="{517AAA0B-9C91-FD40-BA0A-1CEF8B3AAE8B}" name="Information_valence_human"/>
+    <tableColumn id="4" xr3:uid="{402C0041-0966-5A49-A2DB-CBB74E82038D}" name="Leadership_context"/>
+    <tableColumn id="5" xr3:uid="{517AAA0B-9C91-FD40-BA0A-1CEF8B3AAE8B}" name="Information_valence"/>
     <tableColumn id="6" xr3:uid="{BEE5708F-A7D2-594B-A49A-DBED66F6F482}" name="Communication_type"/>
     <tableColumn id="7" xr3:uid="{990E5E31-7B3D-A14F-8BC4-56DF19ECE005}" name="Source_type"/>
     <tableColumn id="8" xr3:uid="{51A3B052-3A3B-C345-8FC3-A957D13211D3}" name="Company"/>
@@ -1177,4741 +1177,4741 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="E1" t="s">
+        <v>250</v>
+      </c>
+      <c r="F1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>6</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>7</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>9</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>10</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>11</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>12</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>13</v>
-      </c>
-      <c r="P1" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
         <v>15</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>16</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>17</v>
       </c>
-      <c r="D2" t="s">
-        <v>18</v>
-      </c>
       <c r="E2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J2">
         <v>2020</v>
       </c>
       <c r="K2" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M2" t="s">
         <v>24</v>
       </c>
-      <c r="M2" t="s">
-        <v>25</v>
-      </c>
       <c r="N2" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="O2" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" t="s">
         <v>26</v>
       </c>
-      <c r="B3" t="s">
-        <v>27</v>
-      </c>
       <c r="C3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" t="s">
         <v>28</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>29</v>
       </c>
-      <c r="E3" t="s">
-        <v>30</v>
-      </c>
       <c r="F3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J3">
         <v>2020</v>
       </c>
       <c r="K3" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M3" t="s">
         <v>24</v>
       </c>
-      <c r="M3" t="s">
-        <v>25</v>
-      </c>
       <c r="O3" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" t="s">
         <v>31</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" t="s">
         <v>32</v>
       </c>
-      <c r="C4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D4" t="s">
-        <v>33</v>
-      </c>
       <c r="E4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J4">
         <v>2020</v>
       </c>
       <c r="K4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L4" t="s">
+        <v>23</v>
+      </c>
+      <c r="M4" t="s">
         <v>24</v>
       </c>
-      <c r="M4" t="s">
-        <v>25</v>
-      </c>
       <c r="O4" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5" t="s">
         <v>34</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" t="s">
         <v>35</v>
       </c>
-      <c r="C5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>36</v>
       </c>
-      <c r="E5" t="s">
-        <v>37</v>
-      </c>
       <c r="F5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J5">
         <v>2020</v>
       </c>
       <c r="K5" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L5" t="s">
+        <v>23</v>
+      </c>
+      <c r="M5" t="s">
         <v>24</v>
       </c>
-      <c r="M5" t="s">
-        <v>25</v>
-      </c>
       <c r="O5" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B6" t="s">
         <v>38</v>
       </c>
-      <c r="B6" t="s">
-        <v>39</v>
-      </c>
       <c r="C6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" t="s">
         <v>28</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>29</v>
       </c>
-      <c r="E6" t="s">
-        <v>30</v>
-      </c>
       <c r="F6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J6">
         <v>2020</v>
       </c>
       <c r="K6" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L6" t="s">
+        <v>23</v>
+      </c>
+      <c r="M6" t="s">
         <v>24</v>
       </c>
-      <c r="M6" t="s">
-        <v>25</v>
-      </c>
       <c r="O6" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B7" t="s">
         <v>40</v>
       </c>
-      <c r="B7" t="s">
-        <v>41</v>
-      </c>
       <c r="C7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D7" t="s">
+        <v>35</v>
+      </c>
+      <c r="E7" t="s">
         <v>36</v>
       </c>
-      <c r="E7" t="s">
-        <v>37</v>
-      </c>
       <c r="F7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J7">
         <v>2020</v>
       </c>
       <c r="K7" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L7" t="s">
+        <v>23</v>
+      </c>
+      <c r="M7" t="s">
         <v>24</v>
       </c>
-      <c r="M7" t="s">
-        <v>25</v>
-      </c>
       <c r="O7" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8" t="s">
         <v>42</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" t="s">
         <v>43</v>
       </c>
-      <c r="C8" t="s">
-        <v>28</v>
-      </c>
-      <c r="D8" t="s">
-        <v>44</v>
-      </c>
       <c r="E8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J8">
         <v>2020</v>
       </c>
       <c r="K8" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L8" t="s">
+        <v>23</v>
+      </c>
+      <c r="M8" t="s">
         <v>24</v>
       </c>
-      <c r="M8" t="s">
-        <v>25</v>
-      </c>
       <c r="O8" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B9" t="s">
         <v>45</v>
       </c>
-      <c r="B9" t="s">
-        <v>46</v>
-      </c>
       <c r="C9" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" t="s">
         <v>28</v>
       </c>
-      <c r="D9" t="s">
-        <v>29</v>
-      </c>
       <c r="E9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J9">
         <v>2020</v>
       </c>
       <c r="K9" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L9" t="s">
+        <v>23</v>
+      </c>
+      <c r="M9" t="s">
         <v>24</v>
       </c>
-      <c r="M9" t="s">
-        <v>25</v>
-      </c>
       <c r="O9" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
+        <v>46</v>
+      </c>
+      <c r="B10" t="s">
         <v>47</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10" t="s">
         <v>48</v>
       </c>
-      <c r="C10" t="s">
-        <v>28</v>
-      </c>
-      <c r="D10" t="s">
-        <v>49</v>
-      </c>
       <c r="E10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J10">
         <v>2020</v>
       </c>
       <c r="K10" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L10" t="s">
+        <v>23</v>
+      </c>
+      <c r="M10" t="s">
         <v>24</v>
       </c>
-      <c r="M10" t="s">
-        <v>25</v>
-      </c>
       <c r="O10" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
+        <v>49</v>
+      </c>
+      <c r="B11" t="s">
         <v>50</v>
       </c>
-      <c r="B11" t="s">
-        <v>51</v>
-      </c>
       <c r="C11" t="s">
+        <v>27</v>
+      </c>
+      <c r="D11" t="s">
         <v>28</v>
       </c>
-      <c r="D11" t="s">
-        <v>29</v>
-      </c>
       <c r="E11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J11">
         <v>2020</v>
       </c>
       <c r="K11" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L11" t="s">
+        <v>23</v>
+      </c>
+      <c r="M11" t="s">
         <v>24</v>
       </c>
-      <c r="M11" t="s">
-        <v>25</v>
-      </c>
       <c r="O11" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
+        <v>51</v>
+      </c>
+      <c r="B12" t="s">
         <v>52</v>
       </c>
-      <c r="B12" t="s">
-        <v>53</v>
-      </c>
       <c r="C12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J12">
         <v>2020</v>
       </c>
       <c r="K12" t="s">
+        <v>239</v>
+      </c>
+      <c r="L12" t="s">
+        <v>23</v>
+      </c>
+      <c r="M12" t="s">
+        <v>24</v>
+      </c>
+      <c r="N12" t="s">
         <v>241</v>
       </c>
-      <c r="L12" t="s">
-        <v>24</v>
-      </c>
-      <c r="M12" t="s">
-        <v>25</v>
-      </c>
-      <c r="N12" t="s">
-        <v>243</v>
-      </c>
       <c r="O12" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="P12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
+        <v>53</v>
+      </c>
+      <c r="B13" t="s">
         <v>54</v>
       </c>
-      <c r="B13" t="s">
-        <v>55</v>
-      </c>
       <c r="C13" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E13" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F13" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J13">
         <v>2020</v>
       </c>
       <c r="K13" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L13" t="s">
+        <v>23</v>
+      </c>
+      <c r="M13" t="s">
         <v>24</v>
       </c>
-      <c r="M13" t="s">
-        <v>25</v>
-      </c>
       <c r="O13" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
+        <v>55</v>
+      </c>
+      <c r="B14" t="s">
         <v>56</v>
       </c>
-      <c r="B14" t="s">
-        <v>57</v>
-      </c>
       <c r="C14" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E14" t="s">
         <v>18</v>
       </c>
-      <c r="E14" t="s">
-        <v>19</v>
-      </c>
       <c r="F14" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G14" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H14" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J14">
         <v>2020</v>
       </c>
       <c r="K14" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L14" t="s">
+        <v>23</v>
+      </c>
+      <c r="M14" t="s">
         <v>24</v>
       </c>
-      <c r="M14" t="s">
-        <v>25</v>
-      </c>
       <c r="N14" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="O14" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
+        <v>57</v>
+      </c>
+      <c r="B15" t="s">
         <v>58</v>
       </c>
-      <c r="B15" t="s">
-        <v>59</v>
-      </c>
       <c r="C15" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D15" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E15" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F15" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J15">
         <v>2020</v>
       </c>
       <c r="K15" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L15" t="s">
+        <v>23</v>
+      </c>
+      <c r="M15" t="s">
         <v>24</v>
       </c>
-      <c r="M15" t="s">
-        <v>25</v>
-      </c>
       <c r="O15" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
+        <v>59</v>
+      </c>
+      <c r="B16" t="s">
         <v>60</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
+        <v>27</v>
+      </c>
+      <c r="D16" t="s">
         <v>61</v>
       </c>
-      <c r="C16" t="s">
-        <v>28</v>
-      </c>
-      <c r="D16" t="s">
-        <v>62</v>
-      </c>
       <c r="E16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J16">
         <v>2020</v>
       </c>
       <c r="K16" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L16" t="s">
+        <v>23</v>
+      </c>
+      <c r="M16" t="s">
         <v>24</v>
       </c>
-      <c r="M16" t="s">
-        <v>25</v>
-      </c>
       <c r="O16" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
+        <v>62</v>
+      </c>
+      <c r="B17" t="s">
         <v>63</v>
       </c>
-      <c r="B17" t="s">
-        <v>64</v>
-      </c>
       <c r="C17" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D17" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F17" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G17" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H17" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I17" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J17">
         <v>2020</v>
       </c>
       <c r="K17" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L17" t="s">
+        <v>23</v>
+      </c>
+      <c r="M17" t="s">
         <v>24</v>
       </c>
-      <c r="M17" t="s">
-        <v>25</v>
-      </c>
       <c r="N17" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="O17" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="P17" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
+        <v>64</v>
+      </c>
+      <c r="B18" t="s">
         <v>65</v>
       </c>
-      <c r="B18" t="s">
-        <v>66</v>
-      </c>
       <c r="C18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D18" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E18" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F18" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G18" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H18" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I18" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J18">
         <v>2020</v>
       </c>
       <c r="K18" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L18" t="s">
+        <v>23</v>
+      </c>
+      <c r="M18" t="s">
         <v>24</v>
       </c>
-      <c r="M18" t="s">
-        <v>25</v>
-      </c>
       <c r="O18" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
+        <v>66</v>
+      </c>
+      <c r="B19" t="s">
         <v>67</v>
       </c>
-      <c r="B19" t="s">
-        <v>68</v>
-      </c>
       <c r="C19" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D19" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G19" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J19">
         <v>2020</v>
       </c>
       <c r="K19" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L19" t="s">
+        <v>23</v>
+      </c>
+      <c r="M19" t="s">
         <v>24</v>
       </c>
-      <c r="M19" t="s">
-        <v>25</v>
-      </c>
       <c r="O19" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
+        <v>68</v>
+      </c>
+      <c r="B20" t="s">
         <v>69</v>
       </c>
-      <c r="B20" t="s">
-        <v>70</v>
-      </c>
       <c r="C20" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D20" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E20" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F20" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G20" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H20" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I20" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J20">
         <v>2020</v>
       </c>
       <c r="K20" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L20" t="s">
+        <v>23</v>
+      </c>
+      <c r="M20" t="s">
         <v>24</v>
       </c>
-      <c r="M20" t="s">
-        <v>25</v>
-      </c>
       <c r="N20" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="O20" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B21" t="s">
+        <v>15</v>
+      </c>
+      <c r="C21" t="s">
         <v>16</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D21" t="s">
         <v>17</v>
       </c>
-      <c r="D21" t="s">
-        <v>18</v>
-      </c>
       <c r="E21" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F21" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G21" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H21" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I21" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J21">
         <v>2021</v>
       </c>
       <c r="K21" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L21" t="s">
+        <v>23</v>
+      </c>
+      <c r="M21" t="s">
         <v>24</v>
       </c>
-      <c r="M21" t="s">
-        <v>25</v>
-      </c>
       <c r="N21" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="O21" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
+        <v>71</v>
+      </c>
+      <c r="B22" t="s">
         <v>72</v>
       </c>
-      <c r="B22" t="s">
-        <v>73</v>
-      </c>
       <c r="C22" t="s">
+        <v>27</v>
+      </c>
+      <c r="D22" t="s">
         <v>28</v>
       </c>
-      <c r="D22" t="s">
+      <c r="E22" t="s">
         <v>29</v>
       </c>
-      <c r="E22" t="s">
-        <v>30</v>
-      </c>
       <c r="F22" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G22" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H22" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I22" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J22">
         <v>2021</v>
       </c>
       <c r="K22" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L22" t="s">
+        <v>23</v>
+      </c>
+      <c r="M22" t="s">
         <v>24</v>
       </c>
-      <c r="M22" t="s">
-        <v>25</v>
-      </c>
       <c r="O22" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
+        <v>73</v>
+      </c>
+      <c r="B23" t="s">
         <v>74</v>
       </c>
-      <c r="B23" t="s">
-        <v>75</v>
-      </c>
       <c r="C23" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D23" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E23" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F23" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G23" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H23" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I23" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J23">
         <v>2021</v>
       </c>
       <c r="K23" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L23" t="s">
+        <v>23</v>
+      </c>
+      <c r="M23" t="s">
         <v>24</v>
       </c>
-      <c r="M23" t="s">
-        <v>25</v>
-      </c>
       <c r="O23" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
+        <v>75</v>
+      </c>
+      <c r="B24" t="s">
         <v>76</v>
       </c>
-      <c r="B24" t="s">
-        <v>77</v>
-      </c>
       <c r="C24" t="s">
+        <v>27</v>
+      </c>
+      <c r="D24" t="s">
         <v>28</v>
       </c>
-      <c r="D24" t="s">
+      <c r="E24" t="s">
         <v>29</v>
       </c>
-      <c r="E24" t="s">
-        <v>30</v>
-      </c>
       <c r="F24" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G24" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H24" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I24" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J24">
         <v>2021</v>
       </c>
       <c r="K24" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L24" t="s">
+        <v>23</v>
+      </c>
+      <c r="M24" t="s">
         <v>24</v>
       </c>
-      <c r="M24" t="s">
-        <v>25</v>
-      </c>
       <c r="O24" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
+        <v>77</v>
+      </c>
+      <c r="B25" t="s">
         <v>78</v>
       </c>
-      <c r="B25" t="s">
-        <v>79</v>
-      </c>
       <c r="C25" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D25" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E25" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F25" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G25" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I25" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J25">
         <v>2021</v>
       </c>
       <c r="K25" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L25" t="s">
+        <v>23</v>
+      </c>
+      <c r="M25" t="s">
         <v>24</v>
       </c>
-      <c r="M25" t="s">
-        <v>25</v>
-      </c>
       <c r="O25" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
+        <v>79</v>
+      </c>
+      <c r="B26" t="s">
         <v>80</v>
       </c>
-      <c r="B26" t="s">
-        <v>81</v>
-      </c>
       <c r="C26" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D26" t="s">
+        <v>35</v>
+      </c>
+      <c r="E26" t="s">
         <v>36</v>
       </c>
-      <c r="E26" t="s">
-        <v>37</v>
-      </c>
       <c r="F26" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G26" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H26" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I26" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J26">
         <v>2021</v>
       </c>
       <c r="K26" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L26" t="s">
+        <v>23</v>
+      </c>
+      <c r="M26" t="s">
         <v>24</v>
       </c>
-      <c r="M26" t="s">
-        <v>25</v>
-      </c>
       <c r="O26" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
+        <v>81</v>
+      </c>
+      <c r="B27" t="s">
         <v>82</v>
       </c>
-      <c r="B27" t="s">
-        <v>83</v>
-      </c>
       <c r="C27" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D27" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E27" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F27" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G27" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H27" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I27" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J27">
         <v>2021</v>
       </c>
       <c r="K27" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L27" t="s">
+        <v>23</v>
+      </c>
+      <c r="M27" t="s">
         <v>24</v>
       </c>
-      <c r="M27" t="s">
-        <v>25</v>
-      </c>
       <c r="O27" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
+        <v>83</v>
+      </c>
+      <c r="B28" t="s">
         <v>84</v>
       </c>
-      <c r="B28" t="s">
-        <v>85</v>
-      </c>
       <c r="C28" t="s">
+        <v>27</v>
+      </c>
+      <c r="D28" t="s">
         <v>28</v>
       </c>
-      <c r="D28" t="s">
+      <c r="E28" t="s">
         <v>29</v>
       </c>
-      <c r="E28" t="s">
-        <v>30</v>
-      </c>
       <c r="F28" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G28" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H28" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I28" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J28">
         <v>2021</v>
       </c>
       <c r="K28" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L28" t="s">
+        <v>23</v>
+      </c>
+      <c r="M28" t="s">
         <v>24</v>
       </c>
-      <c r="M28" t="s">
-        <v>25</v>
-      </c>
       <c r="N28" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="O28" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="P28" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
+        <v>85</v>
+      </c>
+      <c r="B29" t="s">
         <v>86</v>
       </c>
-      <c r="B29" t="s">
-        <v>87</v>
-      </c>
       <c r="C29" t="s">
+        <v>27</v>
+      </c>
+      <c r="D29" t="s">
         <v>28</v>
       </c>
-      <c r="D29" t="s">
+      <c r="E29" t="s">
         <v>29</v>
       </c>
-      <c r="E29" t="s">
-        <v>30</v>
-      </c>
       <c r="F29" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G29" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H29" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I29" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J29">
         <v>2021</v>
       </c>
       <c r="K29" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L29" t="s">
+        <v>23</v>
+      </c>
+      <c r="M29" t="s">
         <v>24</v>
       </c>
-      <c r="M29" t="s">
-        <v>25</v>
-      </c>
       <c r="O29" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
+        <v>87</v>
+      </c>
+      <c r="B30" t="s">
         <v>88</v>
       </c>
-      <c r="B30" t="s">
-        <v>89</v>
-      </c>
       <c r="C30" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D30" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E30" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F30" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G30" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H30" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I30" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J30">
         <v>2021</v>
       </c>
       <c r="K30" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L30" t="s">
+        <v>23</v>
+      </c>
+      <c r="M30" t="s">
         <v>24</v>
       </c>
-      <c r="M30" t="s">
-        <v>25</v>
-      </c>
       <c r="O30" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
+        <v>89</v>
+      </c>
+      <c r="B31" t="s">
         <v>90</v>
       </c>
-      <c r="B31" t="s">
-        <v>91</v>
-      </c>
       <c r="C31" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D31" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E31" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F31" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G31" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H31" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I31" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J31">
         <v>2021</v>
       </c>
       <c r="K31" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L31" t="s">
+        <v>23</v>
+      </c>
+      <c r="M31" t="s">
         <v>24</v>
       </c>
-      <c r="M31" t="s">
-        <v>25</v>
-      </c>
       <c r="O31" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
+        <v>91</v>
+      </c>
+      <c r="B32" t="s">
         <v>92</v>
       </c>
-      <c r="B32" t="s">
-        <v>93</v>
-      </c>
       <c r="C32" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D32" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E32" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F32" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G32" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H32" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I32" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J32">
         <v>2021</v>
       </c>
       <c r="K32" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L32" t="s">
+        <v>23</v>
+      </c>
+      <c r="M32" t="s">
         <v>24</v>
       </c>
-      <c r="M32" t="s">
-        <v>25</v>
-      </c>
       <c r="O32" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
+        <v>93</v>
+      </c>
+      <c r="B33" t="s">
         <v>94</v>
       </c>
-      <c r="B33" t="s">
-        <v>95</v>
-      </c>
       <c r="C33" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D33" t="s">
+        <v>17</v>
+      </c>
+      <c r="E33" t="s">
         <v>18</v>
       </c>
-      <c r="E33" t="s">
-        <v>19</v>
-      </c>
       <c r="F33" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G33" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H33" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I33" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J33">
         <v>2021</v>
       </c>
       <c r="K33" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L33" t="s">
+        <v>23</v>
+      </c>
+      <c r="M33" t="s">
         <v>24</v>
       </c>
-      <c r="M33" t="s">
-        <v>25</v>
-      </c>
       <c r="N33" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="O33" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
+        <v>95</v>
+      </c>
+      <c r="B34" t="s">
         <v>96</v>
       </c>
-      <c r="B34" t="s">
-        <v>97</v>
-      </c>
       <c r="C34" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D34" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E34" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F34" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G34" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H34" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I34" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J34">
         <v>2021</v>
       </c>
       <c r="K34" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L34" t="s">
+        <v>23</v>
+      </c>
+      <c r="M34" t="s">
         <v>24</v>
       </c>
-      <c r="M34" t="s">
-        <v>25</v>
-      </c>
       <c r="O34" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
+        <v>97</v>
+      </c>
+      <c r="B35" t="s">
         <v>98</v>
       </c>
-      <c r="B35" t="s">
-        <v>99</v>
-      </c>
       <c r="C35" t="s">
+        <v>27</v>
+      </c>
+      <c r="D35" t="s">
         <v>28</v>
       </c>
-      <c r="D35" t="s">
-        <v>29</v>
-      </c>
       <c r="E35" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F35" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G35" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H35" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I35" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J35">
         <v>2021</v>
       </c>
       <c r="K35" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L35" t="s">
+        <v>23</v>
+      </c>
+      <c r="M35" t="s">
         <v>24</v>
       </c>
-      <c r="M35" t="s">
-        <v>25</v>
-      </c>
       <c r="O35" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
+        <v>99</v>
+      </c>
+      <c r="B36" t="s">
         <v>100</v>
       </c>
-      <c r="B36" t="s">
-        <v>101</v>
-      </c>
       <c r="C36" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D36" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E36" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F36" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G36" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H36" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I36" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J36">
         <v>2021</v>
       </c>
       <c r="K36" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L36" t="s">
+        <v>23</v>
+      </c>
+      <c r="M36" t="s">
         <v>24</v>
       </c>
-      <c r="M36" t="s">
-        <v>25</v>
-      </c>
       <c r="N36" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="O36" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B37" t="s">
+        <v>15</v>
+      </c>
+      <c r="C37" t="s">
         <v>16</v>
       </c>
-      <c r="C37" t="s">
+      <c r="D37" t="s">
         <v>17</v>
       </c>
-      <c r="D37" t="s">
-        <v>18</v>
-      </c>
       <c r="E37" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F37" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G37" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H37" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I37" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J37">
         <v>2022</v>
       </c>
       <c r="K37" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L37" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M37" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N37" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="O37" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
+        <v>103</v>
+      </c>
+      <c r="B38" t="s">
         <v>104</v>
       </c>
-      <c r="B38" t="s">
-        <v>105</v>
-      </c>
       <c r="C38" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D38" t="s">
+        <v>17</v>
+      </c>
+      <c r="E38" t="s">
         <v>18</v>
       </c>
-      <c r="E38" t="s">
-        <v>19</v>
-      </c>
       <c r="F38" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G38" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H38" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I38" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J38">
         <v>2022</v>
       </c>
       <c r="K38" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L38" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M38" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="O38" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
+        <v>105</v>
+      </c>
+      <c r="B39" t="s">
         <v>106</v>
       </c>
-      <c r="B39" t="s">
-        <v>107</v>
-      </c>
       <c r="C39" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D39" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E39" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F39" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G39" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H39" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I39" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J39">
         <v>2022</v>
       </c>
       <c r="K39" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L39" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M39" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="O39" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
+        <v>107</v>
+      </c>
+      <c r="B40" t="s">
         <v>108</v>
       </c>
-      <c r="B40" t="s">
-        <v>109</v>
-      </c>
       <c r="C40" t="s">
+        <v>27</v>
+      </c>
+      <c r="D40" t="s">
         <v>28</v>
       </c>
-      <c r="D40" t="s">
-        <v>29</v>
-      </c>
       <c r="E40" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F40" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G40" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H40" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I40" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J40">
         <v>2022</v>
       </c>
       <c r="K40" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L40" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M40" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="O40" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
+        <v>109</v>
+      </c>
+      <c r="B41" t="s">
         <v>110</v>
       </c>
-      <c r="B41" t="s">
-        <v>111</v>
-      </c>
       <c r="C41" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D41" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E41" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F41" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G41" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H41" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I41" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J41">
         <v>2022</v>
       </c>
       <c r="K41" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L41" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M41" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="O41" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
+        <v>111</v>
+      </c>
+      <c r="B42" t="s">
         <v>112</v>
       </c>
-      <c r="B42" t="s">
-        <v>113</v>
-      </c>
       <c r="C42" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D42" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E42" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F42" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G42" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H42" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I42" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J42">
         <v>2022</v>
       </c>
       <c r="K42" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L42" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M42" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="O42" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
+        <v>113</v>
+      </c>
+      <c r="B43" t="s">
         <v>114</v>
       </c>
-      <c r="B43" t="s">
-        <v>115</v>
-      </c>
       <c r="C43" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D43" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E43" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F43" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G43" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H43" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I43" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J43">
         <v>2022</v>
       </c>
       <c r="K43" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L43" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M43" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="O43" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
+        <v>115</v>
+      </c>
+      <c r="B44" t="s">
         <v>116</v>
       </c>
-      <c r="B44" t="s">
-        <v>117</v>
-      </c>
       <c r="C44" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D44" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E44" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F44" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G44" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H44" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I44" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J44">
         <v>2022</v>
       </c>
       <c r="K44" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L44" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M44" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="O44" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
+        <v>117</v>
+      </c>
+      <c r="B45" t="s">
         <v>118</v>
       </c>
-      <c r="B45" t="s">
-        <v>119</v>
-      </c>
       <c r="C45" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D45" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E45" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F45" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G45" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H45" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I45" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J45">
         <v>2022</v>
       </c>
       <c r="K45" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L45" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M45" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="O45" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
+        <v>119</v>
+      </c>
+      <c r="B46" t="s">
         <v>120</v>
       </c>
-      <c r="B46" t="s">
-        <v>121</v>
-      </c>
       <c r="C46" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D46" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E46" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F46" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G46" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H46" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I46" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J46">
         <v>2022</v>
       </c>
       <c r="K46" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L46" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M46" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="O46" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
+        <v>121</v>
+      </c>
+      <c r="B47" t="s">
         <v>122</v>
       </c>
-      <c r="B47" t="s">
-        <v>123</v>
-      </c>
       <c r="C47" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D47" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E47" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F47" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G47" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H47" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I47" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J47">
         <v>2022</v>
       </c>
       <c r="K47" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L47" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M47" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N47" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="O47" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="P47" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="48" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
+        <v>123</v>
+      </c>
+      <c r="B48" t="s">
         <v>124</v>
       </c>
-      <c r="B48" t="s">
-        <v>125</v>
-      </c>
       <c r="C48" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D48" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E48" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F48" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G48" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H48" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I48" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J48">
         <v>2022</v>
       </c>
       <c r="K48" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L48" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M48" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="O48" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="49" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
+        <v>125</v>
+      </c>
+      <c r="B49" t="s">
         <v>126</v>
       </c>
-      <c r="B49" t="s">
-        <v>127</v>
-      </c>
       <c r="C49" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D49" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E49" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F49" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G49" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H49" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I49" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J49">
         <v>2022</v>
       </c>
       <c r="K49" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L49" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M49" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="O49" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="50" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
+        <v>127</v>
+      </c>
+      <c r="B50" t="s">
         <v>128</v>
       </c>
-      <c r="B50" t="s">
-        <v>129</v>
-      </c>
       <c r="C50" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D50" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E50" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F50" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G50" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H50" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I50" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J50">
         <v>2022</v>
       </c>
       <c r="K50" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L50" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M50" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="O50" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="51" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
+        <v>129</v>
+      </c>
+      <c r="B51" t="s">
         <v>130</v>
       </c>
-      <c r="B51" t="s">
-        <v>131</v>
-      </c>
       <c r="C51" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D51" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E51" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F51" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G51" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H51" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I51" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J51">
         <v>2022</v>
       </c>
       <c r="K51" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L51" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M51" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="O51" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="52" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
+        <v>131</v>
+      </c>
+      <c r="B52" t="s">
         <v>132</v>
       </c>
-      <c r="B52" t="s">
-        <v>133</v>
-      </c>
       <c r="C52" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D52" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E52" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F52" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G52" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H52" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I52" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J52">
         <v>2022</v>
       </c>
       <c r="K52" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L52" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M52" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="O52" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="53" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
+        <v>133</v>
+      </c>
+      <c r="B53" t="s">
         <v>134</v>
       </c>
-      <c r="B53" t="s">
-        <v>135</v>
-      </c>
       <c r="C53" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D53" t="s">
+        <v>35</v>
+      </c>
+      <c r="E53" t="s">
         <v>36</v>
       </c>
-      <c r="E53" t="s">
-        <v>37</v>
-      </c>
       <c r="F53" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G53" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H53" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I53" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J53">
         <v>2022</v>
       </c>
       <c r="K53" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L53" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M53" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="O53" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="54" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
+        <v>135</v>
+      </c>
+      <c r="B54" t="s">
         <v>136</v>
       </c>
-      <c r="B54" t="s">
-        <v>137</v>
-      </c>
       <c r="C54" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D54" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E54" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F54" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G54" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H54" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I54" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J54">
         <v>2022</v>
       </c>
       <c r="K54" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L54" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M54" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="O54" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="55" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
+        <v>137</v>
+      </c>
+      <c r="B55" t="s">
         <v>138</v>
       </c>
-      <c r="B55" t="s">
-        <v>139</v>
-      </c>
       <c r="C55" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D55" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E55" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F55" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G55" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H55" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I55" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J55">
         <v>2022</v>
       </c>
       <c r="K55" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L55" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M55" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="O55" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="56" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
+        <v>139</v>
+      </c>
+      <c r="B56" t="s">
         <v>140</v>
       </c>
-      <c r="B56" t="s">
-        <v>141</v>
-      </c>
       <c r="C56" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D56" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E56" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F56" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G56" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H56" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I56" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J56">
         <v>2022</v>
       </c>
       <c r="K56" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L56" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M56" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N56" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="O56" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="57" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B57" t="s">
+        <v>15</v>
+      </c>
+      <c r="C57" t="s">
         <v>16</v>
       </c>
-      <c r="C57" t="s">
+      <c r="D57" t="s">
         <v>17</v>
       </c>
-      <c r="D57" t="s">
-        <v>18</v>
-      </c>
       <c r="E57" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F57" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G57" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H57" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I57" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J57">
         <v>2023</v>
       </c>
       <c r="K57" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L57" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M57" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N57" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="O57" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="58" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
+        <v>142</v>
+      </c>
+      <c r="B58" t="s">
         <v>143</v>
       </c>
-      <c r="B58" t="s">
-        <v>144</v>
-      </c>
       <c r="C58" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D58" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E58" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F58" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G58" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H58" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I58" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J58">
         <v>2023</v>
       </c>
       <c r="K58" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L58" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M58" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="O58" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="59" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
+        <v>144</v>
+      </c>
+      <c r="B59" t="s">
         <v>145</v>
       </c>
-      <c r="B59" t="s">
-        <v>146</v>
-      </c>
       <c r="C59" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D59" t="s">
+        <v>35</v>
+      </c>
+      <c r="E59" t="s">
         <v>36</v>
       </c>
-      <c r="E59" t="s">
-        <v>37</v>
-      </c>
       <c r="F59" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G59" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H59" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I59" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J59">
         <v>2023</v>
       </c>
       <c r="K59" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L59" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M59" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="O59" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="60" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
+        <v>146</v>
+      </c>
+      <c r="B60" t="s">
         <v>147</v>
       </c>
-      <c r="B60" t="s">
-        <v>148</v>
-      </c>
       <c r="C60" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D60" t="s">
+        <v>35</v>
+      </c>
+      <c r="E60" t="s">
         <v>36</v>
       </c>
-      <c r="E60" t="s">
-        <v>37</v>
-      </c>
       <c r="F60" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G60" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H60" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I60" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J60">
         <v>2023</v>
       </c>
       <c r="K60" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L60" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M60" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="O60" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="P60" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="61" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
+        <v>148</v>
+      </c>
+      <c r="B61" t="s">
         <v>149</v>
       </c>
-      <c r="B61" t="s">
-        <v>150</v>
-      </c>
       <c r="C61" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D61" t="s">
+        <v>35</v>
+      </c>
+      <c r="E61" t="s">
         <v>36</v>
       </c>
-      <c r="E61" t="s">
-        <v>37</v>
-      </c>
       <c r="F61" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G61" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H61" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I61" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J61">
         <v>2023</v>
       </c>
       <c r="K61" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L61" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M61" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="O61" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="P61" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="62" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
+        <v>150</v>
+      </c>
+      <c r="B62" t="s">
         <v>151</v>
       </c>
-      <c r="B62" t="s">
-        <v>152</v>
-      </c>
       <c r="C62" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D62" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E62" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F62" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G62" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H62" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I62" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J62">
         <v>2023</v>
       </c>
       <c r="K62" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L62" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M62" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="O62" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="63" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
+        <v>152</v>
+      </c>
+      <c r="B63" t="s">
         <v>153</v>
       </c>
-      <c r="B63" t="s">
-        <v>154</v>
-      </c>
       <c r="C63" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D63" t="s">
+        <v>35</v>
+      </c>
+      <c r="E63" t="s">
         <v>36</v>
       </c>
-      <c r="E63" t="s">
-        <v>37</v>
-      </c>
       <c r="F63" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G63" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H63" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I63" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J63">
         <v>2023</v>
       </c>
       <c r="K63" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L63" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M63" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="O63" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="64" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
+        <v>154</v>
+      </c>
+      <c r="B64" t="s">
         <v>155</v>
       </c>
-      <c r="B64" t="s">
-        <v>156</v>
-      </c>
       <c r="C64" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D64" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E64" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F64" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G64" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H64" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I64" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J64">
         <v>2023</v>
       </c>
       <c r="K64" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L64" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M64" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="O64" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
+        <v>156</v>
+      </c>
+      <c r="B65" t="s">
         <v>157</v>
       </c>
-      <c r="B65" t="s">
-        <v>158</v>
-      </c>
       <c r="C65" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D65" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E65" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F65" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G65" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H65" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I65" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J65">
         <v>2023</v>
       </c>
       <c r="K65" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L65" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M65" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="O65" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
+        <v>158</v>
+      </c>
+      <c r="B66" t="s">
         <v>159</v>
       </c>
-      <c r="B66" t="s">
-        <v>160</v>
-      </c>
       <c r="C66" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D66" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E66" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F66" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G66" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H66" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I66" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J66">
         <v>2023</v>
       </c>
       <c r="K66" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L66" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M66" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="O66" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
+        <v>160</v>
+      </c>
+      <c r="B67" t="s">
         <v>161</v>
       </c>
-      <c r="B67" t="s">
-        <v>162</v>
-      </c>
       <c r="C67" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D67" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E67" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F67" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G67" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H67" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I67" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J67">
         <v>2023</v>
       </c>
       <c r="K67" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L67" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M67" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="O67" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
+        <v>162</v>
+      </c>
+      <c r="B68" t="s">
         <v>163</v>
       </c>
-      <c r="B68" t="s">
-        <v>164</v>
-      </c>
       <c r="C68" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D68" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E68" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F68" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G68" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H68" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I68" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J68">
         <v>2023</v>
       </c>
       <c r="K68" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L68" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M68" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="O68" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
+        <v>164</v>
+      </c>
+      <c r="B69" t="s">
         <v>165</v>
       </c>
-      <c r="B69" t="s">
-        <v>166</v>
-      </c>
       <c r="C69" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D69" t="s">
+        <v>35</v>
+      </c>
+      <c r="E69" t="s">
         <v>36</v>
       </c>
-      <c r="E69" t="s">
-        <v>37</v>
-      </c>
       <c r="F69" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G69" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H69" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I69" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J69">
         <v>2023</v>
       </c>
       <c r="K69" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L69" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M69" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="O69" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
+        <v>166</v>
+      </c>
+      <c r="B70" t="s">
         <v>167</v>
       </c>
-      <c r="B70" t="s">
-        <v>168</v>
-      </c>
       <c r="C70" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D70" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E70" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F70" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G70" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H70" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I70" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J70">
         <v>2023</v>
       </c>
       <c r="K70" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L70" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M70" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="O70" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
+        <v>168</v>
+      </c>
+      <c r="B71" t="s">
         <v>169</v>
       </c>
-      <c r="B71" t="s">
-        <v>170</v>
-      </c>
       <c r="C71" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D71" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E71" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F71" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G71" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H71" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I71" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J71">
         <v>2023</v>
       </c>
       <c r="K71" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L71" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M71" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="O71" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
+        <v>170</v>
+      </c>
+      <c r="B72" t="s">
         <v>171</v>
       </c>
-      <c r="B72" t="s">
-        <v>172</v>
-      </c>
       <c r="C72" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D72" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E72" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F72" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G72" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H72" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I72" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J72">
         <v>2023</v>
       </c>
       <c r="K72" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L72" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M72" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="O72" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
+        <v>172</v>
+      </c>
+      <c r="B73" t="s">
         <v>173</v>
       </c>
-      <c r="B73" t="s">
-        <v>174</v>
-      </c>
       <c r="C73" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D73" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E73" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F73" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G73" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H73" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I73" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J73">
         <v>2023</v>
       </c>
       <c r="K73" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L73" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M73" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="O73" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
+        <v>174</v>
+      </c>
+      <c r="B74" t="s">
         <v>175</v>
       </c>
-      <c r="B74" t="s">
-        <v>176</v>
-      </c>
       <c r="C74" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D74" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E74" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F74" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G74" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H74" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I74" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J74">
         <v>2023</v>
       </c>
       <c r="K74" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L74" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M74" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="O74" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
+        <v>176</v>
+      </c>
+      <c r="B75" t="s">
         <v>177</v>
       </c>
-      <c r="B75" t="s">
-        <v>178</v>
-      </c>
       <c r="C75" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D75" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E75" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F75" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G75" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H75" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I75" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J75">
         <v>2023</v>
       </c>
       <c r="K75" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L75" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M75" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="O75" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
+        <v>178</v>
+      </c>
+      <c r="B76" t="s">
         <v>179</v>
       </c>
-      <c r="B76" t="s">
-        <v>180</v>
-      </c>
       <c r="C76" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D76" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E76" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F76" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G76" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H76" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I76" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J76">
         <v>2023</v>
       </c>
       <c r="K76" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L76" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M76" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="O76" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
+        <v>180</v>
+      </c>
+      <c r="B77" t="s">
         <v>181</v>
       </c>
-      <c r="B77" t="s">
-        <v>182</v>
-      </c>
       <c r="C77" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D77" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E77" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F77" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G77" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H77" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I77" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J77">
         <v>2023</v>
       </c>
       <c r="K77" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L77" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M77" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="O77" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
+        <v>182</v>
+      </c>
+      <c r="B78" t="s">
         <v>183</v>
       </c>
-      <c r="B78" t="s">
-        <v>184</v>
-      </c>
       <c r="C78" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D78" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E78" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F78" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G78" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H78" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I78" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J78">
         <v>2023</v>
       </c>
       <c r="K78" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L78" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M78" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="O78" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
+        <v>184</v>
+      </c>
+      <c r="B79" t="s">
         <v>185</v>
       </c>
-      <c r="B79" t="s">
-        <v>186</v>
-      </c>
       <c r="C79" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D79" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E79" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F79" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G79" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H79" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I79" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J79">
         <v>2023</v>
       </c>
       <c r="K79" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L79" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M79" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N79" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="O79" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B80" t="s">
+        <v>15</v>
+      </c>
+      <c r="C80" t="s">
         <v>16</v>
       </c>
-      <c r="C80" t="s">
+      <c r="D80" t="s">
         <v>17</v>
       </c>
-      <c r="D80" t="s">
-        <v>18</v>
-      </c>
       <c r="E80" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F80" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G80" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H80" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I80" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J80">
         <v>2024</v>
       </c>
       <c r="K80" t="s">
+        <v>238</v>
+      </c>
+      <c r="L80" t="s">
+        <v>23</v>
+      </c>
+      <c r="M80" t="s">
+        <v>102</v>
+      </c>
+      <c r="N80" t="s">
         <v>240</v>
       </c>
-      <c r="L80" t="s">
-        <v>24</v>
-      </c>
-      <c r="M80" t="s">
-        <v>103</v>
-      </c>
-      <c r="N80" t="s">
-        <v>242</v>
-      </c>
       <c r="O80" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="81" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
+        <v>187</v>
+      </c>
+      <c r="B81" t="s">
         <v>188</v>
       </c>
-      <c r="B81" t="s">
-        <v>189</v>
-      </c>
       <c r="C81" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D81" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E81" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F81" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G81" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H81" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I81" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J81">
         <v>2024</v>
       </c>
       <c r="K81" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="L81" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M81" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="O81" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="82" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
+        <v>189</v>
+      </c>
+      <c r="B82" t="s">
         <v>190</v>
       </c>
-      <c r="B82" t="s">
-        <v>191</v>
-      </c>
       <c r="C82" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D82" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E82" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F82" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G82" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H82" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I82" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J82">
         <v>2024</v>
       </c>
       <c r="K82" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="L82" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M82" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="O82" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="83" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
+        <v>191</v>
+      </c>
+      <c r="B83" t="s">
         <v>192</v>
       </c>
-      <c r="B83" t="s">
-        <v>193</v>
-      </c>
       <c r="C83" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D83" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E83" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F83" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G83" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H83" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I83" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J83">
         <v>2024</v>
       </c>
       <c r="K83" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="L83" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M83" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="O83" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="P83" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="84" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
+        <v>193</v>
+      </c>
+      <c r="B84" t="s">
         <v>194</v>
       </c>
-      <c r="B84" t="s">
-        <v>195</v>
-      </c>
       <c r="C84" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D84" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E84" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F84" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G84" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H84" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I84" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J84">
         <v>2024</v>
       </c>
       <c r="K84" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="L84" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M84" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="O84" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="85" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
+        <v>195</v>
+      </c>
+      <c r="B85" t="s">
         <v>196</v>
       </c>
-      <c r="B85" t="s">
-        <v>197</v>
-      </c>
       <c r="C85" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D85" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E85" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F85" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G85" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H85" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I85" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J85">
         <v>2024</v>
       </c>
       <c r="K85" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="L85" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M85" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="O85" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="86" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
+        <v>197</v>
+      </c>
+      <c r="B86" t="s">
         <v>198</v>
       </c>
-      <c r="B86" t="s">
-        <v>199</v>
-      </c>
       <c r="C86" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D86" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E86" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F86" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G86" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H86" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I86" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J86">
         <v>2024</v>
       </c>
       <c r="K86" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="L86" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M86" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="O86" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="87" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
+        <v>199</v>
+      </c>
+      <c r="B87" t="s">
         <v>200</v>
       </c>
-      <c r="B87" t="s">
-        <v>201</v>
-      </c>
       <c r="C87" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D87" t="s">
+        <v>35</v>
+      </c>
+      <c r="E87" t="s">
         <v>36</v>
       </c>
-      <c r="E87" t="s">
-        <v>37</v>
-      </c>
       <c r="F87" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G87" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H87" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I87" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J87">
         <v>2024</v>
       </c>
       <c r="K87" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="L87" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M87" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="O87" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="88" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
+        <v>201</v>
+      </c>
+      <c r="B88" t="s">
         <v>202</v>
       </c>
-      <c r="B88" t="s">
-        <v>203</v>
-      </c>
       <c r="C88" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D88" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E88" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F88" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G88" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H88" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I88" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J88">
         <v>2024</v>
       </c>
       <c r="K88" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="L88" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M88" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="O88" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="89" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
+        <v>203</v>
+      </c>
+      <c r="B89" t="s">
         <v>204</v>
       </c>
-      <c r="B89" t="s">
-        <v>205</v>
-      </c>
       <c r="C89" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D89" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E89" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F89" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G89" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H89" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I89" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J89">
         <v>2024</v>
       </c>
       <c r="K89" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="L89" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M89" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="O89" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="90" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B90" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C90" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D90" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E90" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F90" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G90" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H90" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I90" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J90">
         <v>2025</v>
       </c>
       <c r="K90" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="L90" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M90" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N90" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="O90" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="91" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B91" t="s">
+        <v>15</v>
+      </c>
+      <c r="C91" t="s">
         <v>16</v>
       </c>
-      <c r="C91" t="s">
+      <c r="D91" t="s">
         <v>17</v>
       </c>
-      <c r="D91" t="s">
-        <v>18</v>
-      </c>
       <c r="E91" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F91" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G91" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H91" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I91" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J91">
         <v>2025</v>
       </c>
       <c r="K91" t="s">
+        <v>238</v>
+      </c>
+      <c r="L91" t="s">
+        <v>23</v>
+      </c>
+      <c r="M91" t="s">
+        <v>207</v>
+      </c>
+      <c r="N91" t="s">
         <v>240</v>
       </c>
-      <c r="L91" t="s">
-        <v>24</v>
-      </c>
-      <c r="M91" t="s">
-        <v>208</v>
-      </c>
-      <c r="N91" t="s">
-        <v>242</v>
-      </c>
       <c r="O91" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="92" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
+        <v>208</v>
+      </c>
+      <c r="B92" t="s">
         <v>209</v>
       </c>
-      <c r="B92" t="s">
-        <v>210</v>
-      </c>
       <c r="C92" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D92" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E92" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F92" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G92" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H92" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I92" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J92">
         <v>2025</v>
       </c>
       <c r="K92" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="L92" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M92" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="O92" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="93" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
+        <v>210</v>
+      </c>
+      <c r="B93" t="s">
         <v>211</v>
       </c>
-      <c r="B93" t="s">
-        <v>212</v>
-      </c>
       <c r="C93" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D93" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E93" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F93" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G93" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H93" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I93" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J93">
         <v>2025</v>
       </c>
       <c r="K93" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="L93" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M93" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="O93" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="94" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
+        <v>212</v>
+      </c>
+      <c r="B94" t="s">
         <v>213</v>
       </c>
-      <c r="B94" t="s">
-        <v>214</v>
-      </c>
       <c r="C94" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D94" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E94" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F94" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G94" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H94" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I94" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J94">
         <v>2025</v>
       </c>
       <c r="K94" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="L94" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M94" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="O94" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="95" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
+        <v>214</v>
+      </c>
+      <c r="B95" t="s">
         <v>215</v>
       </c>
-      <c r="B95" t="s">
-        <v>216</v>
-      </c>
       <c r="C95" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D95" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E95" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F95" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G95" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H95" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I95" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J95">
         <v>2025</v>
       </c>
       <c r="K95" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="L95" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M95" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="O95" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="96" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
+        <v>216</v>
+      </c>
+      <c r="B96" t="s">
         <v>217</v>
       </c>
-      <c r="B96" t="s">
-        <v>218</v>
-      </c>
       <c r="C96" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D96" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E96" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F96" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G96" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H96" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I96" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J96">
         <v>2025</v>
       </c>
       <c r="K96" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="L96" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M96" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="O96" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="97" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
+        <v>218</v>
+      </c>
+      <c r="B97" t="s">
         <v>219</v>
       </c>
-      <c r="B97" t="s">
-        <v>220</v>
-      </c>
       <c r="C97" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D97" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E97" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F97" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G97" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H97" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I97" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J97">
         <v>2025</v>
       </c>
       <c r="K97" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="L97" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M97" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="O97" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="98" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
+        <v>220</v>
+      </c>
+      <c r="B98" t="s">
         <v>221</v>
       </c>
-      <c r="B98" t="s">
-        <v>222</v>
-      </c>
       <c r="C98" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D98" t="s">
+        <v>35</v>
+      </c>
+      <c r="E98" t="s">
         <v>36</v>
       </c>
-      <c r="E98" t="s">
-        <v>37</v>
-      </c>
       <c r="F98" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G98" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H98" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I98" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J98">
         <v>2025</v>
       </c>
       <c r="K98" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="L98" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M98" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="O98" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="99" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
+        <v>222</v>
+      </c>
+      <c r="B99" t="s">
         <v>223</v>
       </c>
-      <c r="B99" t="s">
-        <v>224</v>
-      </c>
       <c r="C99" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D99" t="s">
+        <v>35</v>
+      </c>
+      <c r="E99" t="s">
         <v>36</v>
       </c>
-      <c r="E99" t="s">
-        <v>37</v>
-      </c>
       <c r="F99" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G99" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H99" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I99" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J99">
         <v>2025</v>
       </c>
       <c r="K99" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="L99" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M99" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="O99" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="100" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
+        <v>224</v>
+      </c>
+      <c r="B100" t="s">
         <v>225</v>
       </c>
-      <c r="B100" t="s">
-        <v>226</v>
-      </c>
       <c r="C100" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D100" t="s">
+        <v>35</v>
+      </c>
+      <c r="E100" t="s">
         <v>36</v>
       </c>
-      <c r="E100" t="s">
-        <v>37</v>
-      </c>
       <c r="F100" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G100" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H100" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I100" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J100">
         <v>2025</v>
       </c>
       <c r="K100" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="L100" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M100" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="O100" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="P100" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="101" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
+        <v>226</v>
+      </c>
+      <c r="B101" t="s">
         <v>227</v>
       </c>
-      <c r="B101" t="s">
-        <v>228</v>
-      </c>
       <c r="C101" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D101" t="s">
+        <v>35</v>
+      </c>
+      <c r="E101" t="s">
         <v>36</v>
       </c>
-      <c r="E101" t="s">
-        <v>37</v>
-      </c>
       <c r="F101" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G101" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H101" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I101" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J101">
         <v>2025</v>
       </c>
       <c r="K101" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="L101" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M101" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="O101" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="102" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
+        <v>228</v>
+      </c>
+      <c r="B102" t="s">
         <v>229</v>
       </c>
-      <c r="B102" t="s">
-        <v>230</v>
-      </c>
       <c r="C102" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D102" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E102" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F102" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G102" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H102" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I102" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J102">
         <v>2025</v>
       </c>
       <c r="K102" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="L102" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M102" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="O102" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="103" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
+        <v>230</v>
+      </c>
+      <c r="B103" t="s">
         <v>231</v>
       </c>
-      <c r="B103" t="s">
-        <v>232</v>
-      </c>
       <c r="C103" t="s">
+        <v>27</v>
+      </c>
+      <c r="D103" t="s">
         <v>28</v>
       </c>
-      <c r="D103" t="s">
-        <v>29</v>
-      </c>
       <c r="E103" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F103" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G103" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H103" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I103" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J103">
         <v>2025</v>
       </c>
       <c r="K103" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="L103" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M103" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="O103" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="104" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
+        <v>232</v>
+      </c>
+      <c r="B104" t="s">
         <v>233</v>
       </c>
-      <c r="B104" t="s">
-        <v>234</v>
-      </c>
       <c r="C104" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D104" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E104" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F104" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G104" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H104" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I104" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J104">
         <v>2025</v>
       </c>
       <c r="K104" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="L104" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M104" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="O104" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="105" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
+        <v>234</v>
+      </c>
+      <c r="B105" t="s">
         <v>235</v>
       </c>
-      <c r="B105" t="s">
-        <v>236</v>
-      </c>
       <c r="C105" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D105" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E105" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F105" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G105" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H105" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I105" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J105">
         <v>2025</v>
       </c>
       <c r="K105" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="L105" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M105" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="O105" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="106" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
+        <v>236</v>
+      </c>
+      <c r="B106" t="s">
         <v>237</v>
       </c>
-      <c r="B106" t="s">
-        <v>238</v>
-      </c>
       <c r="C106" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D106" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E106" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F106" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G106" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H106" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I106" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J106">
         <v>2025</v>
       </c>
       <c r="K106" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="L106" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M106" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="N106" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="O106" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
   </sheetData>
